--- a/AAII_Financials/Quarterly/GOLD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GOLD_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,410 +656,422 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="29" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="30" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3059000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2862000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2833000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2643000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2774000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2527000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2859000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2853000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3310000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2826000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2893000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2956000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3279000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3540000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3055000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2721000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2883000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2678000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2063000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2093000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1904000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1837000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1712000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1790000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2228000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1993000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2160000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>316700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>356400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>300000</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2139000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1915000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1937000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1941000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2093000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1815000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1850000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1739000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1905000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1768000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1704000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1712000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1814000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1927000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1900000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1776000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1987000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1889000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1545000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1490000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1577000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1315000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1176000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1152000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1411000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1270000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1277000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>167400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>196700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>169100</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>920000</v>
+      </c>
+      <c r="E10" s="3">
         <v>947000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>896000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>702000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>681000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>712000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1009000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1114000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1405000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1058000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1189000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1244000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1465000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1613000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1155000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>945000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>896000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>789000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>518000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>603000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>327000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>522000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>536000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>638000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>817000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>723000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>883000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>149300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>159700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>130900</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1092,100 +1104,104 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>103000</v>
+      </c>
+      <c r="E12" s="3">
         <v>86000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>101000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>71000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>106000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>77000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>100000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>67000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>82000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>67000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>77000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>61000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>74000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>72000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>78000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>71000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>40000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>86000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>98000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>74000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>87000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>89000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>97000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>73000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>98000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>100000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>81000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>10900</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>8000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>11200</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1276,100 +1292,106 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>331000</v>
+      </c>
+      <c r="E14" s="3">
         <v>40000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>39000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>23000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1652000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>60000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>17000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>19000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>57000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>27000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>23000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-77000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>64000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-80000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>81000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-311000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-514000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-2726000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>27000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>44000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>451000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>495000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>67000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>28000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>1029000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>117000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>18000</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
       <c r="AE14" s="3">
         <v>0</v>
       </c>
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1460,8 +1482,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1491,192 +1516,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>2272000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2007000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2023000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2111000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3658000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1827000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1774000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1758000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1770000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1798000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1765000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1665000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1737000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1904000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2093000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1583000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>217000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>-670000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1681000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1666000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2176000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1988000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1536000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1264000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2514000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1585000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>602000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>192200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>223900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>196300</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>787000</v>
+      </c>
+      <c r="E18" s="3">
         <v>855000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>810000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>532000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-884000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>700000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1085000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1095000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1540000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1028000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1128000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1291000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1542000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1636000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>962000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1138000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2666000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>3348000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>382000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>427000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-272000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-151000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>176000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>526000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-286000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>408000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1558000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>124500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>132500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>103700</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1709,468 +1741,484 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>58000</v>
+      </c>
+      <c r="E20" s="3">
         <v>36000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>42000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>40000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>21000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>12000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-4000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-3000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-10000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1000</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-2000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-6000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>325000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-13000</v>
-      </c>
-      <c r="U20" s="3">
-        <v>-12000</v>
       </c>
       <c r="V20" s="3">
         <v>-12000</v>
       </c>
       <c r="W20" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="X20" s="3">
         <v>-2000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-20000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>4000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>5000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>7000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>6000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-4800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-4700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>1409000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1395000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1332000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1067000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-259000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1169000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1557000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1553000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2098000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1563000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1618000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1796000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2085000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2210000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1526000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1656000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>3563000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>3894000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>836000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>850000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>167000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>192000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>505000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>855000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>153000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>805000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1973000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>158600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>263000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>113700</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>74000</v>
+      </c>
+      <c r="E22" s="3">
         <v>88000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>86000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>98000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>84000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>87000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>85000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>86000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>85000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>90000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>81000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>85000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>79000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>81000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>80000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>83000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>431000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>109000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>106000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>108000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>115000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>110000</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>137000</v>
       </c>
       <c r="Z22" s="3">
         <v>137000</v>
       </c>
       <c r="AA22" s="3">
+        <v>137000</v>
+      </c>
+      <c r="AB22" s="3">
         <v>135000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>144000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>153000</v>
       </c>
-      <c r="AD22" s="3">
-        <v>0</v>
-      </c>
       <c r="AE22" s="3">
         <v>0</v>
       </c>
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>771000</v>
+      </c>
+      <c r="E23" s="3">
         <v>803000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>766000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>474000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-947000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>625000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>996000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1007000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1456000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>935000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1037000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1204000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1462000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1555000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>880000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1049000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2560000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>3226000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>264000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>307000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-389000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-281000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>40000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>393000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-416000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>271000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1411000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>119600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>127800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>109500</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>174000</v>
+      </c>
+      <c r="E24" s="3">
         <v>218000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>264000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>205000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-131000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>215000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>279000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>301000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>304000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>323000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>343000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>374000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>404000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>284000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>258000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>386000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>784000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>791000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>41000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>167000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>776000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>105000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>116000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>201000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>394000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>314000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>274000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>34700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>33500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>32200</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2261,192 +2309,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>597000</v>
+      </c>
+      <c r="E26" s="3">
         <v>585000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>502000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>269000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-816000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>410000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>717000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>706000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1152000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>612000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>694000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>830000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1058000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1271000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>622000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>663000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1776000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2435000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>223000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>140000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1165000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-386000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-76000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>192000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-810000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-43000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1137000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>84900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>94300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>77300</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>479000</v>
+      </c>
+      <c r="E27" s="3">
         <v>368000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>305000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>120000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-735000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>241000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>488000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>438000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>726000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>347000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>411000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>538000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>685000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>882000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>357000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>400000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1387000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2277000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>194000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>111000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1197000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-412000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-94000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>158000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-657000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-11000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1084000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>69800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>78500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>65600</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2537,8 +2594,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2593,8 +2653,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>91</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>91</v>
@@ -2611,17 +2671,17 @@
       <c r="Z29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="AB29" s="3">
         <v>343000</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AD29" s="3">
-        <v>0</v>
+      <c r="AD29" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="AE29" s="3">
         <v>0</v>
@@ -2629,8 +2689,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -2721,8 +2784,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -2813,192 +2879,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>-58000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-36000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-42000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-40000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-21000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-12000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>4000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>3000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>10000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1000</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>2000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>6000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-325000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>13000</v>
-      </c>
-      <c r="U32" s="3">
-        <v>12000</v>
       </c>
       <c r="V32" s="3">
         <v>12000</v>
       </c>
       <c r="W32" s="3">
+        <v>12000</v>
+      </c>
+      <c r="X32" s="3">
         <v>2000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>20000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-5000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-7000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-6000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>4800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>4700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-5800</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>479000</v>
+      </c>
+      <c r="E33" s="3">
         <v>368000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>305000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>120000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-735000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>241000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>488000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>438000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>726000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>347000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>411000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>538000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>685000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>882000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>357000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>400000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1387000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2277000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>194000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>111000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-1197000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-412000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-94000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>158000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-314000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-11000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1084000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>69800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>78500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>65600</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3089,197 +3164,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>479000</v>
+      </c>
+      <c r="E35" s="3">
         <v>368000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>305000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>120000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-735000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>241000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>488000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>438000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>726000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>347000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>411000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>538000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>685000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>882000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>357000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>400000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1387000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2277000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>194000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>111000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-1197000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-412000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-94000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>158000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-314000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-11000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1084000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>69800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>78500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>65600</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -3312,8 +3396,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -3346,100 +3431,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>4148000</v>
+      </c>
+      <c r="E41" s="3">
         <v>4261000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4157000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4377000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4440000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5240000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5780000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5887000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5280000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5043000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5138000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5672000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5188000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4744000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3743000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3327000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3314000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2405000</v>
-      </c>
-      <c r="U41" s="3">
-        <v>2153000</v>
       </c>
       <c r="V41" s="3">
         <v>2153000</v>
       </c>
       <c r="W41" s="3">
+        <v>2153000</v>
+      </c>
+      <c r="X41" s="3">
         <v>1571000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1697000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2085000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2384000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2234000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2025000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2926000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>600300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>516300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>361100</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
@@ -3530,560 +3619,581 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>693000</v>
+      </c>
+      <c r="E43" s="3">
         <v>561000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>603000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>557000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>554000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>499000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>577000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>640000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>623000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>600000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>554000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>530000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>558000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>509000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>407000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>371000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>363000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>311000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>427000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>383000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>248000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>189000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>194000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>173000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>239000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>224000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>190000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>236800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>231400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>223400</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>1782000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1913000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1868000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1913000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1781000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1691000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1699000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1766000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1734000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1821000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1825000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1776000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1878000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2111000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2160000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2159000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2289000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2265000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1930000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1966000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1852000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1898000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1940000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1887000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1890000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>2038000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1901000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>124600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>119000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>135800</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>815000</v>
+      </c>
+      <c r="E45" s="3">
         <v>684000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>742000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1691000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1690000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>786000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>754000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>722000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>612000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>547000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>522000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>806000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>519000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>495000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>609000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>594000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>921000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>529000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>333000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>372000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>307000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>319000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>356000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>352000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>321000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>455000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>486000</v>
       </c>
-      <c r="AD45" s="3">
-        <v>0</v>
-      </c>
       <c r="AE45" s="3">
         <v>0</v>
       </c>
       <c r="AF45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>7438000</v>
+      </c>
+      <c r="E46" s="3">
         <v>7419000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7370000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>8538000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>8465000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>8216000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8810000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>9015000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>8249000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>8011000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>8039000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>8784000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>8143000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>7859000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>6919000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>6451000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>6887000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>5510000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4843000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4874000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3978000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4103000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4575000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4796000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4684000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>4742000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>5503000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>961600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>866800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>720300</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>4133000</v>
+      </c>
+      <c r="E47" s="3">
         <v>3998000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>4004000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>3969000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>3983000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>4064000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>4113000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>4334000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4594000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4762000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>4715000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4646000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>4670000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>4643000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>4587000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>4556000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>4527000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>4474000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>4459000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>4444000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1234000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1233000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1214000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1233000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1213000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1243000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1218000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1446800</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1448600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1479500</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>26416000</v>
+      </c>
+      <c r="E48" s="3">
         <v>26621000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>26311000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>26084000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>25821000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>25329000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>25202000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>25153000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>24954000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>24747000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>24755000</v>
-      </c>
-      <c r="N48" s="3">
-        <v>24628000</v>
       </c>
       <c r="O48" s="3">
         <v>24628000</v>
       </c>
       <c r="P48" s="3">
+        <v>24628000</v>
+      </c>
+      <c r="Q48" s="3">
         <v>24698000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>24727000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>24809000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>24141000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>24758000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>16890000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>16891000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>12826000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>13226000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>13727000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>13755000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>13806000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>13961000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>13943000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1564000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1560900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1567300</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
@@ -4100,7 +4210,7 @@
         <v>3730000</v>
       </c>
       <c r="H49" s="3">
-        <v>4918000</v>
+        <v>3730000</v>
       </c>
       <c r="I49" s="3">
         <v>4918000</v>
@@ -4109,73 +4219,76 @@
         <v>4918000</v>
       </c>
       <c r="K49" s="3">
+        <v>4918000</v>
+      </c>
+      <c r="L49" s="3">
         <v>4919000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4920000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4927000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4937000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4938000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4939000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4983000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4999000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4995000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>5025000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3064000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3037000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1403000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1559000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1560000</v>
-      </c>
-      <c r="Z49" s="3">
-        <v>1585000</v>
       </c>
       <c r="AA49" s="3">
         <v>1585000</v>
       </c>
       <c r="AB49" s="3">
+        <v>1585000</v>
+      </c>
+      <c r="AC49" s="3">
         <v>1556000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1586000</v>
       </c>
-      <c r="AD49" s="3">
-        <v>0</v>
-      </c>
       <c r="AE49" s="3">
         <v>0</v>
       </c>
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -4266,8 +4379,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -4358,100 +4474,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>4094000</v>
+      </c>
+      <c r="E52" s="3">
         <v>3827000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3871000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3831000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3966000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3915000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3799000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3886000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4174000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4194000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4092000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3853000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4127000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3977000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3964000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4124000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3842000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4100000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3346000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3383000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3190000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3997000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>4046000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>4027000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>4020000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>3570000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>3557000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>163600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>164700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>151000</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -4542,100 +4664,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>45811000</v>
+      </c>
+      <c r="E54" s="3">
         <v>45595000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>45286000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>46152000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>45965000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>46442000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>46842000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>47306000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>46890000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>46634000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>46528000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>46848000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>46506000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>46116000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>45180000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>44939000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>44392000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>43867000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>32602000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>32629000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>22631000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>24118000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>25122000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>25396000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>25308000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>25072000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>25807000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>4136000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>4041000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>3918100</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -4668,8 +4796,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -4702,126 +4831,130 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>1503000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1584000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1525000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1504000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1556000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1571000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1537000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1525000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1448000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1444000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1157000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1168000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1458000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1032000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1072000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1140000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1155000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1337000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1064000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1213000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1101000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1125000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>944000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1046000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1059000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1118000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1044000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>120000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>127400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>136700</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E58" s="3">
         <v>8000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>13000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>12000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>13000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>12000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>13000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>14000</v>
-      </c>
-      <c r="K58" s="3">
-        <v>15000</v>
       </c>
       <c r="L58" s="3">
         <v>15000</v>
@@ -4830,331 +4963,340 @@
         <v>15000</v>
       </c>
       <c r="N58" s="3">
+        <v>15000</v>
+      </c>
+      <c r="O58" s="3">
         <v>13000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>20000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>21000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>26000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>29000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>375000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>66000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>303000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>308000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>43000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>49000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>680000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>57000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>59000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>63000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>116000</v>
       </c>
-      <c r="AD58" s="3">
-        <v>0</v>
-      </c>
       <c r="AE58" s="3">
         <v>0</v>
       </c>
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>842000</v>
+      </c>
+      <c r="E59" s="3">
         <v>826000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>732000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1690000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1551000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>605000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>680000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>708000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>623000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>521000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>626000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1150000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>742000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>698000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>713000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>801000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>846000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>441000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>415000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>463000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>524000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>375000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>536000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>595000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>629000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>557000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>386000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>71100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>61000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>34700</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>2356000</v>
+      </c>
+      <c r="E60" s="3">
         <v>2418000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2270000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3206000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3120000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2188000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2230000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2247000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2086000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1980000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1798000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2331000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2220000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1751000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1811000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1970000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2376000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1844000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1782000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1984000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1668000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1549000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2160000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1698000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1747000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1738000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1546000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>191100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>188400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>171400</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>4715000</v>
+      </c>
+      <c r="E61" s="3">
         <v>4767000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4761000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4765000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4769000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5083000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5131000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5130000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5135000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5139000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5137000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5140000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5135000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>5140000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>5142000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>5150000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>5161000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>5494000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>5504000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>5499000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>5695000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>5696000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>5712000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>6344000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>6364000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>6384000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>7328000</v>
-      </c>
-      <c r="AD61" s="3">
-        <v>2800</v>
       </c>
       <c r="AE61" s="3">
         <v>2800</v>
@@ -5162,100 +5304,106 @@
       <c r="AF61" s="3">
         <v>2800</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>6738000</v>
+      </c>
+      <c r="E62" s="3">
         <v>6712000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>6770000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>6863000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>6787000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>6864000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>6947000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>7303000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7362000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7425000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>7419000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>7298000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>7441000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>7575000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>7481000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>7464000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>7028000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>8129000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>6849000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>6844000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>5883000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>6187000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>6144000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>6088000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>6130000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>5328000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>5248000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>101700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>97800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>88900</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -5346,8 +5494,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5438,8 +5589,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -5530,100 +5684,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>22470000</v>
+      </c>
+      <c r="E66" s="3">
         <v>22575000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>22447000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>23439000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>23194000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>22578000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>22731000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>23131000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>23033000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>23016000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>22839000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>23174000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>23165000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>23317000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>23148000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>23252000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>22960000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>23718000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>16856000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>17031000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>15038000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>15211000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>15766000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>15917000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>16022000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>15458000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>16165000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>559400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>542300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>502400</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -5656,8 +5816,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -5748,8 +5909,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -5840,8 +6004,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -5932,8 +6099,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -6024,100 +6194,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>-6713000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-7016000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-7208000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-7338000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-7282000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-6284000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-6173000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-6306000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-6566000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-7132000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-7320000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-7571000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-7949000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-8474000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-9214000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-9446000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-9722000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-11020000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-13227000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-13351000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-13453000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-12148000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-11701000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-11572000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-11759000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-11428000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-11382000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2014900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1956700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1874200</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -6208,8 +6384,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -6300,8 +6479,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -6392,100 +6574,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>23341000</v>
+      </c>
+      <c r="E76" s="3">
         <v>23020000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>22839000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>22713000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>22771000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>23864000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>24111000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>24175000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>23857000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>23618000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>23689000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>23674000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>23341000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>22799000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>22032000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>21687000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>21432000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>20149000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>15746000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>15598000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>7593000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>8907000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>9356000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>9479000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>9286000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>9614000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>9642000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>3576600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3498700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3415700</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -6576,197 +6764,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>479000</v>
+      </c>
+      <c r="E81" s="3">
         <v>368000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>305000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>120000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-735000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>241000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>488000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>438000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>726000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>347000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>411000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>538000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>685000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>882000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>357000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>400000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1387000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2277000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>194000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>111000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-1197000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-412000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-94000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>158000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-314000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-11000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1084000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>69800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>78500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>65600</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -6799,100 +6996,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>564000</v>
+      </c>
+      <c r="E83" s="3">
         <v>504000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>480000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>495000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>604000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>457000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>476000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>460000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>557000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>538000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>500000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>507000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>544000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>574000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>566000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>524000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>572000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>559000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>466000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>435000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>441000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>363000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>328000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>325000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>434000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>390000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>409000</v>
       </c>
-      <c r="AD83" s="3">
-        <v>0</v>
-      </c>
       <c r="AE83" s="3">
         <v>0</v>
       </c>
       <c r="AF83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -6983,8 +7184,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -7075,8 +7279,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -7167,8 +7374,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -7259,8 +7469,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -7351,100 +7564,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>997000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1127000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>832000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>776000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>795000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>758000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>924000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1004000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1387000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1050000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>639000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1302000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1638000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1859000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1031000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>889000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>875000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1004000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>434000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>520000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>411000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>706000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>141000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>507000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>590000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>532000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>448000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>133100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>204700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>119300</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -7477,100 +7696,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-861000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-768000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-769000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-688000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-891000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-792000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-755000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-611000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-669000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-569000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-658000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-539000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-546000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-548000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-509000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-451000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-446000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-502000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-379000</v>
-      </c>
-      <c r="V91" s="3">
-        <v>-374000</v>
       </c>
       <c r="W91" s="3">
         <v>-374000</v>
       </c>
       <c r="X91" s="3">
+        <v>-374000</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-387000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-313000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-326000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-350000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-307000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-405000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-41300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-50300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-32000</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -7661,8 +7884,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -7753,100 +7979,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-766000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-689000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-743000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-618000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-780000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-639000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-301000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>9000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-387000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-499000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-603000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-408000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-405000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-454000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-264000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-163000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>362000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-383000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-351000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>422000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-477000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-386000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-347000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-284000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-256000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-306000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>556000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-44700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-48000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-27900</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -7879,79 +8111,80 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
+        <v>-176000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-175000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-174000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-175000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-261000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-351000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-353000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-178000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-159000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-158000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-159000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-158000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-160000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-141000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-124000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-122000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-87000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-67000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-61000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-333000</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-31000</v>
       </c>
       <c r="X96" s="3">
         <v>-31000</v>
       </c>
       <c r="Y96" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-32000</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-31000</v>
       </c>
       <c r="AA96" s="3">
         <v>-31000</v>
@@ -7960,19 +8193,22 @@
         <v>-31000</v>
       </c>
       <c r="AC96" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-32000</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
         <v>0</v>
       </c>
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -8063,8 +8299,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -8155,8 +8394,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -8247,109 +8489,115 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-342000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-333000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-309000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-221000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-815000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-656000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-727000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-406000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-763000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-646000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-570000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-409000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-789000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-408000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-348000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-709000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-328000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-369000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-82000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-360000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-57000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-704000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-92000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-72000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-126000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1127000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-355000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-4400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1000</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
         <v>0</v>
       </c>
@@ -8357,13 +8605,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="3">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="I101" s="3">
         <v>-3000</v>
       </c>
       <c r="J101" s="3">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -8375,50 +8623,50 @@
         <v>0</v>
       </c>
       <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
         <v>-1000</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
       <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
         <v>4000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-3000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-4000</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
       <c r="T101" s="3">
         <v>0</v>
       </c>
       <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
         <v>-1000</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
       <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
         <v>-3000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-4000</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>-1000</v>
       </c>
       <c r="Z101" s="3">
         <v>-1000</v>
       </c>
       <c r="AA101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AB101" s="3">
         <v>1000</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
-      </c>
       <c r="AC101" s="3">
         <v>0</v>
       </c>
@@ -8431,96 +8679,102 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>-113000</v>
+      </c>
+      <c r="E102" s="3">
         <v>104000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-220000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-63000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-800000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-540000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-107000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>607000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>237000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-95000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-534000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>484000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>444000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1001000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>416000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>13000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>909000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>252000</v>
       </c>
-      <c r="U102" s="3">
-        <v>0</v>
-      </c>
       <c r="V102" s="3">
+        <v>0</v>
+      </c>
+      <c r="W102" s="3">
         <v>582000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-126000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-388000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-299000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>150000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>209000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-901000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>649000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>84000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>155200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>88400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GOLD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GOLD_QTR_FIN.xlsx
@@ -656,422 +656,435 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="30" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="31" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2747000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3059000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2862000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2833000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2643000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2774000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2527000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2859000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2853000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3310000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2826000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2893000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2956000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3279000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3540000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3055000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2721000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2883000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2678000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2063000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2093000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1904000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1837000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1712000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1790000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2228000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1993000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2160000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>316700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>356400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>300000</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1936000</v>
+      </c>
+      <c r="E9" s="3">
         <v>2139000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1915000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1937000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1941000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2093000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1815000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1850000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1739000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1905000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1768000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1704000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1712000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1814000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1927000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1900000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1776000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1987000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1889000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1545000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1490000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1577000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1315000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1176000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1152000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1411000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1270000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1277000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>167400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>196700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>169100</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>811000</v>
+      </c>
+      <c r="E10" s="3">
         <v>920000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>947000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>896000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>702000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>681000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>712000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1009000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1114000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1405000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1058000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1189000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1244000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1465000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1613000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1155000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>945000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>896000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>789000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>518000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>603000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>327000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>522000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>536000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>638000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>817000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>723000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>883000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>149300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>159700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>130900</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1105,103 +1118,107 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>95000</v>
+      </c>
+      <c r="E12" s="3">
         <v>103000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>86000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>101000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>71000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>106000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>77000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>100000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>67000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>82000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>67000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>77000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>61000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>74000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>72000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>78000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>71000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>40000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>86000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>98000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>74000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>87000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>89000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>97000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>73000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>98000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>100000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>81000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>10900</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>8000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>11200</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1295,103 +1312,109 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E14" s="3">
         <v>331000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>40000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>39000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>23000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1652000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>60000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>17000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>19000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>57000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>27000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>23000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-77000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>64000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-80000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>81000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-311000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-514000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-2726000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>27000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>44000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>451000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>495000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>67000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>28000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>1029000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>117000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>18000</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
       <c r="AF14" s="3">
         <v>0</v>
       </c>
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1485,8 +1508,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1517,198 +1543,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>2055000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2272000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2007000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2023000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2111000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3658000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1827000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1774000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1758000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1770000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1798000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1765000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1665000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1737000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1904000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2093000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1583000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>217000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>-670000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1681000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1666000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2176000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1988000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1536000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1264000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2514000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1585000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>602000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>192200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>223900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>196300</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>692000</v>
+      </c>
+      <c r="E18" s="3">
         <v>787000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>855000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>810000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>532000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-884000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>700000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1085000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1095000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1540000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1028000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1128000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1291000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1542000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1636000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>962000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1138000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2666000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>3348000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>382000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>427000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-272000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-151000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>176000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>526000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-286000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>408000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1558000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>124500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>132500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>103700</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1742,388 +1775,401 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>49000</v>
+      </c>
+      <c r="E20" s="3">
         <v>58000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>36000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>42000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>40000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>21000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>12000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-4000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-3000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-10000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>-2000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-6000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>325000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-13000</v>
-      </c>
-      <c r="V20" s="3">
-        <v>-12000</v>
       </c>
       <c r="W20" s="3">
         <v>-12000</v>
       </c>
       <c r="X20" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-20000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>4000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>5000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>7000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>6000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-4800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-4700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>1215000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1409000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1395000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1332000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1067000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-259000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1169000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1557000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1553000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2098000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1563000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1618000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1796000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2085000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2210000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1526000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1656000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>3563000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>3894000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>836000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>850000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>167000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>192000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>505000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>855000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>153000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>805000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1973000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>158600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>263000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>113700</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>80000</v>
+      </c>
+      <c r="E22" s="3">
         <v>74000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>88000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>86000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>98000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>84000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>87000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>85000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>86000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>85000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>90000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>81000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>85000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>79000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>81000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>80000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>83000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>431000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>109000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>106000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>108000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>115000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>110000</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>137000</v>
       </c>
       <c r="AA22" s="3">
         <v>137000</v>
       </c>
       <c r="AB22" s="3">
+        <v>137000</v>
+      </c>
+      <c r="AC22" s="3">
         <v>135000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>144000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>153000</v>
       </c>
-      <c r="AE22" s="3">
-        <v>0</v>
-      </c>
       <c r="AF22" s="3">
         <v>0</v>
       </c>
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>661000</v>
+      </c>
+      <c r="E23" s="3">
         <v>771000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>803000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>766000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>474000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-947000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>625000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>996000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1007000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1456000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>935000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1037000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1204000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1462000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1555000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>880000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1049000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2560000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>3226000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>264000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>307000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-389000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-281000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>40000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>393000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-416000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>271000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1411000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>119600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>127800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>109500</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
@@ -2131,94 +2177,97 @@
         <v>174000</v>
       </c>
       <c r="E24" s="3">
+        <v>174000</v>
+      </c>
+      <c r="F24" s="3">
         <v>218000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>264000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>205000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-131000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>215000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>279000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>301000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>304000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>323000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>343000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>374000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>404000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>284000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>258000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>386000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>784000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>791000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>41000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>167000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>776000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>105000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>116000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>201000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>394000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>314000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>274000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>34700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>33500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>32200</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2312,198 +2361,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>487000</v>
+      </c>
+      <c r="E26" s="3">
         <v>597000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>585000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>502000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>269000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-816000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>410000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>717000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>706000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1152000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>612000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>694000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>830000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1058000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1271000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>622000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>663000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1776000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2435000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>223000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>140000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1165000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-386000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-76000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>192000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-810000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-43000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1137000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>84900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>94300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>77300</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>295000</v>
+      </c>
+      <c r="E27" s="3">
         <v>479000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>368000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>305000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>120000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-735000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>241000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>488000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>438000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>726000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>347000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>411000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>538000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>685000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>882000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>357000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>400000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1387000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2277000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>194000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>111000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1197000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-412000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-94000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>158000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-657000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-11000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1084000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>69800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>78500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>65600</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2597,8 +2655,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2656,8 +2717,8 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>91</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>91</v>
@@ -2674,17 +2735,17 @@
       <c r="AA29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC29" s="3">
         <v>343000</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
+      <c r="AE29" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="AF29" s="3">
         <v>0</v>
@@ -2692,8 +2753,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -2787,8 +2851,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -2882,198 +2949,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>-49000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-58000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-36000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-42000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-40000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-21000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-12000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>4000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>3000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>10000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1000</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>2000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>6000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-325000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>13000</v>
-      </c>
-      <c r="V32" s="3">
-        <v>12000</v>
       </c>
       <c r="W32" s="3">
         <v>12000</v>
       </c>
       <c r="X32" s="3">
+        <v>12000</v>
+      </c>
+      <c r="Y32" s="3">
         <v>2000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>20000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-5000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-7000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-6000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>4800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>4700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-5800</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>295000</v>
+      </c>
+      <c r="E33" s="3">
         <v>479000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>368000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>305000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>120000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-735000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>241000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>488000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>438000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>726000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>347000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>411000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>538000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>685000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>882000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>357000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>400000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1387000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2277000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>194000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>111000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1197000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-412000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-94000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>158000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-314000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-11000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1084000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>69800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>78500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>65600</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3167,203 +3243,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>295000</v>
+      </c>
+      <c r="E35" s="3">
         <v>479000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>368000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>305000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>120000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-735000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>241000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>488000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>438000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>726000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>347000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>411000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>538000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>685000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>882000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>357000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>400000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1387000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2277000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>194000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>111000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1197000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-412000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-94000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>158000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-314000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-11000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1084000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>69800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>78500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>65600</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -3397,8 +3482,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -3432,103 +3518,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>3942000</v>
+      </c>
+      <c r="E41" s="3">
         <v>4148000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4261000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4157000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4377000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4440000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5240000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5780000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5887000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5280000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5043000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5138000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5672000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5188000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4744000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3743000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3327000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3314000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2405000</v>
-      </c>
-      <c r="V41" s="3">
-        <v>2153000</v>
       </c>
       <c r="W41" s="3">
         <v>2153000</v>
       </c>
       <c r="X41" s="3">
+        <v>2153000</v>
+      </c>
+      <c r="Y41" s="3">
         <v>1571000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1697000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2085000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2384000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2234000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2025000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2926000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>600300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>516300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>361100</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
@@ -3622,583 +3712,604 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>654000</v>
+      </c>
+      <c r="E43" s="3">
         <v>693000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>561000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>603000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>557000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>554000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>499000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>577000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>640000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>623000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>600000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>554000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>530000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>558000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>509000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>407000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>371000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>363000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>311000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>427000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>383000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>248000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>189000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>194000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>173000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>239000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>224000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>190000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>236800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>231400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>223400</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>1805000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1782000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1913000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1868000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1913000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1781000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1691000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1699000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1766000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1734000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1821000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1825000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1776000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1878000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2111000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2160000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2159000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2289000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2265000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1930000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1966000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1852000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1898000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1940000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1887000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1890000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>2038000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1901000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>124600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>119000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>135800</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>880000</v>
+      </c>
+      <c r="E45" s="3">
         <v>815000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>684000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>742000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1691000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1690000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>786000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>754000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>722000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>612000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>547000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>522000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>806000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>519000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>495000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>609000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>594000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>921000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>529000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>333000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>372000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>307000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>319000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>356000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>352000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>321000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>455000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>486000</v>
       </c>
-      <c r="AE45" s="3">
-        <v>0</v>
-      </c>
       <c r="AF45" s="3">
         <v>0</v>
       </c>
       <c r="AG45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>7281000</v>
+      </c>
+      <c r="E46" s="3">
         <v>7438000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7419000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7370000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>8538000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>8465000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8216000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>8810000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9015000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>8249000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>8011000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>8039000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>8784000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>8143000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>7859000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>6919000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>6451000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>6887000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>5510000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4843000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4874000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3978000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4103000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4575000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4796000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>4684000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4742000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>5503000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>961600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>866800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>720300</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>4178000</v>
+      </c>
+      <c r="E47" s="3">
         <v>4133000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>3998000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>4004000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>3969000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>3983000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>4064000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>4113000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4334000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4594000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>4762000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4715000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>4646000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>4670000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>4643000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>4587000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>4556000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>4527000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>4474000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>4459000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>4444000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1234000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1233000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1214000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1233000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1213000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1243000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1218000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1446800</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1448600</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1479500</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>26648000</v>
+      </c>
+      <c r="E48" s="3">
         <v>26416000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>26621000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>26311000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>26084000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>25821000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>25329000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>25202000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>25153000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>24954000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>24747000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>24755000</v>
-      </c>
-      <c r="O48" s="3">
-        <v>24628000</v>
       </c>
       <c r="P48" s="3">
         <v>24628000</v>
       </c>
       <c r="Q48" s="3">
+        <v>24628000</v>
+      </c>
+      <c r="R48" s="3">
         <v>24698000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>24727000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>24809000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>24141000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>24758000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>16890000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>16891000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>12826000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>13226000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>13727000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>13755000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>13806000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>13961000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>13943000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1564000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1560900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1567300</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
-        <v>3730000</v>
+        <v>3729000</v>
       </c>
       <c r="E49" s="3">
         <v>3730000</v>
@@ -4213,7 +4324,7 @@
         <v>3730000</v>
       </c>
       <c r="I49" s="3">
-        <v>4918000</v>
+        <v>3730000</v>
       </c>
       <c r="J49" s="3">
         <v>4918000</v>
@@ -4222,73 +4333,76 @@
         <v>4918000</v>
       </c>
       <c r="L49" s="3">
+        <v>4918000</v>
+      </c>
+      <c r="M49" s="3">
         <v>4919000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4920000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4927000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4937000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4938000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4939000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4983000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4999000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4995000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>5025000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3064000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3037000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1403000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1559000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1560000</v>
-      </c>
-      <c r="AA49" s="3">
-        <v>1585000</v>
       </c>
       <c r="AB49" s="3">
         <v>1585000</v>
       </c>
       <c r="AC49" s="3">
+        <v>1585000</v>
+      </c>
+      <c r="AD49" s="3">
         <v>1556000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1586000</v>
       </c>
-      <c r="AE49" s="3">
-        <v>0</v>
-      </c>
       <c r="AF49" s="3">
         <v>0</v>
       </c>
       <c r="AG49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -4382,8 +4496,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -4477,103 +4594,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>4007000</v>
+      </c>
+      <c r="E52" s="3">
         <v>4094000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3827000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3871000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3831000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3966000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3915000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3799000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3886000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4174000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4194000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4092000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3853000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4127000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3977000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3964000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4124000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3842000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4100000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3346000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3383000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3190000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3997000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>4046000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>4027000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>4020000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>3570000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>3557000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>163600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>164700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>151000</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -4667,103 +4790,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>45843000</v>
+      </c>
+      <c r="E54" s="3">
         <v>45811000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>45595000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>45286000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>46152000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>45965000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>46442000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>46842000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>47306000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>46890000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>46634000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>46528000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>46848000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>46506000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>46116000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>45180000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>44939000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>44392000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>43867000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>32602000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>32629000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>22631000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>24118000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>25122000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>25396000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>25308000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>25072000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>25807000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>4136000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>4041000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>3918100</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -4797,8 +4926,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -4832,132 +4962,136 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>1360000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1503000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1584000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1525000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1504000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1556000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1571000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1537000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1525000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1448000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1444000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1157000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1168000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1458000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1032000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1072000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1140000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1155000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1337000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1064000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1213000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1101000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1125000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>944000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1046000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1059000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1118000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1044000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>120000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>127400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>136700</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E58" s="3">
         <v>11000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>8000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>13000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>12000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>13000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>12000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>13000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>14000</v>
-      </c>
-      <c r="L58" s="3">
-        <v>15000</v>
       </c>
       <c r="M58" s="3">
         <v>15000</v>
@@ -4966,340 +5100,349 @@
         <v>15000</v>
       </c>
       <c r="O58" s="3">
+        <v>15000</v>
+      </c>
+      <c r="P58" s="3">
         <v>13000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>20000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>21000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>26000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>29000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>375000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>66000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>303000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>308000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>43000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>49000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>680000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>57000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>59000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>63000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>116000</v>
       </c>
-      <c r="AE58" s="3">
-        <v>0</v>
-      </c>
       <c r="AF58" s="3">
         <v>0</v>
       </c>
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>823000</v>
+      </c>
+      <c r="E59" s="3">
         <v>842000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>826000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>732000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1690000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1551000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>605000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>680000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>708000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>623000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>521000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>626000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1150000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>742000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>698000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>713000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>801000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>846000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>441000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>415000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>463000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>524000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>375000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>536000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>595000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>629000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>557000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>386000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>71100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>61000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>34700</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>2195000</v>
+      </c>
+      <c r="E60" s="3">
         <v>2356000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2418000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2270000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3206000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3120000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2188000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2230000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2247000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2086000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1980000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1798000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2331000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2220000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1751000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1811000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1970000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2376000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1844000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1782000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1984000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1668000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1549000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2160000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1698000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1747000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1738000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1546000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>191100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>188400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>171400</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>4713000</v>
+      </c>
+      <c r="E61" s="3">
         <v>4715000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4767000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4761000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4765000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4769000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5083000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5131000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5130000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5135000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5139000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5137000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5140000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>5135000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>5140000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>5142000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>5150000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>5161000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>5494000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>5504000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>5499000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>5695000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>5696000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>5712000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>6344000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>6364000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>6384000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>7328000</v>
-      </c>
-      <c r="AE61" s="3">
-        <v>2800</v>
       </c>
       <c r="AF61" s="3">
         <v>2800</v>
@@ -5307,103 +5450,109 @@
       <c r="AG61" s="3">
         <v>2800</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>6718000</v>
+      </c>
+      <c r="E62" s="3">
         <v>6738000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>6712000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>6770000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>6863000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>6787000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>6864000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>6947000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7303000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7362000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>7425000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>7419000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>7298000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>7441000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>7575000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>7481000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>7464000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>7028000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>8129000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>6849000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>6844000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>5883000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>6187000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>6144000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>6088000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>6130000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>5328000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>5248000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>101700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>97800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>88900</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -5497,8 +5646,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5592,8 +5744,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -5687,103 +5842,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>22380000</v>
+      </c>
+      <c r="E66" s="3">
         <v>22470000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>22575000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>22447000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>23439000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>23194000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>22578000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>22731000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>23131000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>23033000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>23016000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>22839000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>23174000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>23165000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>23317000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>23148000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>23252000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>22960000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>23718000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>16856000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>17031000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>15038000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>15211000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>15766000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>15917000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>16022000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>15458000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>16165000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>559400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>542300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>502400</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -5817,8 +5978,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -5912,8 +6074,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -6007,8 +6172,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -6102,8 +6270,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -6197,103 +6368,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>-6594000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-6713000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-7016000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-7208000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-7338000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-7282000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-6284000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-6173000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-6306000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-6566000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-7132000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-7320000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-7571000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-7949000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-8474000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-9214000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-9446000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-9722000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-11020000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-13227000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-13351000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-13453000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-12148000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-11701000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-11572000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-11759000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-11428000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-11382000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>2014900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1956700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1874200</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -6387,8 +6564,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -6482,8 +6662,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -6577,103 +6760,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>23463000</v>
+      </c>
+      <c r="E76" s="3">
         <v>23341000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>23020000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>22839000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>22713000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>22771000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>23864000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>24111000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>24175000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>23857000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>23618000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>23689000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>23674000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>23341000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>22799000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>22032000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>21687000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>21432000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>20149000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>15746000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>15598000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>7593000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>8907000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>9356000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>9479000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>9286000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>9614000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>9642000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3576600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3498700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>3415700</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -6767,203 +6956,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>295000</v>
+      </c>
+      <c r="E81" s="3">
         <v>479000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>368000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>305000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>120000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-735000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>241000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>488000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>438000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>726000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>347000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>411000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>538000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>685000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>882000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>357000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>400000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1387000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2277000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>194000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>111000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1197000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-412000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-94000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>158000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-314000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-11000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1084000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>69800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>78500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>65600</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -6997,103 +7195,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>474000</v>
+      </c>
+      <c r="E83" s="3">
         <v>564000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>504000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>480000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>495000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>604000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>457000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>476000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>460000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>557000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>538000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>500000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>507000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>544000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>574000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>566000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>524000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>572000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>559000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>466000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>435000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>441000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>363000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>328000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>325000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>434000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>390000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>409000</v>
       </c>
-      <c r="AE83" s="3">
-        <v>0</v>
-      </c>
       <c r="AF83" s="3">
         <v>0</v>
       </c>
       <c r="AG83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -7187,8 +7389,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -7282,8 +7487,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -7377,8 +7585,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -7472,8 +7683,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -7567,103 +7781,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>760000</v>
+      </c>
+      <c r="E89" s="3">
         <v>997000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1127000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>832000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>776000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>795000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>758000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>924000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1004000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1387000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1050000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>639000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1302000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1638000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1859000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1031000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>889000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>875000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1004000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>434000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>520000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>411000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>706000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>141000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>507000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>590000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>532000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>448000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>133100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>204700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>119300</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -7697,103 +7917,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-728000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-861000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-768000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-769000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-688000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-891000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-792000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-755000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-611000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-669000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-569000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-658000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-539000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-546000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-548000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-509000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-451000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-446000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-502000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-379000</v>
-      </c>
-      <c r="W91" s="3">
-        <v>-374000</v>
       </c>
       <c r="X91" s="3">
         <v>-374000</v>
       </c>
       <c r="Y91" s="3">
+        <v>-374000</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-387000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-313000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-326000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-350000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-307000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-405000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-41300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-50300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-32000</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -7887,8 +8111,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -7982,103 +8209,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-680000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-766000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-689000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-743000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-618000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-780000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-639000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-301000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>9000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-387000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-499000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-603000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-408000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-405000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-454000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-264000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-163000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>362000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-383000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-351000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>422000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-477000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-386000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-347000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-284000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-256000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-306000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>556000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-44700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-48000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-27900</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -8112,82 +8345,83 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
+        <v>-175000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-176000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-175000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-174000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-175000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-261000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-351000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-353000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-178000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-159000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-158000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-159000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-158000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-160000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-141000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-124000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-122000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-87000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-67000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-61000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-333000</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-31000</v>
       </c>
       <c r="Y96" s="3">
         <v>-31000</v>
       </c>
       <c r="Z96" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-32000</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-31000</v>
       </c>
       <c r="AB96" s="3">
         <v>-31000</v>
@@ -8196,19 +8430,22 @@
         <v>-31000</v>
       </c>
       <c r="AD96" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-32000</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
         <v>0</v>
       </c>
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -8302,8 +8539,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -8397,8 +8637,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -8492,103 +8735,109 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-284000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-342000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-333000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-309000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-221000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-815000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-656000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-727000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-406000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-763000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-646000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-570000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-409000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-789000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-408000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-348000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-709000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-328000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-369000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-82000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-360000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-57000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-704000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-92000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-72000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-126000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1127000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-355000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-4400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
@@ -8596,11 +8845,11 @@
         <v>-2000</v>
       </c>
       <c r="E101" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F101" s="3">
         <v>-1000</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
         <v>0</v>
       </c>
@@ -8608,13 +8857,13 @@
         <v>0</v>
       </c>
       <c r="I101" s="3">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="J101" s="3">
         <v>-3000</v>
       </c>
       <c r="K101" s="3">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -8626,50 +8875,50 @@
         <v>0</v>
       </c>
       <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>-1000</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
       <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
         <v>4000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-3000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-4000</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
       <c r="U101" s="3">
         <v>0</v>
       </c>
       <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
         <v>-1000</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
       <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-4000</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>-1000</v>
       </c>
       <c r="AA101" s="3">
         <v>-1000</v>
       </c>
       <c r="AB101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AC101" s="3">
         <v>1000</v>
       </c>
-      <c r="AC101" s="3">
-        <v>0</v>
-      </c>
       <c r="AD101" s="3">
         <v>0</v>
       </c>
@@ -8682,99 +8931,105 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>-206000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-113000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>104000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-220000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-63000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-800000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-540000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-107000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>607000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>237000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-95000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-534000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>484000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>444000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1001000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>416000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>13000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>909000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>252000</v>
       </c>
-      <c r="V102" s="3">
-        <v>0</v>
-      </c>
       <c r="W102" s="3">
+        <v>0</v>
+      </c>
+      <c r="X102" s="3">
         <v>582000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-126000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-388000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-299000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>150000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>209000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-901000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>649000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>84000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>155200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>88400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GOLD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GOLD_QTR_FIN.xlsx
@@ -656,435 +656,448 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="31" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="32" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3162000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2747000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3059000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2862000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2833000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2643000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2774000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2527000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2859000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2853000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3310000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2826000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2893000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2956000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3279000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3540000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3055000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2721000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2883000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2678000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2063000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2093000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1904000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1837000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1712000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1790000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2228000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1993000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2160000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>316700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>356400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>300000</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1979000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1936000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2139000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1915000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1937000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1941000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2093000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1815000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1850000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1739000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1905000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1768000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1704000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1712000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1814000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1927000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1900000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1776000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1987000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1889000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1545000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1490000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1577000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1315000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1176000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1152000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1411000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1270000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1277000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>167400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>196700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>169100</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1183000</v>
+      </c>
+      <c r="E10" s="3">
         <v>811000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>920000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>947000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>896000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>702000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>681000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>712000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1009000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1114000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1405000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1058000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1189000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1244000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1465000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1613000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1155000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>945000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>896000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>789000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>518000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>603000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>327000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>522000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>536000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>638000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>817000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>723000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>883000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>149300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>159700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>130900</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1119,106 +1132,110 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>97000</v>
+      </c>
+      <c r="E12" s="3">
         <v>95000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>103000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>86000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>101000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>71000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>106000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>77000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>100000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>67000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>82000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>67000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>77000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>61000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>74000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>72000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>78000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>71000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>40000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>86000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>98000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>74000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>87000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>89000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>97000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>73000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>98000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>100000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>81000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>10900</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>8000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>11200</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1315,106 +1332,112 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E14" s="3">
         <v>21000</v>
       </c>
-      <c r="E14" s="3">
-        <v>331000</v>
-      </c>
       <c r="F14" s="3">
+        <v>311000</v>
+      </c>
+      <c r="G14" s="3">
         <v>40000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>39000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>23000</v>
       </c>
-      <c r="I14" s="3">
-        <v>1652000</v>
-      </c>
       <c r="J14" s="3">
+        <v>1637000</v>
+      </c>
+      <c r="K14" s="3">
         <v>60000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>17000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>19000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>57000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>27000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>23000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-77000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>64000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-80000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>81000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-311000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-514000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-2726000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>27000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>44000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>451000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>495000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>67000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>28000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>1029000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>117000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>18000</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
       <c r="AG14" s="3">
         <v>0</v>
       </c>
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1511,8 +1534,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1544,204 +1570,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>2070000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2055000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2272000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2007000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2023000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2111000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3658000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1827000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1774000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1758000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1770000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1798000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1765000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1665000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1737000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1904000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2093000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1583000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>217000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>-670000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1681000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1666000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2176000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1988000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1536000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1264000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2514000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1585000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>602000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>192200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>223900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>196300</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>1092000</v>
+      </c>
+      <c r="E18" s="3">
         <v>692000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>787000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>855000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>810000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>532000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-884000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>700000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1085000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1095000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1540000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1028000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1128000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1291000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1542000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1636000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>962000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1138000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2666000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>3348000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>382000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>427000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-272000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-151000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>176000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>526000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-286000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>408000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1558000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>124500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>132500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>103700</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1776,498 +1809,514 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>46000</v>
+      </c>
+      <c r="E20" s="3">
         <v>49000</v>
       </c>
-      <c r="E20" s="3">
-        <v>58000</v>
-      </c>
       <c r="F20" s="3">
+        <v>63000</v>
+      </c>
+      <c r="G20" s="3">
         <v>36000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>42000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>40000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>21000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>12000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-4000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-3000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-10000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1000</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>-2000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-6000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>325000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-13000</v>
-      </c>
-      <c r="W20" s="3">
-        <v>-12000</v>
       </c>
       <c r="X20" s="3">
         <v>-12000</v>
       </c>
       <c r="Y20" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-20000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>4000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>5000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>7000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>6000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-4800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-4700</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>1618000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1215000</v>
       </c>
-      <c r="E21" s="3">
-        <v>1409000</v>
-      </c>
       <c r="F21" s="3">
+        <v>1414000</v>
+      </c>
+      <c r="G21" s="3">
         <v>1395000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1332000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1067000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-259000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1169000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1557000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1553000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2098000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1563000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1618000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1796000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2085000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2210000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1526000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1656000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>3563000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>3894000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>836000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>850000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>167000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>192000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>505000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>855000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>153000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>805000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1973000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>158600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>263000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>113700</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>97000</v>
+      </c>
+      <c r="E22" s="3">
         <v>80000</v>
       </c>
-      <c r="E22" s="3">
-        <v>74000</v>
-      </c>
       <c r="F22" s="3">
+        <v>79000</v>
+      </c>
+      <c r="G22" s="3">
         <v>88000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>86000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>98000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>84000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>87000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>85000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>86000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>85000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>90000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>81000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>85000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>79000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>81000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>80000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>83000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>431000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>109000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>106000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>108000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>115000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>110000</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>137000</v>
       </c>
       <c r="AB22" s="3">
         <v>137000</v>
       </c>
       <c r="AC22" s="3">
+        <v>137000</v>
+      </c>
+      <c r="AD22" s="3">
         <v>135000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>144000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>153000</v>
       </c>
-      <c r="AF22" s="3">
-        <v>0</v>
-      </c>
       <c r="AG22" s="3">
         <v>0</v>
       </c>
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>1041000</v>
+      </c>
+      <c r="E23" s="3">
         <v>661000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>771000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>803000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>766000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>474000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-947000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>625000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>996000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1007000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1456000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>935000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1037000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1204000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1462000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1555000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>880000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1049000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2560000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>3226000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>264000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>307000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-389000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-281000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>40000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>393000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-416000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>271000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1411000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>119600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>127800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>109500</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>174000</v>
+        <v>407000</v>
       </c>
       <c r="E24" s="3">
         <v>174000</v>
       </c>
       <c r="F24" s="3">
+        <v>174000</v>
+      </c>
+      <c r="G24" s="3">
         <v>218000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>264000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>205000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-131000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>215000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>279000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>301000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>304000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>323000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>343000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>374000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>404000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>284000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>258000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>386000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>784000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>791000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>41000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>167000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>776000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>105000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>116000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>201000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>394000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>314000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>274000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>34700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>33500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>32200</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2364,204 +2413,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>634000</v>
+      </c>
+      <c r="E26" s="3">
         <v>487000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>597000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>585000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>502000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>269000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-816000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>410000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>717000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>706000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1152000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>612000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>694000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>830000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1058000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1271000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>622000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>663000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1776000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2435000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>223000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>140000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-1165000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-386000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-76000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>192000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-810000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-43000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1137000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>84900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>94300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>77300</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>370000</v>
+      </c>
+      <c r="E27" s="3">
         <v>295000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>479000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>368000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>305000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>120000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-735000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>241000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>488000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>438000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>726000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>347000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>411000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>538000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>685000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>882000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>357000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>400000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1387000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2277000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>194000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>111000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1197000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-412000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-94000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>158000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-657000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-11000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1084000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>69800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>78500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>65600</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2658,8 +2716,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2720,8 +2781,8 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>91</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>91</v>
@@ -2738,17 +2799,17 @@
       <c r="AB29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="AD29" s="3">
         <v>343000</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AF29" s="3">
-        <v>0</v>
+      <c r="AF29" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="AG29" s="3">
         <v>0</v>
@@ -2756,8 +2817,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -2854,8 +2918,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -2952,204 +3019,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>-46000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-49000</v>
       </c>
-      <c r="E32" s="3">
-        <v>-58000</v>
-      </c>
       <c r="F32" s="3">
+        <v>-63000</v>
+      </c>
+      <c r="G32" s="3">
         <v>-36000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-42000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-40000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-21000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-12000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>4000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>3000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>10000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1000</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>2000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>6000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-325000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>13000</v>
-      </c>
-      <c r="W32" s="3">
-        <v>12000</v>
       </c>
       <c r="X32" s="3">
         <v>12000</v>
       </c>
       <c r="Y32" s="3">
+        <v>12000</v>
+      </c>
+      <c r="Z32" s="3">
         <v>2000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>20000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-5000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-7000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-6000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>4800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>4700</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-5800</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>370000</v>
+      </c>
+      <c r="E33" s="3">
         <v>295000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>479000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>368000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>305000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>120000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-735000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>241000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>488000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>438000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>726000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>347000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>411000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>538000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>685000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>882000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>357000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>400000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1387000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2277000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>194000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>111000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-1197000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-412000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-94000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>158000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-314000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-11000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1084000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>69800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>78500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>65600</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3246,209 +3322,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>370000</v>
+      </c>
+      <c r="E35" s="3">
         <v>295000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>479000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>368000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>305000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>120000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-735000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>241000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>488000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>438000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>726000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>347000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>411000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>538000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>685000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>882000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>357000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>400000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1387000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2277000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>194000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>111000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-1197000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-412000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-94000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>158000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-314000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-11000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1084000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>69800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>78500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>65600</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -3483,8 +3568,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -3519,106 +3605,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>4036000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3942000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4148000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4261000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4157000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4377000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4440000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5240000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5780000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5887000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5280000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5043000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5138000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5672000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5188000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>4744000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3743000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3327000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3314000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2405000</v>
-      </c>
-      <c r="W41" s="3">
-        <v>2153000</v>
       </c>
       <c r="X41" s="3">
         <v>2153000</v>
       </c>
       <c r="Y41" s="3">
+        <v>2153000</v>
+      </c>
+      <c r="Z41" s="3">
         <v>1571000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1697000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2085000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2384000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2234000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2025000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2926000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>600300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>516300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>361100</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
@@ -3715,596 +3805,617 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>566000</v>
+      </c>
+      <c r="E43" s="3">
         <v>654000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>693000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>561000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>603000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>557000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>554000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>499000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>577000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>640000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>623000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>600000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>554000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>530000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>558000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>509000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>407000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>371000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>363000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>311000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>427000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>383000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>248000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>189000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>194000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>173000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>239000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>224000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>190000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>236800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>231400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>223400</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>1684000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1805000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1782000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1913000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1868000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1913000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1781000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1691000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1699000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1766000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1734000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1821000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1825000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1776000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1878000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2111000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2160000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2159000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2289000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2265000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1930000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1966000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1852000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1898000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1940000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1887000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1890000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>2038000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1901000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>124600</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>119000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>135800</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>916000</v>
+      </c>
+      <c r="E45" s="3">
         <v>880000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>815000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>684000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>742000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1691000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1690000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>786000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>754000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>722000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>612000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>547000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>522000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>806000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>519000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>495000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>609000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>594000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>921000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>529000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>333000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>372000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>307000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>319000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>356000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>352000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>321000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>455000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>486000</v>
       </c>
-      <c r="AF45" s="3">
-        <v>0</v>
-      </c>
       <c r="AG45" s="3">
         <v>0</v>
       </c>
       <c r="AH45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>7202000</v>
+      </c>
+      <c r="E46" s="3">
         <v>7281000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7438000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7419000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7370000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>8538000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8465000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>8216000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>8810000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>9015000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>8249000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>8011000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>8039000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>8784000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>8143000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>7859000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>6919000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>6451000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>6887000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>5510000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4843000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4874000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3978000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4103000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4575000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>4796000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4684000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4742000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>5503000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>961600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>866800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>720300</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>4262000</v>
+      </c>
+      <c r="E47" s="3">
         <v>4178000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>4133000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>3998000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>4004000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>3969000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>3983000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>4064000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4113000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4334000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>4594000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4762000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>4715000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>4646000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>4670000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>4643000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>4587000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>4556000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>4527000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>4474000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>4459000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>4444000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1234000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1233000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1214000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1233000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1213000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1243000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1218000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1446800</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1448600</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1479500</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>26994000</v>
+      </c>
+      <c r="E48" s="3">
         <v>26648000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>26416000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>26621000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>26311000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>26084000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>25821000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>25329000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>25202000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>25153000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>24954000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>24747000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>24755000</v>
-      </c>
-      <c r="P48" s="3">
-        <v>24628000</v>
       </c>
       <c r="Q48" s="3">
         <v>24628000</v>
       </c>
       <c r="R48" s="3">
+        <v>24628000</v>
+      </c>
+      <c r="S48" s="3">
         <v>24698000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>24727000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>24809000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>24141000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>24758000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>16890000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>16891000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>12826000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>13226000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>13727000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>13755000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>13806000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>13961000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>13943000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1564000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1560900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1567300</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
@@ -4312,7 +4423,7 @@
         <v>3729000</v>
       </c>
       <c r="E49" s="3">
-        <v>3730000</v>
+        <v>3729000</v>
       </c>
       <c r="F49" s="3">
         <v>3730000</v>
@@ -4327,7 +4438,7 @@
         <v>3730000</v>
       </c>
       <c r="J49" s="3">
-        <v>4918000</v>
+        <v>3730000</v>
       </c>
       <c r="K49" s="3">
         <v>4918000</v>
@@ -4336,73 +4447,76 @@
         <v>4918000</v>
       </c>
       <c r="M49" s="3">
+        <v>4918000</v>
+      </c>
+      <c r="N49" s="3">
         <v>4919000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4920000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4927000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4937000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4938000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4939000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4983000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4999000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4995000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>5025000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3064000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3037000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1403000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1559000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1560000</v>
-      </c>
-      <c r="AB49" s="3">
-        <v>1585000</v>
       </c>
       <c r="AC49" s="3">
         <v>1585000</v>
       </c>
       <c r="AD49" s="3">
+        <v>1585000</v>
+      </c>
+      <c r="AE49" s="3">
         <v>1556000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1586000</v>
       </c>
-      <c r="AF49" s="3">
-        <v>0</v>
-      </c>
       <c r="AG49" s="3">
         <v>0</v>
       </c>
       <c r="AH49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -4499,8 +4613,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -4597,106 +4714,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>4032000</v>
+      </c>
+      <c r="E52" s="3">
         <v>4007000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4094000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3827000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3871000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3831000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3966000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3915000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3799000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3886000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4174000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4194000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4092000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3853000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4127000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3977000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3964000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4124000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3842000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4100000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3346000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3383000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3190000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3997000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>4046000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>4027000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>4020000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>3570000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>3557000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>163600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>164700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>151000</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -4793,106 +4916,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>46219000</v>
+      </c>
+      <c r="E54" s="3">
         <v>45843000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>45811000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>45595000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>45286000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>46152000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>45965000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>46442000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>46842000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>47306000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>46890000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>46634000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>46528000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>46848000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>46506000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>46116000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>45180000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>44939000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>44392000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>43867000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>32602000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>32629000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>22631000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>24118000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>25122000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>25396000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>25308000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>25072000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>25807000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>4136000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>4041000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>3918100</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -4927,8 +5056,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -4963,138 +5093,142 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>1386000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1360000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1503000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1584000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1525000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1504000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1556000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1571000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1537000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1525000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1448000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1444000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1157000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1168000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1458000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1032000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1072000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1140000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1155000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1337000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1064000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1213000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1101000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1125000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>944000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1046000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1059000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1118000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1044000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>120000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>127400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>136700</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E58" s="3">
         <v>12000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>11000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>8000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>13000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>12000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>13000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>12000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>13000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>14000</v>
-      </c>
-      <c r="M58" s="3">
-        <v>15000</v>
       </c>
       <c r="N58" s="3">
         <v>15000</v>
@@ -5103,260 +5237,269 @@
         <v>15000</v>
       </c>
       <c r="P58" s="3">
+        <v>15000</v>
+      </c>
+      <c r="Q58" s="3">
         <v>13000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>20000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>21000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>26000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>29000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>375000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>66000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>303000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>308000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>43000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>49000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>680000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>57000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>59000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>63000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>116000</v>
       </c>
-      <c r="AF58" s="3">
-        <v>0</v>
-      </c>
       <c r="AG58" s="3">
         <v>0</v>
       </c>
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>995000</v>
+      </c>
+      <c r="E59" s="3">
         <v>823000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>842000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>826000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>732000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1690000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1551000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>605000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>680000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>708000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>623000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>521000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>626000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1150000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>742000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>698000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>713000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>801000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>846000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>441000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>415000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>463000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>524000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>375000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>536000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>595000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>629000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>557000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>386000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>71100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>61000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>34700</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>2392000</v>
+      </c>
+      <c r="E60" s="3">
         <v>2195000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2356000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2418000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2270000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3206000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3120000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2188000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2230000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2247000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2086000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1980000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1798000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2331000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2220000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1751000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1811000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1970000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2376000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1844000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1782000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1984000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1668000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1549000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2160000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1698000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1747000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1738000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1546000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>191100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>188400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>171400</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
@@ -5364,88 +5507,88 @@
         <v>4713000</v>
       </c>
       <c r="E61" s="3">
+        <v>4713000</v>
+      </c>
+      <c r="F61" s="3">
         <v>4715000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4767000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4761000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4765000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4769000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5083000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5131000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5130000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5135000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5139000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5137000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>5140000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>5135000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>5140000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>5142000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>5150000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>5161000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>5494000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>5504000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>5499000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>5695000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>5696000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>5712000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>6344000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>6364000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>6384000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>7328000</v>
-      </c>
-      <c r="AF61" s="3">
-        <v>2800</v>
       </c>
       <c r="AG61" s="3">
         <v>2800</v>
@@ -5453,106 +5596,112 @@
       <c r="AH61" s="3">
         <v>2800</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>6619000</v>
+      </c>
+      <c r="E62" s="3">
         <v>6718000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>6738000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>6712000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>6770000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>6863000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>6787000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>6864000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>6947000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7303000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>7362000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>7425000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>7419000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>7298000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>7441000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>7575000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>7481000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>7464000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>7028000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>8129000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>6849000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>6844000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>5883000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>6187000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>6144000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>6088000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>6130000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>5328000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>5248000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>101700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>97800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>88900</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -5649,8 +5798,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5747,8 +5899,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -5845,106 +6000,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>22603000</v>
+      </c>
+      <c r="E66" s="3">
         <v>22380000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>22470000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>22575000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>22447000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>23439000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>23194000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>22578000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>22731000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>23131000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>23033000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>23016000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>22839000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>23174000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>23165000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>23317000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>23148000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>23252000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>22960000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>23718000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>16856000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>17031000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>15038000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>15211000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>15766000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>15917000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>16022000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>15458000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>16165000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>559400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>542300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>502400</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -5979,8 +6140,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -6077,8 +6239,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -6175,8 +6340,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -6273,8 +6441,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -6371,106 +6542,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>-6400000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-6594000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-6713000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-7016000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-7208000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-7338000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-7282000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-6284000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-6173000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-6306000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-6566000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-7132000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-7320000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-7571000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-7949000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-8474000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-9214000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-9446000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-9722000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-11020000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-13227000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-13351000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-13453000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-12148000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-11701000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-11572000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-11759000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-11428000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-11382000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>2014900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1956700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1874200</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -6567,8 +6744,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -6665,8 +6845,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -6763,106 +6946,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>23616000</v>
+      </c>
+      <c r="E76" s="3">
         <v>23463000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>23341000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>23020000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>22839000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>22713000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>22771000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>23864000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>24111000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>24175000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>23857000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>23618000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>23689000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>23674000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>23341000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>22799000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>22032000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>21687000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>21432000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>20149000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>15746000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>15598000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>7593000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>8907000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>9356000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>9479000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>9286000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>9614000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>9642000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3576600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>3498700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>3415700</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -6959,209 +7148,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>370000</v>
+      </c>
+      <c r="E81" s="3">
         <v>295000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>479000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>368000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>305000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>120000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-735000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>241000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>488000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>438000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>726000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>347000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>411000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>538000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>685000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>882000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>357000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>400000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1387000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2277000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>194000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>111000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-1197000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-412000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-94000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>158000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-314000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-11000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1084000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>69800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>78500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>65600</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -7196,106 +7394,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>480000</v>
+      </c>
+      <c r="E83" s="3">
         <v>474000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>564000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>504000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>480000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>495000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>604000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>457000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>476000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>460000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>557000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>538000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>500000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>507000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>544000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>574000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>566000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>524000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>572000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>559000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>466000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>435000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>441000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>363000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>328000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>325000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>434000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>390000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>409000</v>
       </c>
-      <c r="AF83" s="3">
-        <v>0</v>
-      </c>
       <c r="AG83" s="3">
         <v>0</v>
       </c>
       <c r="AH83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -7392,8 +7594,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -7490,8 +7695,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -7588,8 +7796,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -7686,8 +7897,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -7784,106 +7998,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>1159000</v>
+      </c>
+      <c r="E89" s="3">
         <v>760000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>997000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1127000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>832000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>776000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>795000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>758000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>924000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1004000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1387000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1050000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>639000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1302000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1638000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1859000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1031000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>889000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>875000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1004000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>434000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>520000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>411000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>706000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>141000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>507000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>590000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>532000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>448000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>133100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>204700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>119300</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -7918,106 +8138,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-819000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-728000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-861000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-768000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-769000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-688000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-891000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-792000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-755000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-611000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-669000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-569000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-658000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-539000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-546000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-548000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-509000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-451000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-446000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-502000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-379000</v>
-      </c>
-      <c r="X91" s="3">
-        <v>-374000</v>
       </c>
       <c r="Y91" s="3">
         <v>-374000</v>
       </c>
       <c r="Z91" s="3">
+        <v>-374000</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-387000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-313000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-326000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-350000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-307000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-405000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-41300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-50300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-32000</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -8114,8 +8338,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -8212,106 +8439,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-703000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-680000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-766000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-689000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-743000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-618000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-780000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-639000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-301000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>9000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-387000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-499000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-603000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-408000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-405000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-454000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-264000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-163000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>362000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-383000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-351000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>422000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-477000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-386000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-347000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-284000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-256000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-306000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>556000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-44700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-48000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-27900</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -8346,8 +8579,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
@@ -8355,76 +8589,76 @@
         <v>-175000</v>
       </c>
       <c r="E96" s="3">
+        <v>-175000</v>
+      </c>
+      <c r="F96" s="3">
         <v>-176000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-175000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-174000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-175000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-261000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-351000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-353000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-178000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-159000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-158000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-159000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-158000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-160000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-141000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-124000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-122000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-87000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-67000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-61000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-333000</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-31000</v>
       </c>
       <c r="Z96" s="3">
         <v>-31000</v>
       </c>
       <c r="AA96" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-32000</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-31000</v>
       </c>
       <c r="AC96" s="3">
         <v>-31000</v>
@@ -8433,19 +8667,22 @@
         <v>-31000</v>
       </c>
       <c r="AE96" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-32000</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
         <v>0</v>
       </c>
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -8542,8 +8779,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -8640,8 +8880,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -8738,121 +8981,127 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-362000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-284000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-342000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-333000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-309000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-221000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-815000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-656000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-727000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-406000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-763000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-646000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-570000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-409000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-789000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-408000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-348000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-709000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-328000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-369000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-82000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-360000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-57000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-704000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-92000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-72000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-126000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1127000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-355000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-4400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="E101" s="3">
         <v>-2000</v>
       </c>
       <c r="F101" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="G101" s="3">
         <v>-1000</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
         <v>0</v>
       </c>
@@ -8860,13 +9109,13 @@
         <v>0</v>
       </c>
       <c r="J101" s="3">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="K101" s="3">
         <v>-3000</v>
       </c>
       <c r="L101" s="3">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -8878,50 +9127,50 @@
         <v>0</v>
       </c>
       <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
       <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
         <v>4000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-3000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-4000</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
       <c r="V101" s="3">
         <v>0</v>
       </c>
       <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
         <v>-1000</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
       <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-4000</v>
-      </c>
-      <c r="AA101" s="3">
-        <v>-1000</v>
       </c>
       <c r="AB101" s="3">
         <v>-1000</v>
       </c>
       <c r="AC101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AD101" s="3">
         <v>1000</v>
       </c>
-      <c r="AD101" s="3">
-        <v>0</v>
-      </c>
       <c r="AE101" s="3">
         <v>0</v>
       </c>
@@ -8934,102 +9183,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>94000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-206000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-113000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>104000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-220000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-63000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-800000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-540000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-107000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>607000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>237000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-95000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-534000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>484000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>444000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1001000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>416000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>13000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>909000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>252000</v>
       </c>
-      <c r="W102" s="3">
-        <v>0</v>
-      </c>
       <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3">
         <v>582000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-126000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-388000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-299000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>150000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>209000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-901000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>649000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>84000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>155200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>88400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GOLD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GOLD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="92">
   <si>
     <t>GOLD</t>
   </si>
@@ -656,448 +656,461 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="32" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="33" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3368000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3162000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2747000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3059000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2862000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2833000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2643000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2774000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2527000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2859000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2853000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3310000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2826000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2893000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2956000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3279000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3540000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3055000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2721000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2883000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2678000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2063000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2093000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1904000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1837000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1712000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1790000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2228000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1993000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2160000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>316700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>356400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>300000</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1979000</v>
+        <v>2046000</v>
       </c>
       <c r="E9" s="3">
+        <v>1968000</v>
+      </c>
+      <c r="F9" s="3">
+        <v>1914000</v>
+      </c>
+      <c r="G9" s="3">
+        <v>2166000</v>
+      </c>
+      <c r="H9" s="3">
+        <v>1902000</v>
+      </c>
+      <c r="I9" s="3">
         <v>1936000</v>
       </c>
-      <c r="F9" s="3">
-        <v>2139000</v>
-      </c>
-      <c r="G9" s="3">
-        <v>1915000</v>
-      </c>
-      <c r="H9" s="3">
-        <v>1937000</v>
-      </c>
-      <c r="I9" s="3">
-        <v>1941000</v>
-      </c>
       <c r="J9" s="3">
+        <v>1928000</v>
+      </c>
+      <c r="K9" s="3">
         <v>2093000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1815000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1850000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1739000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1905000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1768000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1704000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1712000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1814000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1927000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1900000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1776000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1987000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1889000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1545000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1490000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1577000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1315000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1176000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1152000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1411000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1270000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1277000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>167400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>196700</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>169100</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1183000</v>
+        <v>1322000</v>
       </c>
       <c r="E10" s="3">
-        <v>811000</v>
+        <v>1194000</v>
       </c>
       <c r="F10" s="3">
-        <v>920000</v>
+        <v>833000</v>
       </c>
       <c r="G10" s="3">
-        <v>947000</v>
+        <v>893000</v>
       </c>
       <c r="H10" s="3">
+        <v>960000</v>
+      </c>
+      <c r="I10" s="3">
+        <v>897000</v>
+      </c>
+      <c r="J10" s="3">
+        <v>715000</v>
+      </c>
+      <c r="K10" s="3">
+        <v>681000</v>
+      </c>
+      <c r="L10" s="3">
+        <v>712000</v>
+      </c>
+      <c r="M10" s="3">
+        <v>1009000</v>
+      </c>
+      <c r="N10" s="3">
+        <v>1114000</v>
+      </c>
+      <c r="O10" s="3">
+        <v>1405000</v>
+      </c>
+      <c r="P10" s="3">
+        <v>1058000</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>1189000</v>
+      </c>
+      <c r="R10" s="3">
+        <v>1244000</v>
+      </c>
+      <c r="S10" s="3">
+        <v>1465000</v>
+      </c>
+      <c r="T10" s="3">
+        <v>1613000</v>
+      </c>
+      <c r="U10" s="3">
+        <v>1155000</v>
+      </c>
+      <c r="V10" s="3">
+        <v>945000</v>
+      </c>
+      <c r="W10" s="3">
         <v>896000</v>
       </c>
-      <c r="I10" s="3">
-        <v>702000</v>
-      </c>
-      <c r="J10" s="3">
-        <v>681000</v>
-      </c>
-      <c r="K10" s="3">
-        <v>712000</v>
-      </c>
-      <c r="L10" s="3">
-        <v>1009000</v>
-      </c>
-      <c r="M10" s="3">
-        <v>1114000</v>
-      </c>
-      <c r="N10" s="3">
-        <v>1405000</v>
-      </c>
-      <c r="O10" s="3">
-        <v>1058000</v>
-      </c>
-      <c r="P10" s="3">
-        <v>1189000</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>1244000</v>
-      </c>
-      <c r="R10" s="3">
-        <v>1465000</v>
-      </c>
-      <c r="S10" s="3">
-        <v>1613000</v>
-      </c>
-      <c r="T10" s="3">
-        <v>1155000</v>
-      </c>
-      <c r="U10" s="3">
-        <v>945000</v>
-      </c>
-      <c r="V10" s="3">
-        <v>896000</v>
-      </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>789000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>518000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>603000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>327000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>522000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>536000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>638000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>817000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>723000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>883000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>149300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>159700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>130900</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1133,109 +1146,113 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K12" s="3">
+        <v>106000</v>
+      </c>
+      <c r="L12" s="3">
+        <v>77000</v>
+      </c>
+      <c r="M12" s="3">
+        <v>100000</v>
+      </c>
+      <c r="N12" s="3">
+        <v>67000</v>
+      </c>
+      <c r="O12" s="3">
+        <v>82000</v>
+      </c>
+      <c r="P12" s="3">
+        <v>67000</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>77000</v>
+      </c>
+      <c r="R12" s="3">
+        <v>61000</v>
+      </c>
+      <c r="S12" s="3">
+        <v>74000</v>
+      </c>
+      <c r="T12" s="3">
+        <v>72000</v>
+      </c>
+      <c r="U12" s="3">
+        <v>78000</v>
+      </c>
+      <c r="V12" s="3">
+        <v>71000</v>
+      </c>
+      <c r="W12" s="3">
+        <v>40000</v>
+      </c>
+      <c r="X12" s="3">
+        <v>86000</v>
+      </c>
+      <c r="Y12" s="3">
+        <v>98000</v>
+      </c>
+      <c r="Z12" s="3">
+        <v>74000</v>
+      </c>
+      <c r="AA12" s="3">
+        <v>87000</v>
+      </c>
+      <c r="AB12" s="3">
+        <v>89000</v>
+      </c>
+      <c r="AC12" s="3">
         <v>97000</v>
       </c>
-      <c r="E12" s="3">
-        <v>95000</v>
-      </c>
-      <c r="F12" s="3">
-        <v>103000</v>
-      </c>
-      <c r="G12" s="3">
-        <v>86000</v>
-      </c>
-      <c r="H12" s="3">
-        <v>101000</v>
-      </c>
-      <c r="I12" s="3">
-        <v>71000</v>
-      </c>
-      <c r="J12" s="3">
-        <v>106000</v>
-      </c>
-      <c r="K12" s="3">
-        <v>77000</v>
-      </c>
-      <c r="L12" s="3">
+      <c r="AD12" s="3">
+        <v>73000</v>
+      </c>
+      <c r="AE12" s="3">
+        <v>98000</v>
+      </c>
+      <c r="AF12" s="3">
         <v>100000</v>
       </c>
-      <c r="M12" s="3">
-        <v>67000</v>
-      </c>
-      <c r="N12" s="3">
-        <v>82000</v>
-      </c>
-      <c r="O12" s="3">
-        <v>67000</v>
-      </c>
-      <c r="P12" s="3">
-        <v>77000</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>61000</v>
-      </c>
-      <c r="R12" s="3">
-        <v>74000</v>
-      </c>
-      <c r="S12" s="3">
-        <v>72000</v>
-      </c>
-      <c r="T12" s="3">
-        <v>78000</v>
-      </c>
-      <c r="U12" s="3">
-        <v>71000</v>
-      </c>
-      <c r="V12" s="3">
-        <v>40000</v>
-      </c>
-      <c r="W12" s="3">
-        <v>86000</v>
-      </c>
-      <c r="X12" s="3">
-        <v>98000</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>74000</v>
-      </c>
-      <c r="Z12" s="3">
-        <v>87000</v>
-      </c>
-      <c r="AA12" s="3">
-        <v>89000</v>
-      </c>
-      <c r="AB12" s="3">
-        <v>97000</v>
-      </c>
-      <c r="AC12" s="3">
-        <v>73000</v>
-      </c>
-      <c r="AD12" s="3">
-        <v>98000</v>
-      </c>
-      <c r="AE12" s="3">
-        <v>100000</v>
-      </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>81000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>10900</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>8000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>11200</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1335,132 +1352,138 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>8000</v>
+        <v>9000</v>
       </c>
       <c r="E14" s="3">
-        <v>21000</v>
+        <v>15000</v>
       </c>
       <c r="F14" s="3">
-        <v>311000</v>
+        <v>44000</v>
       </c>
       <c r="G14" s="3">
-        <v>40000</v>
+        <v>-344000</v>
       </c>
       <c r="H14" s="3">
-        <v>39000</v>
+        <v>31000</v>
       </c>
       <c r="I14" s="3">
+        <v>27000</v>
+      </c>
+      <c r="J14" s="3">
+        <v>18000</v>
+      </c>
+      <c r="K14" s="3">
+        <v>1637000</v>
+      </c>
+      <c r="L14" s="3">
+        <v>60000</v>
+      </c>
+      <c r="M14" s="3">
+        <v>17000</v>
+      </c>
+      <c r="N14" s="3">
+        <v>19000</v>
+      </c>
+      <c r="O14" s="3">
+        <v>57000</v>
+      </c>
+      <c r="P14" s="3">
+        <v>27000</v>
+      </c>
+      <c r="Q14" s="3">
         <v>23000</v>
       </c>
-      <c r="J14" s="3">
-        <v>1637000</v>
-      </c>
-      <c r="K14" s="3">
-        <v>60000</v>
-      </c>
-      <c r="L14" s="3">
-        <v>17000</v>
-      </c>
-      <c r="M14" s="3">
-        <v>19000</v>
-      </c>
-      <c r="N14" s="3">
-        <v>57000</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="R14" s="3">
+        <v>-77000</v>
+      </c>
+      <c r="S14" s="3">
+        <v>64000</v>
+      </c>
+      <c r="T14" s="3">
+        <v>-80000</v>
+      </c>
+      <c r="U14" s="3">
+        <v>81000</v>
+      </c>
+      <c r="V14" s="3">
+        <v>-311000</v>
+      </c>
+      <c r="W14" s="3">
+        <v>-514000</v>
+      </c>
+      <c r="X14" s="3">
+        <v>-2726000</v>
+      </c>
+      <c r="Y14" s="3">
         <v>27000</v>
       </c>
-      <c r="P14" s="3">
-        <v>23000</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>-77000</v>
-      </c>
-      <c r="R14" s="3">
-        <v>64000</v>
-      </c>
-      <c r="S14" s="3">
-        <v>-80000</v>
-      </c>
-      <c r="T14" s="3">
-        <v>81000</v>
-      </c>
-      <c r="U14" s="3">
-        <v>-311000</v>
-      </c>
-      <c r="V14" s="3">
-        <v>-514000</v>
-      </c>
-      <c r="W14" s="3">
-        <v>-2726000</v>
-      </c>
-      <c r="X14" s="3">
-        <v>27000</v>
-      </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>44000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>451000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>495000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>67000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>28000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>1029000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>117000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>18000</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
       <c r="AH14" s="3">
         <v>0</v>
       </c>
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>503000</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>495000</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>268000</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>526000</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>501000</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>516000</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1537,8 +1560,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1571,210 +1597,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>2070000</v>
+        <v>2328000</v>
       </c>
       <c r="E17" s="3">
-        <v>2055000</v>
+        <v>2131000</v>
       </c>
       <c r="F17" s="3">
-        <v>2272000</v>
+        <v>2073000</v>
       </c>
       <c r="G17" s="3">
-        <v>2007000</v>
+        <v>2659000</v>
       </c>
       <c r="H17" s="3">
-        <v>2023000</v>
+        <v>2042000</v>
       </c>
       <c r="I17" s="3">
-        <v>2111000</v>
+        <v>2093000</v>
       </c>
       <c r="J17" s="3">
+        <v>2134000</v>
+      </c>
+      <c r="K17" s="3">
         <v>3658000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1827000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1774000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1758000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1770000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1798000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1765000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1665000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1737000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1904000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2093000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1583000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>217000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>-670000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1681000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1666000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2176000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1988000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1536000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1264000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2514000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1585000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>602000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>192200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>223900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>196300</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>1092000</v>
+        <v>1040000</v>
       </c>
       <c r="E18" s="3">
-        <v>692000</v>
+        <v>1031000</v>
       </c>
       <c r="F18" s="3">
-        <v>787000</v>
+        <v>674000</v>
       </c>
       <c r="G18" s="3">
-        <v>855000</v>
+        <v>400000</v>
       </c>
       <c r="H18" s="3">
-        <v>810000</v>
+        <v>820000</v>
       </c>
       <c r="I18" s="3">
-        <v>532000</v>
+        <v>740000</v>
       </c>
       <c r="J18" s="3">
+        <v>509000</v>
+      </c>
+      <c r="K18" s="3">
         <v>-884000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>700000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1085000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1095000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1540000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1028000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1128000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1291000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1542000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1636000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>962000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1138000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2666000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>3348000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>382000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>427000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-272000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-151000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>176000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>526000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-286000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>408000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1558000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>124500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>132500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>103700</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1810,513 +1843,529 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>46000</v>
+        <v>-45000</v>
       </c>
       <c r="E20" s="3">
-        <v>49000</v>
+        <v>-109000</v>
       </c>
       <c r="F20" s="3">
-        <v>63000</v>
+        <v>-35000</v>
       </c>
       <c r="G20" s="3">
-        <v>36000</v>
+        <v>-19000</v>
       </c>
       <c r="H20" s="3">
-        <v>42000</v>
+        <v>-36000</v>
       </c>
       <c r="I20" s="3">
-        <v>40000</v>
+        <v>-69000</v>
       </c>
       <c r="J20" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="K20" s="3">
         <v>21000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>12000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-4000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-3000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-10000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1000</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-2000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-6000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>325000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-13000</v>
-      </c>
-      <c r="X20" s="3">
-        <v>-12000</v>
       </c>
       <c r="Y20" s="3">
         <v>-12000</v>
       </c>
       <c r="Z20" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-20000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>4000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>5000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>7000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>6000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-4800</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-4700</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>1585000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>1643000</v>
+      </c>
+      <c r="F21" s="3">
+        <v>1204000</v>
+      </c>
+      <c r="G21" s="3">
+        <v>687000</v>
+      </c>
+      <c r="H21" s="3">
+        <v>1382000</v>
+      </c>
+      <c r="I21" s="3">
+        <v>1310000</v>
+      </c>
+      <c r="J21" s="3">
+        <v>1039000</v>
+      </c>
+      <c r="K21" s="3">
+        <v>-259000</v>
+      </c>
+      <c r="L21" s="3">
+        <v>1169000</v>
+      </c>
+      <c r="M21" s="3">
+        <v>1557000</v>
+      </c>
+      <c r="N21" s="3">
+        <v>1553000</v>
+      </c>
+      <c r="O21" s="3">
+        <v>2098000</v>
+      </c>
+      <c r="P21" s="3">
+        <v>1563000</v>
+      </c>
+      <c r="Q21" s="3">
         <v>1618000</v>
       </c>
-      <c r="E21" s="3">
-        <v>1215000</v>
-      </c>
-      <c r="F21" s="3">
-        <v>1414000</v>
-      </c>
-      <c r="G21" s="3">
-        <v>1395000</v>
-      </c>
-      <c r="H21" s="3">
-        <v>1332000</v>
-      </c>
-      <c r="I21" s="3">
-        <v>1067000</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-259000</v>
-      </c>
-      <c r="K21" s="3">
-        <v>1169000</v>
-      </c>
-      <c r="L21" s="3">
-        <v>1557000</v>
-      </c>
-      <c r="M21" s="3">
-        <v>1553000</v>
-      </c>
-      <c r="N21" s="3">
-        <v>2098000</v>
-      </c>
-      <c r="O21" s="3">
-        <v>1563000</v>
-      </c>
-      <c r="P21" s="3">
-        <v>1618000</v>
-      </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1796000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2085000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2210000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1526000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1656000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>3563000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>3894000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>836000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>850000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>167000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>192000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>505000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>855000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>153000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>805000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1973000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>158600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>263000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>113700</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>97000</v>
+        <v>133000</v>
       </c>
       <c r="E22" s="3">
+        <v>158000</v>
+      </c>
+      <c r="F22" s="3">
         <v>80000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
+        <v>78000</v>
+      </c>
+      <c r="H22" s="3">
+        <v>88000</v>
+      </c>
+      <c r="I22" s="3">
+        <v>86000</v>
+      </c>
+      <c r="J22" s="3">
+        <v>98000</v>
+      </c>
+      <c r="K22" s="3">
+        <v>84000</v>
+      </c>
+      <c r="L22" s="3">
+        <v>87000</v>
+      </c>
+      <c r="M22" s="3">
+        <v>85000</v>
+      </c>
+      <c r="N22" s="3">
+        <v>86000</v>
+      </c>
+      <c r="O22" s="3">
+        <v>85000</v>
+      </c>
+      <c r="P22" s="3">
+        <v>90000</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>81000</v>
+      </c>
+      <c r="R22" s="3">
+        <v>85000</v>
+      </c>
+      <c r="S22" s="3">
         <v>79000</v>
       </c>
-      <c r="G22" s="3">
-        <v>88000</v>
-      </c>
-      <c r="H22" s="3">
-        <v>86000</v>
-      </c>
-      <c r="I22" s="3">
-        <v>98000</v>
-      </c>
-      <c r="J22" s="3">
-        <v>84000</v>
-      </c>
-      <c r="K22" s="3">
-        <v>87000</v>
-      </c>
-      <c r="L22" s="3">
-        <v>85000</v>
-      </c>
-      <c r="M22" s="3">
-        <v>86000</v>
-      </c>
-      <c r="N22" s="3">
-        <v>85000</v>
-      </c>
-      <c r="O22" s="3">
-        <v>90000</v>
-      </c>
-      <c r="P22" s="3">
+      <c r="T22" s="3">
         <v>81000</v>
       </c>
-      <c r="Q22" s="3">
-        <v>85000</v>
-      </c>
-      <c r="R22" s="3">
-        <v>79000</v>
-      </c>
-      <c r="S22" s="3">
-        <v>81000</v>
-      </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>80000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>83000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>431000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>109000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>106000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>108000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>115000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>110000</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>137000</v>
       </c>
       <c r="AC22" s="3">
         <v>137000</v>
       </c>
       <c r="AD22" s="3">
+        <v>137000</v>
+      </c>
+      <c r="AE22" s="3">
         <v>135000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>144000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>153000</v>
       </c>
-      <c r="AG22" s="3">
-        <v>0</v>
-      </c>
       <c r="AH22" s="3">
         <v>0</v>
       </c>
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>1025000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1041000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>661000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>771000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>803000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>766000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>474000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-947000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>625000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>996000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1007000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1456000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>935000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1037000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1204000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1462000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1555000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>880000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1049000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2560000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>3226000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>264000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>307000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-389000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-281000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>40000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>393000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-416000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>271000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1411000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>119600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>127800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>109500</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>245000</v>
+      </c>
+      <c r="E24" s="3">
         <v>407000</v>
-      </c>
-      <c r="E24" s="3">
-        <v>174000</v>
       </c>
       <c r="F24" s="3">
         <v>174000</v>
       </c>
       <c r="G24" s="3">
+        <v>174000</v>
+      </c>
+      <c r="H24" s="3">
         <v>218000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>264000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>205000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-131000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>215000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>279000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>301000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>304000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>323000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>343000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>374000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>404000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>284000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>258000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>386000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>784000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>791000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>41000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>167000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>776000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>105000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>116000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>201000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>394000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>314000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>274000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>34700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>33500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>32200</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2416,210 +2465,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>780000</v>
+      </c>
+      <c r="E26" s="3">
         <v>634000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>487000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>597000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>585000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>502000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>269000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-816000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>410000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>717000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>706000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1152000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>612000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>694000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>830000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1058000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1271000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>622000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>663000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1776000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2435000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>223000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>140000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-1165000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-386000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-76000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>192000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-810000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-43000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1137000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>84900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>94300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>77300</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>483000</v>
+      </c>
+      <c r="E27" s="3">
         <v>370000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>295000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>479000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>368000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>305000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>120000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-735000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>241000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>488000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>438000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>726000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>347000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>411000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>538000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>685000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>882000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>357000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>400000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1387000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2277000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>194000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>111000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-1197000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-412000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-94000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>158000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-657000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-11000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1084000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>69800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>78500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>65600</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2719,8 +2777,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2784,8 +2845,8 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>91</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>91</v>
@@ -2802,17 +2863,17 @@
       <c r="AC29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE29" s="3">
         <v>343000</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
+      <c r="AG29" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="AH29" s="3">
         <v>0</v>
@@ -2820,8 +2881,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -2921,8 +2985,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -3022,210 +3089,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>-46000</v>
+        <v>45000</v>
       </c>
       <c r="E32" s="3">
-        <v>-49000</v>
+        <v>109000</v>
       </c>
       <c r="F32" s="3">
-        <v>-63000</v>
+        <v>35000</v>
       </c>
       <c r="G32" s="3">
-        <v>-36000</v>
+        <v>19000</v>
       </c>
       <c r="H32" s="3">
-        <v>-42000</v>
+        <v>36000</v>
       </c>
       <c r="I32" s="3">
-        <v>-40000</v>
+        <v>69000</v>
       </c>
       <c r="J32" s="3">
+        <v>14000</v>
+      </c>
+      <c r="K32" s="3">
         <v>-21000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-12000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>4000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>3000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>10000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1000</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>2000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>6000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-325000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>13000</v>
-      </c>
-      <c r="X32" s="3">
-        <v>12000</v>
       </c>
       <c r="Y32" s="3">
         <v>12000</v>
       </c>
       <c r="Z32" s="3">
+        <v>12000</v>
+      </c>
+      <c r="AA32" s="3">
         <v>2000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>20000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-5000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-7000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-6000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>4800</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>4700</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-5800</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>483000</v>
+      </c>
+      <c r="E33" s="3">
         <v>370000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>295000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>479000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>368000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>305000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>120000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-735000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>241000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>488000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>438000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>726000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>347000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>411000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>538000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>685000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>882000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>357000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>400000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1387000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2277000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>194000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>111000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-1197000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-412000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-94000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>158000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-314000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-11000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1084000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>69800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>78500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>65600</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3325,215 +3401,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>483000</v>
+      </c>
+      <c r="E35" s="3">
         <v>370000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>295000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>479000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>368000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>305000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>120000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-735000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>241000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>488000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>438000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>726000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>347000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>411000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>538000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>685000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>882000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>357000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>400000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1387000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2277000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>194000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>111000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-1197000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-412000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-94000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>158000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-314000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-11000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1084000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>69800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>78500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>65600</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -3569,8 +3654,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -3606,109 +3692,113 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>4225000</v>
+      </c>
+      <c r="E41" s="3">
         <v>4036000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3942000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4148000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4261000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4157000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4377000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4440000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5240000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5780000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5887000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5280000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5043000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5138000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5672000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5188000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>4744000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3743000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3327000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3314000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2405000</v>
-      </c>
-      <c r="X41" s="3">
-        <v>2153000</v>
       </c>
       <c r="Y41" s="3">
         <v>2153000</v>
       </c>
       <c r="Z41" s="3">
+        <v>2153000</v>
+      </c>
+      <c r="AA41" s="3">
         <v>1571000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1697000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2085000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2384000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2234000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2025000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2926000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>600300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>516300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>361100</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
@@ -3808,614 +3898,635 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>684000</v>
+      </c>
+      <c r="E43" s="3">
         <v>566000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>654000</v>
       </c>
-      <c r="F43" s="3">
-        <v>693000</v>
-      </c>
       <c r="G43" s="3">
+        <v>1178000</v>
+      </c>
+      <c r="H43" s="3">
         <v>561000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>603000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>557000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>554000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>499000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>577000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>640000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>623000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>600000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>554000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>530000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>558000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>509000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>407000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>371000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>363000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>311000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>427000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>383000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>248000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>189000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>194000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>173000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>239000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>224000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>190000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>236800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>231400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>223400</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>1784000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1684000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1805000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1782000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1913000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1868000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1913000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1781000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1691000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1699000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1766000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1734000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1821000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1825000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1776000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1878000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2111000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2160000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2159000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2289000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2265000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1930000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1966000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1852000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1898000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1940000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1887000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1890000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>2038000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1901000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>124600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>119000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>135800</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>1334000</v>
+      </c>
+      <c r="E45" s="3">
         <v>916000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>880000</v>
       </c>
-      <c r="F45" s="3">
-        <v>815000</v>
-      </c>
       <c r="G45" s="3">
+        <v>127000</v>
+      </c>
+      <c r="H45" s="3">
         <v>684000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>742000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1691000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1690000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>786000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>754000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>722000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>612000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>547000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>522000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>806000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>519000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>495000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>609000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>594000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>921000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>529000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>333000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>372000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>307000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>319000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>356000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>352000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>321000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>455000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>486000</v>
       </c>
-      <c r="AG45" s="3">
-        <v>0</v>
-      </c>
       <c r="AH45" s="3">
         <v>0</v>
       </c>
       <c r="AI45" s="3">
         <v>0</v>
       </c>
+      <c r="AJ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>8027000</v>
+      </c>
+      <c r="E46" s="3">
         <v>7202000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7281000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7438000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7419000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7370000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8538000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>8465000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>8216000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>8810000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>9015000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>8249000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>8011000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>8039000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>8784000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>8143000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>7859000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>6919000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>6451000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>6887000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>5510000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4843000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4874000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3978000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4103000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>4575000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4796000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4684000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>4742000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>5503000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>961600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>866800</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>720300</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>4275000</v>
+      </c>
+      <c r="E47" s="3">
         <v>4262000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>4178000</v>
       </c>
-      <c r="F47" s="3">
-        <v>4133000</v>
-      </c>
       <c r="G47" s="3">
+        <v>4264000</v>
+      </c>
+      <c r="H47" s="3">
         <v>3998000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>4004000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>3969000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>3983000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4064000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4113000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>4334000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4594000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>4762000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>4715000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>4646000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>4670000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>4643000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>4587000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>4556000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>4527000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>4474000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>4459000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>4444000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1234000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1233000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1214000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1233000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1213000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1243000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1218000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1446800</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1448600</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1479500</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>27288000</v>
+      </c>
+      <c r="E48" s="3">
         <v>26994000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>26648000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>26416000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>26621000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>26311000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>26084000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>25821000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>25329000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>25202000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>25153000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>24954000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>24747000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>24755000</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>24628000</v>
       </c>
       <c r="R48" s="3">
         <v>24628000</v>
       </c>
       <c r="S48" s="3">
+        <v>24628000</v>
+      </c>
+      <c r="T48" s="3">
         <v>24698000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>24727000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>24809000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>24141000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>24758000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>16890000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>16891000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>12826000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>13226000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>13727000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>13755000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>13806000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>13961000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>13943000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1564000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1560900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1567300</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
@@ -4426,7 +4537,7 @@
         <v>3729000</v>
       </c>
       <c r="F49" s="3">
-        <v>3730000</v>
+        <v>3729000</v>
       </c>
       <c r="G49" s="3">
         <v>3730000</v>
@@ -4441,7 +4552,7 @@
         <v>3730000</v>
       </c>
       <c r="K49" s="3">
-        <v>4918000</v>
+        <v>3730000</v>
       </c>
       <c r="L49" s="3">
         <v>4918000</v>
@@ -4450,73 +4561,76 @@
         <v>4918000</v>
       </c>
       <c r="N49" s="3">
+        <v>4918000</v>
+      </c>
+      <c r="O49" s="3">
         <v>4919000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4920000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4927000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4937000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4938000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4939000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4983000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4999000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4995000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>5025000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3064000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3037000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1403000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1559000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1560000</v>
-      </c>
-      <c r="AC49" s="3">
-        <v>1585000</v>
       </c>
       <c r="AD49" s="3">
         <v>1585000</v>
       </c>
       <c r="AE49" s="3">
+        <v>1585000</v>
+      </c>
+      <c r="AF49" s="3">
         <v>1556000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1586000</v>
       </c>
-      <c r="AG49" s="3">
-        <v>0</v>
-      </c>
       <c r="AH49" s="3">
         <v>0</v>
       </c>
       <c r="AI49" s="3">
         <v>0</v>
       </c>
+      <c r="AJ49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -4616,8 +4730,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -4717,109 +4834,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>4035000</v>
+      </c>
+      <c r="E52" s="3">
         <v>4032000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4007000</v>
       </c>
-      <c r="F52" s="3">
-        <v>4094000</v>
-      </c>
       <c r="G52" s="3">
-        <v>3827000</v>
+        <v>3776000</v>
       </c>
       <c r="H52" s="3">
-        <v>3871000</v>
+        <v>3800000</v>
       </c>
       <c r="I52" s="3">
-        <v>3831000</v>
+        <v>3852000</v>
       </c>
       <c r="J52" s="3">
+        <v>3812000</v>
+      </c>
+      <c r="K52" s="3">
         <v>3966000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3915000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3799000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3886000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4174000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4194000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4092000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3853000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4127000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3977000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3964000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4124000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3842000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>4100000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3346000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3383000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3190000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3997000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>4046000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>4027000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>4020000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>3570000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>3557000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>163600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>164700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>151000</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -4919,109 +5042,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>47354000</v>
+      </c>
+      <c r="E54" s="3">
         <v>46219000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>45843000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>45811000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>45595000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>45286000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>46152000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>45965000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>46442000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>46842000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>47306000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>46890000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>46634000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>46528000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>46848000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>46506000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>46116000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>45180000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>44939000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>44392000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>43867000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>32602000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>32629000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>22631000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>24118000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>25122000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>25396000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>25308000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>25072000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>25807000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>4136000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>4041000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>3918100</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -5057,8 +5186,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -5094,144 +5224,148 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>1479000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1386000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1360000</v>
       </c>
-      <c r="F57" s="3">
-        <v>1503000</v>
-      </c>
       <c r="G57" s="3">
+        <v>678000</v>
+      </c>
+      <c r="H57" s="3">
         <v>1584000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1525000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1504000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1556000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1571000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1537000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1525000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1448000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1444000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1157000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1168000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1458000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1032000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1072000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1140000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1155000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1337000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1064000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1213000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1101000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1125000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>944000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1046000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1059000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1118000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1044000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>120000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>127400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>136700</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E58" s="3">
         <v>11000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>12000</v>
       </c>
-      <c r="F58" s="3">
-        <v>11000</v>
-      </c>
       <c r="G58" s="3">
+        <v>43000</v>
+      </c>
+      <c r="H58" s="3">
         <v>8000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>13000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>12000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>13000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>12000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>13000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>14000</v>
-      </c>
-      <c r="N58" s="3">
-        <v>15000</v>
       </c>
       <c r="O58" s="3">
         <v>15000</v>
@@ -5240,358 +5374,367 @@
         <v>15000</v>
       </c>
       <c r="Q58" s="3">
+        <v>15000</v>
+      </c>
+      <c r="R58" s="3">
         <v>13000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>20000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>21000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>26000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>29000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>375000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>66000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>303000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>308000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>43000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>49000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>680000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>57000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>59000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>63000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>116000</v>
       </c>
-      <c r="AG58" s="3">
-        <v>0</v>
-      </c>
       <c r="AH58" s="3">
         <v>0</v>
       </c>
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>1537000</v>
+      </c>
+      <c r="E59" s="3">
         <v>995000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>823000</v>
       </c>
-      <c r="F59" s="3">
-        <v>842000</v>
-      </c>
       <c r="G59" s="3">
+        <v>760000</v>
+      </c>
+      <c r="H59" s="3">
         <v>826000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>732000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1690000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1551000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>605000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>680000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>708000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>623000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>521000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>626000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1150000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>742000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>698000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>713000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>801000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>846000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>441000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>415000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>463000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>524000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>375000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>536000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>595000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>629000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>557000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>386000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>71100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>61000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>34700</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>3029000</v>
+      </c>
+      <c r="E60" s="3">
         <v>2392000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2195000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2356000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2418000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2270000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3206000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3120000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2188000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2230000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2247000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2086000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1980000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1798000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2331000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2220000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1751000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1811000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1970000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2376000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1844000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1782000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1984000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1668000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1549000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2160000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1698000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1747000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1738000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1546000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>191100</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>188400</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>171400</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
-        <v>4713000</v>
+        <v>4712000</v>
       </c>
       <c r="E61" s="3">
         <v>4713000</v>
       </c>
       <c r="F61" s="3">
-        <v>4715000</v>
+        <v>4713000</v>
       </c>
       <c r="G61" s="3">
+        <v>5180000</v>
+      </c>
+      <c r="H61" s="3">
         <v>4767000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4761000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4765000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4769000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5083000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5131000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5130000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5135000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5139000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>5137000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>5140000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>5135000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>5140000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>5142000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>5150000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>5161000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>5494000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>5504000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>5499000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>5695000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>5696000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>5712000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>6344000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>6364000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>6384000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>7328000</v>
-      </c>
-      <c r="AG61" s="3">
-        <v>2800</v>
       </c>
       <c r="AH61" s="3">
         <v>2800</v>
@@ -5599,109 +5742,115 @@
       <c r="AI61" s="3">
         <v>2800</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>2800</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>6619000</v>
+        <v>3237000</v>
       </c>
       <c r="E62" s="3">
-        <v>6718000</v>
+        <v>3148000</v>
       </c>
       <c r="F62" s="3">
-        <v>6738000</v>
+        <v>3246000</v>
       </c>
       <c r="G62" s="3">
-        <v>6712000</v>
+        <v>2202000</v>
       </c>
       <c r="H62" s="3">
-        <v>6770000</v>
+        <v>3345000</v>
       </c>
       <c r="I62" s="3">
-        <v>6863000</v>
+        <v>3484000</v>
       </c>
       <c r="J62" s="3">
+        <v>3593000</v>
+      </c>
+      <c r="K62" s="3">
         <v>6787000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>6864000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>6947000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>7303000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>7362000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>7425000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>7419000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>7298000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>7441000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>7575000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>7481000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>7464000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>7028000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>8129000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>6849000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>6844000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>5883000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>6187000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>6144000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>6088000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>6130000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>5328000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>5248000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>101700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>97800</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>88900</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -5801,8 +5950,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5902,8 +6054,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -6003,109 +6158,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
-        <v>22603000</v>
+        <v>14457000</v>
       </c>
       <c r="E66" s="3">
-        <v>22380000</v>
+        <v>13724000</v>
       </c>
       <c r="F66" s="3">
-        <v>22470000</v>
+        <v>13626000</v>
       </c>
       <c r="G66" s="3">
-        <v>22575000</v>
+        <v>13809000</v>
       </c>
       <c r="H66" s="3">
-        <v>22447000</v>
+        <v>13897000</v>
       </c>
       <c r="I66" s="3">
-        <v>23439000</v>
+        <v>13801000</v>
       </c>
       <c r="J66" s="3">
+        <v>14834000</v>
+      </c>
+      <c r="K66" s="3">
         <v>23194000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>22578000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>22731000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>23131000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>23033000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>23016000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>22839000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>23174000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>23165000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>23317000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>23148000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>23252000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>22960000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>23718000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>16856000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>17031000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>15038000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>15211000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>15766000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>15917000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>16022000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>15458000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>16165000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>559400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>542300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>502400</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -6141,8 +6302,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -6242,8 +6404,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -6343,8 +6508,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -6444,8 +6612,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -6545,109 +6716,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>-6092000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-6400000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-6594000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-6713000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-7016000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-7208000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-7338000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-7282000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-6284000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-6173000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-6306000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-6566000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-7132000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-7320000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-7571000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-7949000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-8474000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-9214000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-9446000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-9722000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-11020000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-13227000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-13351000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-13453000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-12148000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-11701000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-11572000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-11759000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-11428000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-11382000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>2014900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1956700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>1874200</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -6747,8 +6924,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -6848,8 +7028,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -6949,109 +7132,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>23831000</v>
+      </c>
+      <c r="E76" s="3">
         <v>23616000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>23463000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>23341000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>23020000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>22839000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>22713000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>22771000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>23864000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>24111000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>24175000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>23857000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>23618000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>23689000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>23674000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>23341000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>22799000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>22032000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>21687000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>21432000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>20149000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>15746000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>15598000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>7593000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>8907000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>9356000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>9479000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>9286000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>9614000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>9642000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>3576600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>3498700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>3415700</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -7151,215 +7340,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>483000</v>
+      </c>
+      <c r="E81" s="3">
         <v>370000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>295000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>479000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>368000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>305000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>120000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-735000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>241000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>488000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>438000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>726000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>347000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>411000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>538000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>685000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>882000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>357000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>400000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1387000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2277000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>194000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>111000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-1197000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-412000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-94000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>158000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-314000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-11000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1084000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>69800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>78500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>65600</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -7395,109 +7593,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>504000</v>
+      </c>
+      <c r="E83" s="3">
         <v>480000</v>
       </c>
-      <c r="E83" s="3">
-        <v>474000</v>
-      </c>
       <c r="F83" s="3">
-        <v>564000</v>
+        <v>495000</v>
       </c>
       <c r="G83" s="3">
-        <v>504000</v>
+        <v>603000</v>
       </c>
       <c r="H83" s="3">
-        <v>480000</v>
+        <v>457000</v>
       </c>
       <c r="I83" s="3">
-        <v>495000</v>
+        <v>476000</v>
       </c>
       <c r="J83" s="3">
+        <v>460000</v>
+      </c>
+      <c r="K83" s="3">
         <v>604000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>457000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>476000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>460000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>557000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>538000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>500000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>507000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>544000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>574000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>566000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>524000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>572000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>559000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>466000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>435000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>441000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>363000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>328000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>325000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>434000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>390000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>409000</v>
       </c>
-      <c r="AG83" s="3">
-        <v>0</v>
-      </c>
       <c r="AH83" s="3">
         <v>0</v>
       </c>
       <c r="AI83" s="3">
         <v>0</v>
       </c>
+      <c r="AJ83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -7597,8 +7799,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -7698,8 +7903,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -7799,8 +8007,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -7900,8 +8111,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -8001,109 +8215,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>1180000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1159000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>760000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>997000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1127000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>832000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>776000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>795000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>758000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>924000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1004000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1387000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1050000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>639000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1302000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1638000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1859000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1031000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>889000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>875000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1004000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>434000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>520000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>411000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>706000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>141000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>507000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>590000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>532000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>448000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>133100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>204700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>119300</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -8139,109 +8359,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-736000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-819000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-728000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-861000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-768000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-769000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-688000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-891000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-792000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-755000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-611000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-669000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-569000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-658000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-539000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-546000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-548000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-509000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-451000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-446000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-502000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-379000</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>-374000</v>
       </c>
       <c r="Z91" s="3">
         <v>-374000</v>
       </c>
       <c r="AA91" s="3">
+        <v>-374000</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-387000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-313000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-326000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-350000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-307000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-405000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-41300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-50300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-32000</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -8341,8 +8565,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -8442,109 +8669,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-603000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-703000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-680000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-766000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-689000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-743000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-618000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-780000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-639000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-301000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>9000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-387000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-499000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-603000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-408000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-405000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-454000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-264000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-163000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>362000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-383000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-351000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>422000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-477000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-386000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-347000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-284000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-256000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-306000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>556000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-44700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-48000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-27900</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -8580,88 +8813,89 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
-        <v>-175000</v>
+        <v>174000</v>
       </c>
       <c r="E96" s="3">
-        <v>-175000</v>
+        <v>175000</v>
       </c>
       <c r="F96" s="3">
-        <v>-176000</v>
+        <v>175000</v>
       </c>
       <c r="G96" s="3">
-        <v>-175000</v>
+        <v>176000</v>
       </c>
       <c r="H96" s="3">
-        <v>-174000</v>
+        <v>175000</v>
       </c>
       <c r="I96" s="3">
-        <v>-175000</v>
+        <v>174000</v>
       </c>
       <c r="J96" s="3">
+        <v>175000</v>
+      </c>
+      <c r="K96" s="3">
         <v>-261000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-351000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-353000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-178000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-159000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-158000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-159000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-158000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-160000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-141000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-124000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-122000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-87000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-67000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-61000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-333000</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-31000</v>
       </c>
       <c r="AA96" s="3">
         <v>-31000</v>
       </c>
       <c r="AB96" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-32000</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-31000</v>
       </c>
       <c r="AD96" s="3">
         <v>-31000</v>
@@ -8670,19 +8904,22 @@
         <v>-31000</v>
       </c>
       <c r="AF96" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-32000</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
       <c r="AH96" s="3">
         <v>0</v>
       </c>
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -8782,8 +9019,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -8883,8 +9123,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -8984,141 +9227,147 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-387000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-362000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-284000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-342000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-333000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-309000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-221000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-815000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-656000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-727000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-406000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-763000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-646000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-570000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-409000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-789000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-408000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-348000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-709000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-328000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-369000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-82000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-360000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-57000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-704000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-92000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-72000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-126000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1127000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-355000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-4400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="F101" s="3">
-        <v>-2000</v>
+        <v>-1000</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="G101" s="3">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="H101" s="3">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+        <v>-3000</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="K101" s="3">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="L101" s="3">
         <v>-3000</v>
       </c>
       <c r="M101" s="3">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -9130,50 +9379,50 @@
         <v>0</v>
       </c>
       <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
         <v>-1000</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
       <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
         <v>4000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-3000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-4000</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
       <c r="W101" s="3">
         <v>0</v>
       </c>
       <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
       <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-4000</v>
-      </c>
-      <c r="AB101" s="3">
-        <v>-1000</v>
       </c>
       <c r="AC101" s="3">
         <v>-1000</v>
       </c>
       <c r="AD101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AE101" s="3">
         <v>1000</v>
       </c>
-      <c r="AE101" s="3">
-        <v>0</v>
-      </c>
       <c r="AF101" s="3">
         <v>0</v>
       </c>
@@ -9186,105 +9435,111 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>189000</v>
+      </c>
+      <c r="E102" s="3">
         <v>94000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-206000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-113000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>104000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-220000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-63000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-800000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-540000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-107000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>607000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>237000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-95000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-534000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>484000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>444000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1001000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>416000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>13000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>909000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>252000</v>
       </c>
-      <c r="X102" s="3">
-        <v>0</v>
-      </c>
       <c r="Y102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="3">
         <v>582000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-126000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-388000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-299000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>150000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>209000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-901000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>649000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>84000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>155200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>88400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GOLD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GOLD_QTR_FIN.xlsx
@@ -656,461 +656,473 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="33" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="34" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3645000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3368000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3162000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2747000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3059000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2862000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2833000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2643000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2774000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2527000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2859000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2853000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3310000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2826000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2893000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2956000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3279000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3540000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3055000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2721000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2883000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2678000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2063000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2093000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1904000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1837000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1712000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1790000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2228000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1993000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2160000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>316700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>356400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>300000</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2033000</v>
+      </c>
+      <c r="E9" s="3">
         <v>2046000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1968000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1914000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2166000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1902000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1936000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1928000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2093000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1815000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1850000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1739000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1905000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1768000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1704000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1712000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1814000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1927000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1900000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1776000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1987000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1889000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1545000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1490000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1577000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1315000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1176000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1152000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1411000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1270000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1277000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>167400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>196700</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>169100</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1612000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1322000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1194000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>833000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>893000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>960000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>897000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>715000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>681000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>712000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1009000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1114000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1405000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1058000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1189000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1244000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1465000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1613000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1155000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>945000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>896000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>789000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>518000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>603000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>327000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>522000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>536000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>638000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>817000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>723000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>883000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>149300</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>159700</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>130900</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1147,13 +1159,14 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>91</v>
+      <c r="D12" s="3">
+        <v>1000</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>91</v>
@@ -1173,86 +1186,89 @@
       <c r="J12" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="L12" s="3">
         <v>106000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>77000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>100000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>67000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>82000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>67000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>77000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>61000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>74000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>72000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>78000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>71000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>40000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>86000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>98000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>74000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>87000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>89000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>97000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>73000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>98000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>100000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>81000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>10900</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>8000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>11200</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1355,139 +1371,145 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>69000</v>
+      </c>
+      <c r="E14" s="3">
         <v>9000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>15000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>44000</v>
       </c>
-      <c r="G14" s="3">
-        <v>-344000</v>
-      </c>
       <c r="H14" s="3">
+        <v>-32000</v>
+      </c>
+      <c r="I14" s="3">
         <v>31000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>27000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>18000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1637000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>60000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>17000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>19000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>57000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>27000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>23000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-77000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>64000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-80000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>81000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-311000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-514000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-2726000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>27000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>44000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>451000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>495000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>67000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>28000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>1029000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>117000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>18000</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
       <c r="AI14" s="3">
         <v>0</v>
       </c>
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>-594000</v>
+      </c>
+      <c r="E15" s="3">
         <v>500000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>503000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>495000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>268000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>526000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>501000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>516000</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1563,8 +1585,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1598,216 +1623,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>1571000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2328000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2131000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2073000</v>
       </c>
-      <c r="G17" s="3">
-        <v>2659000</v>
-      </c>
       <c r="H17" s="3">
+        <v>2260000</v>
+      </c>
+      <c r="I17" s="3">
         <v>2042000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2093000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2134000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3658000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1827000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1774000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1758000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1770000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1798000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1765000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1665000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1737000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1904000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2093000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1583000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>217000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>-670000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1681000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1666000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2176000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1988000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1536000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1264000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2514000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1585000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>602000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>192200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>223900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>196300</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>2074000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1040000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1031000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>674000</v>
       </c>
-      <c r="G18" s="3">
-        <v>400000</v>
-      </c>
       <c r="H18" s="3">
+        <v>799000</v>
+      </c>
+      <c r="I18" s="3">
         <v>820000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>740000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>509000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-884000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>700000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1085000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1095000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1540000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1028000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1128000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1291000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1542000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1636000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>962000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1138000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2666000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>3348000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>382000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>427000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-272000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-151000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>176000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>526000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-286000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>408000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1558000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>124500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>132500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>103700</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1844,528 +1876,544 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>77000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-45000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-109000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-35000</v>
       </c>
-      <c r="G20" s="3">
-        <v>-19000</v>
-      </c>
       <c r="H20" s="3">
+        <v>69000</v>
+      </c>
+      <c r="I20" s="3">
         <v>-36000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-69000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-14000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>21000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>12000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-4000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-10000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1000</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>-2000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-6000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>325000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-13000</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>-12000</v>
       </c>
       <c r="Z20" s="3">
         <v>-12000</v>
       </c>
       <c r="AA20" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-20000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>1000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>4000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>5000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>7000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>6000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-4800</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-4700</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>1403000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1585000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1643000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1204000</v>
       </c>
-      <c r="G21" s="3">
-        <v>687000</v>
-      </c>
       <c r="H21" s="3">
+        <v>998000</v>
+      </c>
+      <c r="I21" s="3">
         <v>1382000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1310000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1039000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-259000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1169000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1557000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1553000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2098000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1563000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1618000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1796000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2085000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2210000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1526000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1656000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>3563000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>3894000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>836000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>850000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>167000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>192000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>505000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>855000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>153000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>805000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1973000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>158600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>263000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>113700</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>113000</v>
+      </c>
+      <c r="E22" s="3">
         <v>133000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>158000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>80000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>78000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>88000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>86000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>98000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>84000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>87000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>85000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>86000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>85000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>90000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>81000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>85000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>79000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>81000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>80000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>83000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>431000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>109000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>106000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>108000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>115000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>110000</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>137000</v>
       </c>
       <c r="AD22" s="3">
         <v>137000</v>
       </c>
       <c r="AE22" s="3">
+        <v>137000</v>
+      </c>
+      <c r="AF22" s="3">
         <v>135000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>144000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>153000</v>
       </c>
-      <c r="AH22" s="3">
-        <v>0</v>
-      </c>
       <c r="AI22" s="3">
         <v>0</v>
       </c>
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>1881000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1025000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1041000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>661000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>771000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>803000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>766000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>474000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-947000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>625000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>996000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1007000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1456000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>935000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1037000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1204000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1462000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1555000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>880000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1049000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2560000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>3226000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>264000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>307000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-389000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-281000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>40000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>393000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-416000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>271000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1411000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>119600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>127800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>109500</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>694000</v>
+      </c>
+      <c r="E24" s="3">
         <v>245000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>407000</v>
-      </c>
-      <c r="F24" s="3">
-        <v>174000</v>
       </c>
       <c r="G24" s="3">
         <v>174000</v>
       </c>
       <c r="H24" s="3">
+        <v>174000</v>
+      </c>
+      <c r="I24" s="3">
         <v>218000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>264000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>205000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-131000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>215000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>279000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>301000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>304000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>323000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>343000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>374000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>404000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>284000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>258000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>386000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>784000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>791000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>41000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>167000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>776000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>105000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>116000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>201000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>394000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>314000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>274000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>34700</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>33500</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>32200</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2468,216 +2516,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>1187000</v>
+      </c>
+      <c r="E26" s="3">
         <v>780000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>634000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>487000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>597000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>585000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>502000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>269000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-816000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>410000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>717000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>706000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1152000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>612000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>694000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>830000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1058000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1271000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>622000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>663000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1776000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2435000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>223000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>140000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-1165000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-386000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-76000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>192000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-810000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-43000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1137000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>84900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>94300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>77300</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>996000</v>
+      </c>
+      <c r="E27" s="3">
         <v>483000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>370000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>295000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>479000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>368000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>305000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>120000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-735000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>241000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>488000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>438000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>726000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>347000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>411000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>538000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>685000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>882000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>357000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>400000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1387000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2277000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>194000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>111000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-1197000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-412000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-94000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>158000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-657000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-11000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1084000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>69800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>78500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>65600</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2780,8 +2837,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2848,8 +2908,8 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>91</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>91</v>
@@ -2866,17 +2926,17 @@
       <c r="AD29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="AF29" s="3">
         <v>343000</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AH29" s="3">
-        <v>0</v>
+      <c r="AH29" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="AI29" s="3">
         <v>0</v>
@@ -2884,8 +2944,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -2988,8 +3051,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -3092,216 +3158,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>-77000</v>
+      </c>
+      <c r="E32" s="3">
         <v>45000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>109000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>35000</v>
       </c>
-      <c r="G32" s="3">
-        <v>19000</v>
-      </c>
       <c r="H32" s="3">
+        <v>-69000</v>
+      </c>
+      <c r="I32" s="3">
         <v>36000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>69000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>14000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-21000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-12000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>4000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>3000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>10000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1000</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>2000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>6000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-325000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>13000</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>12000</v>
       </c>
       <c r="Z32" s="3">
         <v>12000</v>
       </c>
       <c r="AA32" s="3">
+        <v>12000</v>
+      </c>
+      <c r="AB32" s="3">
         <v>2000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>20000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-5000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-7000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-6000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>4800</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>4700</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-5800</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>996000</v>
+      </c>
+      <c r="E33" s="3">
         <v>483000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>370000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>295000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>479000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>368000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>305000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>120000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-735000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>241000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>488000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>438000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>726000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>347000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>411000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>538000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>685000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>882000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>357000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>400000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1387000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2277000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>194000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>111000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-1197000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-412000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-94000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>158000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-314000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-11000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1084000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>69800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>78500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>65600</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3404,221 +3479,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>996000</v>
+      </c>
+      <c r="E35" s="3">
         <v>483000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>370000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>295000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>479000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>368000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>305000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>120000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-735000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>241000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>488000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>438000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>726000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>347000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>411000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>538000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>685000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>882000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>357000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>400000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1387000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2277000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>194000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>111000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-1197000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-412000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-94000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>158000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-314000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-11000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1084000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>69800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>78500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>65600</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -3655,8 +3739,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -3693,112 +3778,116 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>4074000</v>
+      </c>
+      <c r="E41" s="3">
         <v>4225000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4036000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3942000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4148000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4261000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4157000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4377000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4440000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5240000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5780000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5887000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5280000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5043000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5138000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5672000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5188000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>4744000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3743000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3327000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3314000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2405000</v>
-      </c>
-      <c r="Y41" s="3">
-        <v>2153000</v>
       </c>
       <c r="Z41" s="3">
         <v>2153000</v>
       </c>
       <c r="AA41" s="3">
+        <v>2153000</v>
+      </c>
+      <c r="AB41" s="3">
         <v>1571000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1697000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2085000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2384000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2234000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2025000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2926000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>600300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>516300</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>361100</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
@@ -3901,637 +3990,658 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>1363000</v>
+      </c>
+      <c r="E43" s="3">
         <v>684000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>566000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>654000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1178000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>561000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>603000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>557000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>554000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>499000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>577000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>640000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>623000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>600000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>554000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>530000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>558000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>509000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>407000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>371000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>363000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>311000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>427000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>383000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>248000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>189000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>194000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>173000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>239000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>224000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>190000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>236800</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>231400</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>223400</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>1942000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1784000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1684000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1805000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1782000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1913000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1868000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1913000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1781000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1691000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1699000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1766000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1734000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1821000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1825000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1776000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1878000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2111000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2160000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2159000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2289000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2265000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1930000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1966000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1852000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1898000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1940000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1887000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1890000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>2038000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1901000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>124600</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>119000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>135800</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>103000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1334000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>916000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>880000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>127000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>684000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>742000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1691000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1690000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>786000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>754000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>722000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>612000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>547000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>522000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>806000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>519000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>495000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>609000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>594000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>921000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>529000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>333000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>372000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>307000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>319000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>356000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>352000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>321000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>455000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>486000</v>
       </c>
-      <c r="AH45" s="3">
-        <v>0</v>
-      </c>
       <c r="AI45" s="3">
         <v>0</v>
       </c>
       <c r="AJ45" s="3">
         <v>0</v>
       </c>
+      <c r="AK45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>7632000</v>
+      </c>
+      <c r="E46" s="3">
         <v>8027000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7202000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7281000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7438000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7419000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>7370000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>8538000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>8465000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>8216000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>8810000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>9015000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>8249000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>8011000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>8039000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>8784000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>8143000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>7859000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>6919000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>6451000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>6887000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>5510000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4843000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4874000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3978000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>4103000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4575000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4796000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>4684000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>4742000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>5503000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>961600</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>866800</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>720300</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>4154000</v>
+      </c>
+      <c r="E47" s="3">
         <v>4275000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>4262000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>4178000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>4264000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>3998000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>4004000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>3969000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3983000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4064000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>4113000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4334000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>4594000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>4762000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>4715000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>4646000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>4670000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>4643000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>4587000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>4556000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>4527000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>4474000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>4459000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>4444000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1234000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1233000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1214000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1233000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1213000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1243000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1218000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1446800</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1448600</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>1479500</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>28559000</v>
+      </c>
+      <c r="E48" s="3">
         <v>27288000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>26994000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>26648000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>26416000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>26621000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>26311000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>26084000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>25821000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>25329000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>25202000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>25153000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>24954000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>24747000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>24755000</v>
-      </c>
-      <c r="R48" s="3">
-        <v>24628000</v>
       </c>
       <c r="S48" s="3">
         <v>24628000</v>
       </c>
       <c r="T48" s="3">
+        <v>24628000</v>
+      </c>
+      <c r="U48" s="3">
         <v>24698000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>24727000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>24809000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>24141000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>24758000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>16890000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>16891000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>12826000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>13226000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>13727000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>13755000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>13806000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>13961000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>13943000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1564000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1560900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1567300</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
-        <v>3729000</v>
+        <v>3245000</v>
       </c>
       <c r="E49" s="3">
         <v>3729000</v>
@@ -4540,7 +4650,7 @@
         <v>3729000</v>
       </c>
       <c r="G49" s="3">
-        <v>3730000</v>
+        <v>3729000</v>
       </c>
       <c r="H49" s="3">
         <v>3730000</v>
@@ -4555,7 +4665,7 @@
         <v>3730000</v>
       </c>
       <c r="L49" s="3">
-        <v>4918000</v>
+        <v>3730000</v>
       </c>
       <c r="M49" s="3">
         <v>4918000</v>
@@ -4564,73 +4674,76 @@
         <v>4918000</v>
       </c>
       <c r="O49" s="3">
+        <v>4918000</v>
+      </c>
+      <c r="P49" s="3">
         <v>4919000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4920000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4927000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4937000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4938000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4939000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4983000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4999000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4995000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>5025000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3064000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3037000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1403000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1559000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1560000</v>
-      </c>
-      <c r="AD49" s="3">
-        <v>1585000</v>
       </c>
       <c r="AE49" s="3">
         <v>1585000</v>
       </c>
       <c r="AF49" s="3">
+        <v>1585000</v>
+      </c>
+      <c r="AG49" s="3">
         <v>1556000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1586000</v>
       </c>
-      <c r="AH49" s="3">
-        <v>0</v>
-      </c>
       <c r="AI49" s="3">
         <v>0</v>
       </c>
       <c r="AJ49" s="3">
         <v>0</v>
       </c>
+      <c r="AK49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -4733,8 +4846,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -4837,112 +4953,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>3819000</v>
+      </c>
+      <c r="E52" s="3">
         <v>4035000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4032000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4007000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3776000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3800000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3852000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3812000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3966000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3915000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3799000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3886000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4174000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4194000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4092000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3853000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4127000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3977000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3964000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4124000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3842000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>4100000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3346000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3383000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3190000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>3997000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>4046000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>4027000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>4020000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>3570000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>3557000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>163600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>164700</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>151000</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -5045,112 +5167,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>47626000</v>
+      </c>
+      <c r="E54" s="3">
         <v>47354000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>46219000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>45843000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>45811000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>45595000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>45286000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>46152000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>45965000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>46442000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>46842000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>47306000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>46890000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>46634000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>46528000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>46848000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>46506000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>46116000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>45180000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>44939000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>44392000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>43867000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>32602000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>32629000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>22631000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>24118000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>25122000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>25396000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>25308000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>25072000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>25807000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>4136000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>4041000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>3918100</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -5187,8 +5315,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -5225,150 +5354,154 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>655000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1479000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1386000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1360000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>678000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1584000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1525000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1504000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1556000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1571000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1537000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1525000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1448000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1444000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1157000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1168000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1458000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1032000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1072000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1140000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1155000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1337000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1064000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1213000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1101000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1125000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>944000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1046000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1059000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1118000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1044000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>120000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>127400</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>136700</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>84000</v>
+      </c>
+      <c r="E58" s="3">
         <v>13000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>11000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>12000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>43000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>8000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>13000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>12000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>13000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>12000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>13000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>14000</v>
-      </c>
-      <c r="O58" s="3">
-        <v>15000</v>
       </c>
       <c r="P58" s="3">
         <v>15000</v>
@@ -5377,367 +5510,376 @@
         <v>15000</v>
       </c>
       <c r="R58" s="3">
+        <v>15000</v>
+      </c>
+      <c r="S58" s="3">
         <v>13000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>20000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>21000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>26000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>29000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>375000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>66000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>303000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>308000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>43000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>49000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>680000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>57000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>59000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>63000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>116000</v>
       </c>
-      <c r="AH58" s="3">
-        <v>0</v>
-      </c>
       <c r="AI58" s="3">
         <v>0</v>
       </c>
       <c r="AJ58" s="3">
         <v>0</v>
       </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>891000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1537000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>995000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>823000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>760000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>826000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>732000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1690000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1551000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>605000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>680000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>708000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>623000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>521000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>626000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1150000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>742000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>698000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>713000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>801000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>846000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>441000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>415000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>463000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>524000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>375000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>536000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>595000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>629000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>557000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>386000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>71100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>61000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>34700</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>2642000</v>
+      </c>
+      <c r="E60" s="3">
         <v>3029000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2392000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2195000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2356000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2418000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2270000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3206000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3120000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2188000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2230000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2247000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2086000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1980000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1798000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2331000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2220000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1751000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1811000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1970000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2376000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1844000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1782000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1984000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1668000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1549000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2160000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1698000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1747000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1738000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1546000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>191100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>188400</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>171400</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>5172000</v>
+      </c>
+      <c r="E61" s="3">
         <v>4712000</v>
-      </c>
-      <c r="E61" s="3">
-        <v>4713000</v>
       </c>
       <c r="F61" s="3">
         <v>4713000</v>
       </c>
       <c r="G61" s="3">
+        <v>4713000</v>
+      </c>
+      <c r="H61" s="3">
         <v>5180000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4767000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4761000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4765000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4769000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5083000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5131000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5130000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5135000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>5139000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>5137000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>5140000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>5135000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>5140000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>5142000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>5150000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>5161000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>5494000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>5504000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>5499000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>5695000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>5696000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>5712000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>6344000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>6364000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>6384000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>7328000</v>
-      </c>
-      <c r="AH61" s="3">
-        <v>2800</v>
       </c>
       <c r="AI61" s="3">
         <v>2800</v>
@@ -5745,112 +5887,118 @@
       <c r="AJ61" s="3">
         <v>2800</v>
       </c>
+      <c r="AK61" s="3">
+        <v>2800</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>2028000</v>
+      </c>
+      <c r="E62" s="3">
         <v>3237000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3148000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3246000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2202000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3345000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3484000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3593000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>6787000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>6864000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>6947000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>7303000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>7362000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>7425000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>7419000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>7298000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>7441000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>7575000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>7481000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>7464000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>7028000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>8129000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>6849000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>6844000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>5883000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>6187000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>6144000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>6088000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>6130000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>5328000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>5248000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>101700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>97800</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>88900</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -5953,8 +6101,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6057,8 +6208,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -6161,112 +6315,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>14370000</v>
+      </c>
+      <c r="E66" s="3">
         <v>14457000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>13724000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>13626000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>13809000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>13897000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>13801000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>14834000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>23194000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>22578000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>22731000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>23131000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>23033000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>23016000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>22839000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>23174000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>23165000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>23317000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>23148000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>23252000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>22960000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>23718000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>16856000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>17031000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>15038000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>15211000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>15766000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>15917000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>16022000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>15458000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>16165000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>559400</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>542300</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>502400</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -6303,8 +6463,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -6407,8 +6568,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -6511,8 +6675,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -6615,8 +6782,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -6719,112 +6889,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>-5269000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-6092000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-6400000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-6594000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-6713000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-7016000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-7208000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-7338000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-7282000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-6284000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-6173000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-6306000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-6566000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-7132000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-7320000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-7571000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-7949000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-8474000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-9214000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-9446000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-9722000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-11020000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-13227000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-13351000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-13453000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-12148000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-11701000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-11572000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-11759000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-11428000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-11382000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>2014900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>1956700</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>1874200</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -6927,8 +7103,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -7031,8 +7210,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -7135,112 +7317,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>24290000</v>
+      </c>
+      <c r="E76" s="3">
         <v>23831000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>23616000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>23463000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>23341000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>23020000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>22839000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>22713000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>22771000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>23864000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>24111000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>24175000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>23857000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>23618000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>23689000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>23674000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>23341000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>22799000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>22032000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>21687000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>21432000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>20149000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>15746000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>15598000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>7593000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>8907000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>9356000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>9479000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>9286000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>9614000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>9642000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>3576600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>3498700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>3415700</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -7343,221 +7531,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>996000</v>
+      </c>
+      <c r="E81" s="3">
         <v>483000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>370000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>295000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>479000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>368000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>305000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>120000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-735000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>241000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>488000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>438000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>726000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>347000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>411000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>538000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>685000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>882000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>357000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>400000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1387000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2277000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>194000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>111000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-1197000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-412000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-94000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>158000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-314000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-11000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1084000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>69800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>78500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>65600</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -7594,112 +7791,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>564000</v>
+      </c>
+      <c r="E83" s="3">
         <v>504000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>480000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>495000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>603000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>457000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>476000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>460000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>604000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>457000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>476000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>460000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>557000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>538000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>500000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>507000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>544000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>574000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>566000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>524000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>572000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>559000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>466000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>435000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>441000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>363000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>328000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>325000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>434000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>390000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>409000</v>
       </c>
-      <c r="AH83" s="3">
-        <v>0</v>
-      </c>
       <c r="AI83" s="3">
         <v>0</v>
       </c>
       <c r="AJ83" s="3">
         <v>0</v>
       </c>
+      <c r="AK83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -7802,8 +8003,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -7906,8 +8110,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -8010,8 +8217,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -8114,8 +8324,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -8218,112 +8431,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>1392000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1180000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1159000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>760000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>997000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1127000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>832000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>776000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>795000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>758000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>924000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1004000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1387000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1050000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>639000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1302000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1638000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1859000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1031000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>889000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>875000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1004000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>434000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>520000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>411000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>706000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>141000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>507000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>590000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>532000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>448000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>133100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>204700</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>119300</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -8360,112 +8579,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-891000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-736000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-819000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-728000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-861000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-768000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-769000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-688000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-891000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-792000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-755000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-611000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-669000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-569000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-658000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-539000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-546000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-548000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-509000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-451000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-446000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-502000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-379000</v>
-      </c>
-      <c r="Z91" s="3">
-        <v>-374000</v>
       </c>
       <c r="AA91" s="3">
         <v>-374000</v>
       </c>
       <c r="AB91" s="3">
+        <v>-374000</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-387000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-313000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-326000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-350000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-307000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-405000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-41300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-50300</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-32000</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -8568,8 +8791,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -8672,112 +8898,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-778000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-603000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-703000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-680000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-766000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-689000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-743000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-618000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-780000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-639000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-301000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>9000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-387000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-499000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-603000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-408000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-405000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-454000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-264000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-163000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>362000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-383000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-351000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>422000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-477000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-386000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-347000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-284000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-256000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-306000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>556000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-44700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-48000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-27900</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -8814,91 +9046,92 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
+        <v>172000</v>
+      </c>
+      <c r="E96" s="3">
         <v>174000</v>
-      </c>
-      <c r="E96" s="3">
-        <v>175000</v>
       </c>
       <c r="F96" s="3">
         <v>175000</v>
       </c>
       <c r="G96" s="3">
+        <v>175000</v>
+      </c>
+      <c r="H96" s="3">
         <v>176000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>175000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>174000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>175000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-261000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-351000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-353000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-178000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-159000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-158000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-159000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-158000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-160000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-141000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-124000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-122000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-87000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-67000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-61000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-333000</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-31000</v>
       </c>
       <c r="AB96" s="3">
         <v>-31000</v>
       </c>
       <c r="AC96" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-32000</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-31000</v>
       </c>
       <c r="AE96" s="3">
         <v>-31000</v>
@@ -8907,19 +9140,22 @@
         <v>-31000</v>
       </c>
       <c r="AG96" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-32000</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
         <v>0</v>
       </c>
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -9022,8 +9258,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -9126,8 +9365,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -9230,147 +9472,153 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-762000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-387000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-362000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-284000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-342000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-333000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-309000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-221000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-815000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-656000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-727000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-406000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-763000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-646000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-570000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-409000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-789000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-408000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-348000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-709000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-328000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-369000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-82000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-360000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-57000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-704000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-92000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-72000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-126000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1127000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-355000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-4400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1000</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
+      <c r="G101" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="H101" s="3">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="I101" s="3">
         <v>-3000</v>
       </c>
-      <c r="J101" s="3" t="s">
+      <c r="J101" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="K101" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
       <c r="L101" s="3">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="M101" s="3">
         <v>-3000</v>
       </c>
       <c r="N101" s="3">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="O101" s="3">
         <v>0</v>
@@ -9382,50 +9630,50 @@
         <v>0</v>
       </c>
       <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
         <v>-1000</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
       <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
         <v>4000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-3000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-4000</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
       <c r="X101" s="3">
         <v>0</v>
       </c>
       <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
       <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
         <v>-3000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-4000</v>
-      </c>
-      <c r="AC101" s="3">
-        <v>-1000</v>
       </c>
       <c r="AD101" s="3">
         <v>-1000</v>
       </c>
       <c r="AE101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AF101" s="3">
         <v>1000</v>
       </c>
-      <c r="AF101" s="3">
-        <v>0</v>
-      </c>
       <c r="AG101" s="3">
         <v>0</v>
       </c>
@@ -9438,108 +9686,114 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>-151000</v>
+      </c>
+      <c r="E102" s="3">
         <v>189000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>94000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-206000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-113000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>104000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-220000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-63000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-800000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-540000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-107000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>607000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>237000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-95000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-534000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>484000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>444000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1001000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>416000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>13000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>909000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>252000</v>
       </c>
-      <c r="Y102" s="3">
-        <v>0</v>
-      </c>
       <c r="Z102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="3">
         <v>582000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-126000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-388000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-299000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>150000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>209000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-901000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>649000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>84000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>155200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>88400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GOLD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GOLD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
   <si>
     <t>GOLD</t>
   </si>
@@ -656,17 +656,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -677,452 +677,503 @@
     <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="34" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="38" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="G7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>3645000</v>
+        <v>6476900</v>
       </c>
       <c r="E8" s="3">
-        <v>3368000</v>
+        <v>3680800</v>
       </c>
       <c r="F8" s="3">
-        <v>3162000</v>
+        <v>2512000</v>
       </c>
       <c r="G8" s="3">
+        <v>3009100</v>
+      </c>
+      <c r="H8" s="3">
+        <v>2742300</v>
+      </c>
+      <c r="I8" s="3">
+        <v>2715100</v>
+      </c>
+      <c r="J8" s="3">
+        <v>2525000</v>
+      </c>
+      <c r="K8" s="3">
         <v>2747000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="L8" s="3">
         <v>3059000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="M8" s="3">
         <v>2862000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="N8" s="3">
         <v>2833000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="O8" s="3">
         <v>2643000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="P8" s="3">
         <v>2774000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="Q8" s="3">
         <v>2527000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="R8" s="3">
         <v>2859000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="S8" s="3">
         <v>2853000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="T8" s="3">
         <v>3310000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="U8" s="3">
         <v>2826000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="V8" s="3">
         <v>2893000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="W8" s="3">
         <v>2956000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="X8" s="3">
         <v>3279000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="Y8" s="3">
         <v>3540000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="Z8" s="3">
         <v>3055000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="AA8" s="3">
         <v>2721000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="AB8" s="3">
         <v>2883000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AC8" s="3">
         <v>2678000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AD8" s="3">
         <v>2063000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AE8" s="3">
         <v>2093000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AF8" s="3">
         <v>1904000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AG8" s="3">
         <v>1837000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AH8" s="3">
         <v>1712000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AI8" s="3">
         <v>1790000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AJ8" s="3">
         <v>2228000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AK8" s="3">
         <v>1993000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AL8" s="3">
         <v>2160000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AM8" s="3">
         <v>316700</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AN8" s="3">
         <v>356400</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AO8" s="3">
         <v>300000</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>2033000</v>
+        <v>6383500</v>
       </c>
       <c r="E9" s="3">
-        <v>2046000</v>
+        <v>3607900</v>
       </c>
       <c r="F9" s="3">
-        <v>1968000</v>
+        <v>2430400</v>
       </c>
       <c r="G9" s="3">
+        <v>2968100</v>
+      </c>
+      <c r="H9" s="3">
+        <v>2697600</v>
+      </c>
+      <c r="I9" s="3">
+        <v>2671700</v>
+      </c>
+      <c r="J9" s="3">
+        <v>2482000</v>
+      </c>
+      <c r="K9" s="3">
         <v>1914000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="L9" s="3">
         <v>2166000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="M9" s="3">
         <v>1902000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="N9" s="3">
         <v>1936000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="O9" s="3">
         <v>1928000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="P9" s="3">
         <v>2093000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="Q9" s="3">
         <v>1815000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="R9" s="3">
         <v>1850000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="S9" s="3">
         <v>1739000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="T9" s="3">
         <v>1905000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="U9" s="3">
         <v>1768000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="V9" s="3">
         <v>1704000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="W9" s="3">
         <v>1712000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="X9" s="3">
         <v>1814000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="Y9" s="3">
         <v>1927000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="Z9" s="3">
         <v>1900000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="AA9" s="3">
         <v>1776000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="AB9" s="3">
         <v>1987000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AC9" s="3">
         <v>1889000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AD9" s="3">
         <v>1545000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AE9" s="3">
         <v>1490000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AF9" s="3">
         <v>1577000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AG9" s="3">
         <v>1315000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AH9" s="3">
         <v>1176000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AI9" s="3">
         <v>1152000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AJ9" s="3">
         <v>1411000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AK9" s="3">
         <v>1270000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AL9" s="3">
         <v>1277000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AM9" s="3">
         <v>167400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AN9" s="3">
         <v>196700</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AO9" s="3">
         <v>169100</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1612000</v>
+        <v>93400</v>
       </c>
       <c r="E10" s="3">
-        <v>1322000</v>
+        <v>72900</v>
       </c>
       <c r="F10" s="3">
-        <v>1194000</v>
+        <v>81700</v>
       </c>
       <c r="G10" s="3">
+        <v>41000</v>
+      </c>
+      <c r="H10" s="3">
+        <v>44800</v>
+      </c>
+      <c r="I10" s="3">
+        <v>43400</v>
+      </c>
+      <c r="J10" s="3">
+        <v>43000</v>
+      </c>
+      <c r="K10" s="3">
         <v>833000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="L10" s="3">
         <v>893000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="M10" s="3">
         <v>960000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="N10" s="3">
         <v>897000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="O10" s="3">
         <v>715000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="P10" s="3">
         <v>681000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="Q10" s="3">
         <v>712000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="R10" s="3">
         <v>1009000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="S10" s="3">
         <v>1114000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="T10" s="3">
         <v>1405000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="U10" s="3">
         <v>1058000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="V10" s="3">
         <v>1189000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="W10" s="3">
         <v>1244000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="X10" s="3">
         <v>1465000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="Y10" s="3">
         <v>1613000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="Z10" s="3">
         <v>1155000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="AA10" s="3">
         <v>945000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="AB10" s="3">
         <v>896000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AC10" s="3">
         <v>789000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AD10" s="3">
         <v>518000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AE10" s="3">
         <v>603000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AF10" s="3">
         <v>327000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AG10" s="3">
         <v>522000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AH10" s="3">
         <v>536000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AI10" s="3">
         <v>638000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AJ10" s="3">
         <v>817000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AK10" s="3">
         <v>723000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AL10" s="3">
         <v>883000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AM10" s="3">
         <v>149300</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AN10" s="3">
         <v>159700</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AO10" s="3">
         <v>130900</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1160,13 +1211,17 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
-        <v>1000</v>
+      <c r="D12" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>91</v>
@@ -1189,86 +1244,98 @@
       <c r="K12" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="P12" s="3">
         <v>106000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="Q12" s="3">
         <v>77000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="R12" s="3">
         <v>100000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="S12" s="3">
         <v>67000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="T12" s="3">
         <v>82000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="U12" s="3">
         <v>67000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="V12" s="3">
         <v>77000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="W12" s="3">
         <v>61000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="X12" s="3">
         <v>74000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="Y12" s="3">
         <v>72000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="Z12" s="3">
         <v>78000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="AA12" s="3">
         <v>71000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="AB12" s="3">
         <v>40000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AC12" s="3">
         <v>86000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AD12" s="3">
         <v>98000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AE12" s="3">
         <v>74000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AF12" s="3">
         <v>87000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AG12" s="3">
         <v>89000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AH12" s="3">
         <v>97000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AI12" s="3">
         <v>73000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AJ12" s="3">
         <v>98000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AK12" s="3">
         <v>100000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AL12" s="3">
         <v>81000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AM12" s="3">
         <v>10900</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AN12" s="3">
         <v>8000</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AO12" s="3">
         <v>11200</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1374,154 +1441,178 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>69000</v>
+        <v>100</v>
       </c>
       <c r="E14" s="3">
-        <v>9000</v>
+        <v>-2400</v>
       </c>
       <c r="F14" s="3">
-        <v>15000</v>
+        <v>-3600</v>
       </c>
       <c r="G14" s="3">
+        <v>11700</v>
+      </c>
+      <c r="H14" s="3">
+        <v>700</v>
+      </c>
+      <c r="I14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J14" s="3">
+        <v>-16700</v>
+      </c>
+      <c r="K14" s="3">
         <v>44000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="L14" s="3">
         <v>-32000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="M14" s="3">
         <v>31000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="N14" s="3">
         <v>27000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="O14" s="3">
         <v>18000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="P14" s="3">
         <v>1637000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="Q14" s="3">
         <v>60000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="R14" s="3">
         <v>17000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="S14" s="3">
         <v>19000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="T14" s="3">
         <v>57000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="U14" s="3">
         <v>27000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="V14" s="3">
         <v>23000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="W14" s="3">
         <v>-77000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="X14" s="3">
         <v>64000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="Y14" s="3">
         <v>-80000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="Z14" s="3">
         <v>81000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="AA14" s="3">
         <v>-311000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="AB14" s="3">
         <v>-514000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AC14" s="3">
         <v>-2726000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AD14" s="3">
         <v>27000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AE14" s="3">
         <v>44000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AF14" s="3">
         <v>451000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AG14" s="3">
         <v>495000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AH14" s="3">
         <v>67000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AI14" s="3">
         <v>28000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AJ14" s="3">
         <v>1029000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AK14" s="3">
         <v>117000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AL14" s="3">
         <v>18000</v>
       </c>
-      <c r="AI14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK14" s="3">
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO14" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>-594000</v>
+        <v>7600</v>
       </c>
       <c r="E15" s="3">
-        <v>500000</v>
+        <v>7600</v>
       </c>
       <c r="F15" s="3">
-        <v>503000</v>
+        <v>8600</v>
       </c>
       <c r="G15" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H15" s="3">
+        <v>4600</v>
+      </c>
+      <c r="I15" s="3">
+        <v>4700</v>
+      </c>
+      <c r="J15" s="3">
+        <v>2800</v>
+      </c>
+      <c r="K15" s="3">
         <v>495000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="L15" s="3">
         <v>268000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="M15" s="3">
         <v>526000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="N15" s="3">
         <v>501000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="O15" s="3">
         <v>516000</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
-      <c r="N15" s="3">
-        <v>0</v>
-      </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1588,8 +1679,20 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1624,222 +1727,250 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
+      <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>1571000</v>
+        <v>6450800</v>
       </c>
       <c r="E17" s="3">
-        <v>2328000</v>
+        <v>3677700</v>
       </c>
       <c r="F17" s="3">
-        <v>2131000</v>
+        <v>2492900</v>
       </c>
       <c r="G17" s="3">
+        <v>3001900</v>
+      </c>
+      <c r="H17" s="3">
+        <v>2727300</v>
+      </c>
+      <c r="I17" s="3">
+        <v>2703100</v>
+      </c>
+      <c r="J17" s="3">
+        <v>2507200</v>
+      </c>
+      <c r="K17" s="3">
         <v>2073000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="L17" s="3">
         <v>2260000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="M17" s="3">
         <v>2042000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="N17" s="3">
         <v>2093000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="O17" s="3">
         <v>2134000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="P17" s="3">
         <v>3658000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="Q17" s="3">
         <v>1827000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="R17" s="3">
         <v>1774000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="S17" s="3">
         <v>1758000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="T17" s="3">
         <v>1770000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="U17" s="3">
         <v>1798000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="V17" s="3">
         <v>1765000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="W17" s="3">
         <v>1665000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="X17" s="3">
         <v>1737000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="Y17" s="3">
         <v>1904000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="Z17" s="3">
         <v>2093000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="AA17" s="3">
         <v>1583000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="AB17" s="3">
         <v>217000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AC17" s="3">
         <v>-670000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AD17" s="3">
         <v>1681000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AE17" s="3">
         <v>1666000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AF17" s="3">
         <v>2176000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AG17" s="3">
         <v>1988000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AH17" s="3">
         <v>1536000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AI17" s="3">
         <v>1264000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AJ17" s="3">
         <v>2514000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AK17" s="3">
         <v>1585000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AL17" s="3">
         <v>602000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AM17" s="3">
         <v>192200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AN17" s="3">
         <v>223900</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AO17" s="3">
         <v>196300</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>2074000</v>
+        <v>26100</v>
       </c>
       <c r="E18" s="3">
-        <v>1040000</v>
+        <v>3100</v>
       </c>
       <c r="F18" s="3">
-        <v>1031000</v>
+        <v>19200</v>
       </c>
       <c r="G18" s="3">
+        <v>7300</v>
+      </c>
+      <c r="H18" s="3">
+        <v>15100</v>
+      </c>
+      <c r="I18" s="3">
+        <v>12000</v>
+      </c>
+      <c r="J18" s="3">
+        <v>17800</v>
+      </c>
+      <c r="K18" s="3">
         <v>674000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="L18" s="3">
         <v>799000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="M18" s="3">
         <v>820000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="N18" s="3">
         <v>740000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="O18" s="3">
         <v>509000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="P18" s="3">
         <v>-884000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="Q18" s="3">
         <v>700000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="R18" s="3">
         <v>1085000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="S18" s="3">
         <v>1095000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="T18" s="3">
         <v>1540000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="U18" s="3">
         <v>1028000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="V18" s="3">
         <v>1128000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="W18" s="3">
         <v>1291000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="X18" s="3">
         <v>1542000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="Y18" s="3">
         <v>1636000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="Z18" s="3">
         <v>962000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="AA18" s="3">
         <v>1138000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="AB18" s="3">
         <v>2666000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AC18" s="3">
         <v>3348000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AD18" s="3">
         <v>382000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AE18" s="3">
         <v>427000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AF18" s="3">
         <v>-272000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AG18" s="3">
         <v>-151000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AH18" s="3">
         <v>176000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AI18" s="3">
         <v>526000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AJ18" s="3">
         <v>-286000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AK18" s="3">
         <v>408000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AL18" s="3">
         <v>1558000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AM18" s="3">
         <v>124500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AN18" s="3">
         <v>132500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AO18" s="3">
         <v>103700</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1877,543 +2008,607 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>77000</v>
+        <v>-300</v>
       </c>
       <c r="E20" s="3">
-        <v>-45000</v>
+        <v>-1200</v>
       </c>
       <c r="F20" s="3">
-        <v>-109000</v>
+        <v>2200</v>
       </c>
       <c r="G20" s="3">
+        <v>-700</v>
+      </c>
+      <c r="H20" s="3">
+        <v>2800</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="K20" s="3">
         <v>-35000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="L20" s="3">
         <v>69000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="M20" s="3">
         <v>-36000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="N20" s="3">
         <v>-69000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="O20" s="3">
         <v>-14000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="P20" s="3">
         <v>21000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="Q20" s="3">
         <v>12000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="R20" s="3">
         <v>-4000</v>
-      </c>
-      <c r="O20" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="P20" s="3">
-        <v>1000</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="R20" s="3">
-        <v>-10000</v>
       </c>
       <c r="S20" s="3">
         <v>-2000</v>
       </c>
       <c r="T20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="U20" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="V20" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="W20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="X20" s="3">
         <v>-1000</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
-      <c r="V20" s="3">
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-2000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="AA20" s="3">
         <v>-6000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="AB20" s="3">
         <v>325000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AC20" s="3">
         <v>-13000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AD20" s="3">
         <v>-12000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AE20" s="3">
         <v>-12000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AF20" s="3">
         <v>-2000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AG20" s="3">
         <v>-20000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AH20" s="3">
         <v>1000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AI20" s="3">
         <v>4000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AJ20" s="3">
         <v>5000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AK20" s="3">
         <v>7000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AL20" s="3">
         <v>6000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AM20" s="3">
         <v>-4800</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AN20" s="3">
         <v>-4700</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AO20" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>1403000</v>
+        <v>34000</v>
       </c>
       <c r="E21" s="3">
-        <v>1585000</v>
+        <v>11900</v>
       </c>
       <c r="F21" s="3">
-        <v>1643000</v>
+        <v>25600</v>
       </c>
       <c r="G21" s="3">
+        <v>13000</v>
+      </c>
+      <c r="H21" s="3">
+        <v>16900</v>
+      </c>
+      <c r="I21" s="3">
+        <v>17700</v>
+      </c>
+      <c r="J21" s="3">
+        <v>21700</v>
+      </c>
+      <c r="K21" s="3">
         <v>1204000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="L21" s="3">
         <v>998000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="M21" s="3">
         <v>1382000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="N21" s="3">
         <v>1310000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="O21" s="3">
         <v>1039000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="P21" s="3">
         <v>-259000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="Q21" s="3">
         <v>1169000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="R21" s="3">
         <v>1557000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="S21" s="3">
         <v>1553000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="T21" s="3">
         <v>2098000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="U21" s="3">
         <v>1563000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="V21" s="3">
         <v>1618000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="W21" s="3">
         <v>1796000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="X21" s="3">
         <v>2085000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="Y21" s="3">
         <v>2210000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="Z21" s="3">
         <v>1526000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="AA21" s="3">
         <v>1656000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="AB21" s="3">
         <v>3563000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AC21" s="3">
         <v>3894000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AD21" s="3">
         <v>836000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AE21" s="3">
         <v>850000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AF21" s="3">
         <v>167000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AG21" s="3">
         <v>192000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AH21" s="3">
         <v>505000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AI21" s="3">
         <v>855000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AJ21" s="3">
         <v>153000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AK21" s="3">
         <v>805000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AL21" s="3">
         <v>1973000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AM21" s="3">
         <v>158600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AN21" s="3">
         <v>263000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AO21" s="3">
         <v>113700</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>113000</v>
+        <v>16300</v>
       </c>
       <c r="E22" s="3">
-        <v>133000</v>
+        <v>12600</v>
       </c>
       <c r="F22" s="3">
-        <v>158000</v>
+        <v>12900</v>
       </c>
       <c r="G22" s="3">
+        <v>13000</v>
+      </c>
+      <c r="H22" s="3">
+        <v>10400</v>
+      </c>
+      <c r="I22" s="3">
+        <v>10000</v>
+      </c>
+      <c r="J22" s="3">
+        <v>9600</v>
+      </c>
+      <c r="K22" s="3">
         <v>80000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="L22" s="3">
         <v>78000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="M22" s="3">
         <v>88000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="N22" s="3">
         <v>86000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="O22" s="3">
         <v>98000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="P22" s="3">
         <v>84000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="Q22" s="3">
         <v>87000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="R22" s="3">
         <v>85000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="S22" s="3">
         <v>86000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="T22" s="3">
         <v>85000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="U22" s="3">
         <v>90000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="V22" s="3">
         <v>81000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="W22" s="3">
         <v>85000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="X22" s="3">
         <v>79000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="Y22" s="3">
         <v>81000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="Z22" s="3">
         <v>80000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="AA22" s="3">
         <v>83000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="AB22" s="3">
         <v>431000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AC22" s="3">
         <v>109000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AD22" s="3">
         <v>106000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AE22" s="3">
         <v>108000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AF22" s="3">
         <v>115000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AG22" s="3">
         <v>110000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AH22" s="3">
         <v>137000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AI22" s="3">
         <v>137000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AJ22" s="3">
         <v>135000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AK22" s="3">
         <v>144000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AL22" s="3">
         <v>153000</v>
       </c>
-      <c r="AI22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK22" s="3">
+      <c r="AM22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO22" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>1881000</v>
+        <v>15800</v>
       </c>
       <c r="E23" s="3">
-        <v>1025000</v>
+        <v>-300</v>
       </c>
       <c r="F23" s="3">
-        <v>1041000</v>
+        <v>13000</v>
       </c>
       <c r="G23" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="H23" s="3">
+        <v>8000</v>
+      </c>
+      <c r="I23" s="3">
+        <v>10200</v>
+      </c>
+      <c r="J23" s="3">
+        <v>34000</v>
+      </c>
+      <c r="K23" s="3">
         <v>661000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="L23" s="3">
         <v>771000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="M23" s="3">
         <v>803000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="N23" s="3">
         <v>766000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="O23" s="3">
         <v>474000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="P23" s="3">
         <v>-947000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="Q23" s="3">
         <v>625000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="R23" s="3">
         <v>996000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="S23" s="3">
         <v>1007000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="T23" s="3">
         <v>1456000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="U23" s="3">
         <v>935000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="V23" s="3">
         <v>1037000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="W23" s="3">
         <v>1204000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="X23" s="3">
         <v>1462000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="Y23" s="3">
         <v>1555000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="Z23" s="3">
         <v>880000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="AA23" s="3">
         <v>1049000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="AB23" s="3">
         <v>2560000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AC23" s="3">
         <v>3226000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AD23" s="3">
         <v>264000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AE23" s="3">
         <v>307000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AF23" s="3">
         <v>-389000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AG23" s="3">
         <v>-281000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AH23" s="3">
         <v>40000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AI23" s="3">
         <v>393000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AJ23" s="3">
         <v>-416000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AK23" s="3">
         <v>271000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AL23" s="3">
         <v>1411000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AM23" s="3">
         <v>119600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AN23" s="3">
         <v>127800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AO23" s="3">
         <v>109500</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>694000</v>
+        <v>2200</v>
       </c>
       <c r="E24" s="3">
-        <v>245000</v>
+        <v>700</v>
       </c>
       <c r="F24" s="3">
-        <v>407000</v>
+        <v>2900</v>
       </c>
       <c r="G24" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="H24" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I24" s="3">
+        <v>1800</v>
+      </c>
+      <c r="J24" s="3">
+        <v>3000</v>
+      </c>
+      <c r="K24" s="3">
         <v>174000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="L24" s="3">
         <v>174000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="M24" s="3">
         <v>218000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="N24" s="3">
         <v>264000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="O24" s="3">
         <v>205000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="P24" s="3">
         <v>-131000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="Q24" s="3">
         <v>215000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="R24" s="3">
         <v>279000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="S24" s="3">
         <v>301000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="T24" s="3">
         <v>304000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="U24" s="3">
         <v>323000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="V24" s="3">
         <v>343000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="W24" s="3">
         <v>374000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="X24" s="3">
         <v>404000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="Y24" s="3">
         <v>284000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="Z24" s="3">
         <v>258000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="AA24" s="3">
         <v>386000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="AB24" s="3">
         <v>784000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AC24" s="3">
         <v>791000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AD24" s="3">
         <v>41000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AE24" s="3">
         <v>167000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AF24" s="3">
         <v>776000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AG24" s="3">
         <v>105000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AH24" s="3">
         <v>116000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AI24" s="3">
         <v>201000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AJ24" s="3">
         <v>394000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AK24" s="3">
         <v>314000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AL24" s="3">
         <v>274000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AM24" s="3">
         <v>34700</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AN24" s="3">
         <v>33500</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AO24" s="3">
         <v>32200</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2519,222 +2714,258 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>1187000</v>
+        <v>13500</v>
       </c>
       <c r="E26" s="3">
-        <v>780000</v>
+        <v>-1000</v>
       </c>
       <c r="F26" s="3">
-        <v>634000</v>
+        <v>10200</v>
       </c>
       <c r="G26" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="H26" s="3">
+        <v>6000</v>
+      </c>
+      <c r="I26" s="3">
+        <v>8400</v>
+      </c>
+      <c r="J26" s="3">
+        <v>30900</v>
+      </c>
+      <c r="K26" s="3">
         <v>487000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="L26" s="3">
         <v>597000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="M26" s="3">
         <v>585000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="N26" s="3">
         <v>502000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="O26" s="3">
         <v>269000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="P26" s="3">
         <v>-816000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="Q26" s="3">
         <v>410000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="R26" s="3">
         <v>717000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="S26" s="3">
         <v>706000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="T26" s="3">
         <v>1152000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="U26" s="3">
         <v>612000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="V26" s="3">
         <v>694000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="W26" s="3">
         <v>830000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="X26" s="3">
         <v>1058000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="Y26" s="3">
         <v>1271000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="Z26" s="3">
         <v>622000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="AA26" s="3">
         <v>663000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="AB26" s="3">
         <v>1776000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AC26" s="3">
         <v>2435000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AD26" s="3">
         <v>223000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AE26" s="3">
         <v>140000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AF26" s="3">
         <v>-1165000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AG26" s="3">
         <v>-386000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AH26" s="3">
         <v>-76000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AI26" s="3">
         <v>192000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AJ26" s="3">
         <v>-810000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AK26" s="3">
         <v>-43000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AL26" s="3">
         <v>1137000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AM26" s="3">
         <v>84900</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AN26" s="3">
         <v>94300</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AO26" s="3">
         <v>77300</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>996000</v>
+        <v>11600</v>
       </c>
       <c r="E27" s="3">
-        <v>483000</v>
+        <v>-900</v>
       </c>
       <c r="F27" s="3">
-        <v>370000</v>
+        <v>10300</v>
       </c>
       <c r="G27" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="H27" s="3">
+        <v>6600</v>
+      </c>
+      <c r="I27" s="3">
+        <v>9000</v>
+      </c>
+      <c r="J27" s="3">
+        <v>30900</v>
+      </c>
+      <c r="K27" s="3">
         <v>295000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="L27" s="3">
         <v>479000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="M27" s="3">
         <v>368000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="N27" s="3">
         <v>305000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="O27" s="3">
         <v>120000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="P27" s="3">
         <v>-735000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="Q27" s="3">
         <v>241000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="R27" s="3">
         <v>488000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="S27" s="3">
         <v>438000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="T27" s="3">
         <v>726000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="U27" s="3">
         <v>347000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="V27" s="3">
         <v>411000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="W27" s="3">
         <v>538000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="X27" s="3">
         <v>685000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="Y27" s="3">
         <v>882000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="Z27" s="3">
         <v>357000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="AA27" s="3">
         <v>400000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="AB27" s="3">
         <v>1387000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AC27" s="3">
         <v>2277000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AD27" s="3">
         <v>194000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AE27" s="3">
         <v>111000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AF27" s="3">
         <v>-1197000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AG27" s="3">
         <v>-412000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AH27" s="3">
         <v>-94000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AI27" s="3">
         <v>158000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AJ27" s="3">
         <v>-657000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AK27" s="3">
         <v>-11000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AL27" s="3">
         <v>1084000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AM27" s="3">
         <v>69800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AN27" s="3">
         <v>78500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AO27" s="3">
         <v>65600</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2840,8 +3071,20 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2911,17 +3154,17 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>91</v>
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>91</v>
@@ -2929,8 +3172,8 @@
       <c r="AE29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AF29" s="3">
-        <v>343000</v>
+      <c r="AF29" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>91</v>
@@ -2938,17 +3181,29 @@
       <c r="AH29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AI29" s="3">
-        <v>0</v>
+      <c r="AI29" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="AJ29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK29" s="3">
+        <v>343000</v>
+      </c>
+      <c r="AK29" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL29" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO29" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -3054,8 +3309,20 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -3161,222 +3428,258 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>-77000</v>
+        <v>300</v>
       </c>
       <c r="E32" s="3">
-        <v>45000</v>
+        <v>1200</v>
       </c>
       <c r="F32" s="3">
-        <v>109000</v>
+        <v>-2200</v>
       </c>
       <c r="G32" s="3">
+        <v>700</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="I32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J32" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K32" s="3">
         <v>35000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="L32" s="3">
         <v>-69000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="M32" s="3">
         <v>36000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="N32" s="3">
         <v>69000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="O32" s="3">
         <v>14000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="P32" s="3">
         <v>-21000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="Q32" s="3">
         <v>-12000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="R32" s="3">
         <v>4000</v>
-      </c>
-      <c r="O32" s="3">
-        <v>2000</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>3000</v>
-      </c>
-      <c r="R32" s="3">
-        <v>10000</v>
       </c>
       <c r="S32" s="3">
         <v>2000</v>
       </c>
       <c r="T32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="U32" s="3">
+        <v>3000</v>
+      </c>
+      <c r="V32" s="3">
+        <v>10000</v>
+      </c>
+      <c r="W32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="X32" s="3">
         <v>1000</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
-      <c r="V32" s="3">
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>2000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="AA32" s="3">
         <v>6000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="AB32" s="3">
         <v>-325000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AC32" s="3">
         <v>13000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AD32" s="3">
         <v>12000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AE32" s="3">
         <v>12000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AF32" s="3">
         <v>2000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AG32" s="3">
         <v>20000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AH32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AI32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AJ32" s="3">
         <v>-5000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AK32" s="3">
         <v>-7000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AL32" s="3">
         <v>-6000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AM32" s="3">
         <v>4800</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AN32" s="3">
         <v>4700</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AO32" s="3">
         <v>-5800</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>996000</v>
+        <v>11600</v>
       </c>
       <c r="E33" s="3">
-        <v>483000</v>
+        <v>-900</v>
       </c>
       <c r="F33" s="3">
-        <v>370000</v>
+        <v>10300</v>
       </c>
       <c r="G33" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="H33" s="3">
+        <v>6600</v>
+      </c>
+      <c r="I33" s="3">
+        <v>9000</v>
+      </c>
+      <c r="J33" s="3">
+        <v>30900</v>
+      </c>
+      <c r="K33" s="3">
         <v>295000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="L33" s="3">
         <v>479000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="M33" s="3">
         <v>368000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="N33" s="3">
         <v>305000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="O33" s="3">
         <v>120000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="P33" s="3">
         <v>-735000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="Q33" s="3">
         <v>241000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="R33" s="3">
         <v>488000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="S33" s="3">
         <v>438000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="T33" s="3">
         <v>726000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="U33" s="3">
         <v>347000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="V33" s="3">
         <v>411000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="W33" s="3">
         <v>538000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="X33" s="3">
         <v>685000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="Y33" s="3">
         <v>882000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="Z33" s="3">
         <v>357000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="AA33" s="3">
         <v>400000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="AB33" s="3">
         <v>1387000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AC33" s="3">
         <v>2277000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AD33" s="3">
         <v>194000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AE33" s="3">
         <v>111000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AF33" s="3">
         <v>-1197000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AG33" s="3">
         <v>-412000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AH33" s="3">
         <v>-94000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AI33" s="3">
         <v>158000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AJ33" s="3">
         <v>-314000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AK33" s="3">
         <v>-11000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AL33" s="3">
         <v>1084000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AM33" s="3">
         <v>69800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AN33" s="3">
         <v>78500</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AO33" s="3">
         <v>65600</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3482,227 +3785,263 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>996000</v>
+        <v>11600</v>
       </c>
       <c r="E35" s="3">
-        <v>483000</v>
+        <v>-900</v>
       </c>
       <c r="F35" s="3">
-        <v>370000</v>
+        <v>10300</v>
       </c>
       <c r="G35" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="H35" s="3">
+        <v>6600</v>
+      </c>
+      <c r="I35" s="3">
+        <v>9000</v>
+      </c>
+      <c r="J35" s="3">
+        <v>30900</v>
+      </c>
+      <c r="K35" s="3">
         <v>295000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="L35" s="3">
         <v>479000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="M35" s="3">
         <v>368000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="N35" s="3">
         <v>305000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="O35" s="3">
         <v>120000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="P35" s="3">
         <v>-735000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="Q35" s="3">
         <v>241000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="R35" s="3">
         <v>488000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="S35" s="3">
         <v>438000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="T35" s="3">
         <v>726000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="U35" s="3">
         <v>347000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="V35" s="3">
         <v>411000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="W35" s="3">
         <v>538000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="X35" s="3">
         <v>685000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="Y35" s="3">
         <v>882000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="Z35" s="3">
         <v>357000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="AA35" s="3">
         <v>400000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="AB35" s="3">
         <v>1387000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AC35" s="3">
         <v>2277000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AD35" s="3">
         <v>194000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AE35" s="3">
         <v>111000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AF35" s="3">
         <v>-1197000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AG35" s="3">
         <v>-412000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AH35" s="3">
         <v>-94000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AI35" s="3">
         <v>158000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AJ35" s="3">
         <v>-314000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AK35" s="3">
         <v>-11000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AL35" s="3">
         <v>1084000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AM35" s="3">
         <v>69800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AN35" s="3">
         <v>78500</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AO35" s="3">
         <v>65600</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="G38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -3740,8 +4079,12 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
+      <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -3779,115 +4122,131 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
+      <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
-        <v>4074000</v>
+        <v>152100</v>
       </c>
       <c r="E41" s="3">
-        <v>4225000</v>
+        <v>89200</v>
       </c>
       <c r="F41" s="3">
-        <v>4036000</v>
+        <v>77700</v>
       </c>
       <c r="G41" s="3">
+        <v>114300</v>
+      </c>
+      <c r="H41" s="3">
+        <v>37800</v>
+      </c>
+      <c r="I41" s="3">
+        <v>46900</v>
+      </c>
+      <c r="J41" s="3">
+        <v>48600</v>
+      </c>
+      <c r="K41" s="3">
         <v>3942000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="L41" s="3">
         <v>4148000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="M41" s="3">
         <v>4261000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="N41" s="3">
         <v>4157000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="O41" s="3">
         <v>4377000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="P41" s="3">
         <v>4440000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="Q41" s="3">
         <v>5240000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="R41" s="3">
         <v>5780000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="S41" s="3">
         <v>5887000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="T41" s="3">
         <v>5280000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="U41" s="3">
         <v>5043000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="V41" s="3">
         <v>5138000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="W41" s="3">
         <v>5672000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="X41" s="3">
         <v>5188000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="Y41" s="3">
         <v>4744000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="Z41" s="3">
         <v>3743000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="AA41" s="3">
         <v>3327000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="AB41" s="3">
         <v>3314000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AC41" s="3">
         <v>2405000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AD41" s="3">
         <v>2153000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AE41" s="3">
         <v>2153000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AF41" s="3">
         <v>1571000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AG41" s="3">
         <v>1697000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AH41" s="3">
         <v>2085000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AI41" s="3">
         <v>2384000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AJ41" s="3">
         <v>2234000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AK41" s="3">
         <v>2025000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AL41" s="3">
         <v>2926000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AM41" s="3">
         <v>600300</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AN41" s="3">
         <v>516300</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AO41" s="3">
         <v>361100</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
@@ -3993,757 +4352,853 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>1363000</v>
+        <v>652500</v>
       </c>
       <c r="E43" s="3">
-        <v>684000</v>
+        <v>368900</v>
       </c>
       <c r="F43" s="3">
-        <v>566000</v>
+        <v>211300</v>
       </c>
       <c r="G43" s="3">
+        <v>197500</v>
+      </c>
+      <c r="H43" s="3">
+        <v>126100</v>
+      </c>
+      <c r="I43" s="3">
+        <v>157400</v>
+      </c>
+      <c r="J43" s="3">
+        <v>140200</v>
+      </c>
+      <c r="K43" s="3">
         <v>654000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="L43" s="3">
         <v>1178000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="M43" s="3">
         <v>561000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="N43" s="3">
         <v>603000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="O43" s="3">
         <v>557000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="P43" s="3">
         <v>554000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="Q43" s="3">
         <v>499000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="R43" s="3">
         <v>577000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="S43" s="3">
         <v>640000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="T43" s="3">
         <v>623000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="U43" s="3">
         <v>600000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="V43" s="3">
         <v>554000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="W43" s="3">
         <v>530000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="X43" s="3">
         <v>558000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="Y43" s="3">
         <v>509000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="Z43" s="3">
         <v>407000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="AA43" s="3">
         <v>371000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="AB43" s="3">
         <v>363000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AC43" s="3">
         <v>311000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AD43" s="3">
         <v>427000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AE43" s="3">
         <v>383000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AF43" s="3">
         <v>248000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AG43" s="3">
         <v>189000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AH43" s="3">
         <v>194000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AI43" s="3">
         <v>173000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AJ43" s="3">
         <v>239000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AK43" s="3">
         <v>224000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AL43" s="3">
         <v>190000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AM43" s="3">
         <v>236800</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AN43" s="3">
         <v>231400</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AO43" s="3">
         <v>223400</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
-        <v>1942000</v>
+        <v>1569900</v>
       </c>
       <c r="E44" s="3">
-        <v>1784000</v>
+        <v>1245500</v>
       </c>
       <c r="F44" s="3">
-        <v>1684000</v>
+        <v>1304600</v>
       </c>
       <c r="G44" s="3">
+        <v>1339600</v>
+      </c>
+      <c r="H44" s="3">
+        <v>1205300</v>
+      </c>
+      <c r="I44" s="3">
+        <v>1295900</v>
+      </c>
+      <c r="J44" s="3">
+        <v>1108200</v>
+      </c>
+      <c r="K44" s="3">
         <v>1805000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="L44" s="3">
         <v>1782000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="M44" s="3">
         <v>1913000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="N44" s="3">
         <v>1868000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="O44" s="3">
         <v>1913000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="P44" s="3">
         <v>1781000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="Q44" s="3">
         <v>1691000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="R44" s="3">
         <v>1699000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="S44" s="3">
         <v>1766000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="T44" s="3">
         <v>1734000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="U44" s="3">
         <v>1821000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="V44" s="3">
         <v>1825000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="W44" s="3">
         <v>1776000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="X44" s="3">
         <v>1878000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="Y44" s="3">
         <v>2111000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="Z44" s="3">
         <v>2160000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="AA44" s="3">
         <v>2159000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="AB44" s="3">
         <v>2289000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AC44" s="3">
         <v>2265000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AD44" s="3">
         <v>1930000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AE44" s="3">
         <v>1966000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AF44" s="3">
         <v>1852000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AG44" s="3">
         <v>1898000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AH44" s="3">
         <v>1940000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AI44" s="3">
         <v>1887000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AJ44" s="3">
         <v>1890000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AK44" s="3">
         <v>2038000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AL44" s="3">
         <v>1901000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AM44" s="3">
         <v>124600</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AN44" s="3">
         <v>119000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AO44" s="3">
         <v>135800</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>103000</v>
+        <v>947700</v>
       </c>
       <c r="E45" s="3">
-        <v>1334000</v>
+        <v>390200</v>
       </c>
       <c r="F45" s="3">
-        <v>916000</v>
+        <v>134500</v>
       </c>
       <c r="G45" s="3">
+        <v>92400</v>
+      </c>
+      <c r="H45" s="3">
+        <v>112300</v>
+      </c>
+      <c r="I45" s="3">
+        <v>136100</v>
+      </c>
+      <c r="J45" s="3">
+        <v>136800</v>
+      </c>
+      <c r="K45" s="3">
         <v>880000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="L45" s="3">
         <v>127000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="M45" s="3">
         <v>684000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="N45" s="3">
         <v>742000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="O45" s="3">
         <v>1691000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="P45" s="3">
         <v>1690000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="Q45" s="3">
         <v>786000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="R45" s="3">
         <v>754000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="S45" s="3">
         <v>722000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="T45" s="3">
         <v>612000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="U45" s="3">
         <v>547000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="V45" s="3">
         <v>522000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="W45" s="3">
         <v>806000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="X45" s="3">
         <v>519000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="Y45" s="3">
         <v>495000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="Z45" s="3">
         <v>609000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="AA45" s="3">
         <v>594000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="AB45" s="3">
         <v>921000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AC45" s="3">
         <v>529000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AD45" s="3">
         <v>333000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AE45" s="3">
         <v>372000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AF45" s="3">
         <v>307000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AG45" s="3">
         <v>319000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AH45" s="3">
         <v>356000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AI45" s="3">
         <v>352000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AJ45" s="3">
         <v>321000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AK45" s="3">
         <v>455000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AL45" s="3">
         <v>486000</v>
       </c>
-      <c r="AI45" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ45" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK45" s="3">
+      <c r="AM45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO45" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
-        <v>7632000</v>
+        <v>3341700</v>
       </c>
       <c r="E46" s="3">
-        <v>8027000</v>
+        <v>2111300</v>
       </c>
       <c r="F46" s="3">
-        <v>7202000</v>
+        <v>1743500</v>
       </c>
       <c r="G46" s="3">
+        <v>1757900</v>
+      </c>
+      <c r="H46" s="3">
+        <v>1489700</v>
+      </c>
+      <c r="I46" s="3">
+        <v>1645500</v>
+      </c>
+      <c r="J46" s="3">
+        <v>1442200</v>
+      </c>
+      <c r="K46" s="3">
         <v>7281000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="L46" s="3">
         <v>7438000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="M46" s="3">
         <v>7419000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="N46" s="3">
         <v>7370000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="O46" s="3">
         <v>8538000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="P46" s="3">
         <v>8465000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="Q46" s="3">
         <v>8216000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="R46" s="3">
         <v>8810000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="S46" s="3">
         <v>9015000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="T46" s="3">
         <v>8249000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="U46" s="3">
         <v>8011000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="V46" s="3">
         <v>8039000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="W46" s="3">
         <v>8784000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="X46" s="3">
         <v>8143000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="Y46" s="3">
         <v>7859000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="Z46" s="3">
         <v>6919000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="AA46" s="3">
         <v>6451000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="AB46" s="3">
         <v>6887000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AC46" s="3">
         <v>5510000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AD46" s="3">
         <v>4843000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AE46" s="3">
         <v>4874000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AF46" s="3">
         <v>3978000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AG46" s="3">
         <v>4103000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AH46" s="3">
         <v>4575000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AI46" s="3">
         <v>4796000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AJ46" s="3">
         <v>4684000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AK46" s="3">
         <v>4742000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AL46" s="3">
         <v>5503000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AM46" s="3">
         <v>961600</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AN46" s="3">
         <v>866800</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AO46" s="3">
         <v>720300</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
-        <v>4154000</v>
+        <v>38400</v>
       </c>
       <c r="E47" s="3">
-        <v>4275000</v>
+        <v>31700</v>
       </c>
       <c r="F47" s="3">
-        <v>4262000</v>
+        <v>33000</v>
       </c>
       <c r="G47" s="3">
+        <v>38400</v>
+      </c>
+      <c r="H47" s="3">
+        <v>48500</v>
+      </c>
+      <c r="I47" s="3">
+        <v>51000</v>
+      </c>
+      <c r="J47" s="3">
+        <v>50500</v>
+      </c>
+      <c r="K47" s="3">
         <v>4178000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="L47" s="3">
         <v>4264000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="M47" s="3">
         <v>3998000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="N47" s="3">
         <v>4004000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="O47" s="3">
         <v>3969000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="P47" s="3">
         <v>3983000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="Q47" s="3">
         <v>4064000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="R47" s="3">
         <v>4113000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="S47" s="3">
         <v>4334000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="T47" s="3">
         <v>4594000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="U47" s="3">
         <v>4762000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="V47" s="3">
         <v>4715000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="W47" s="3">
         <v>4646000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="X47" s="3">
         <v>4670000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="Y47" s="3">
         <v>4643000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="Z47" s="3">
         <v>4587000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="AA47" s="3">
         <v>4556000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="AB47" s="3">
         <v>4527000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AC47" s="3">
         <v>4474000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AD47" s="3">
         <v>4459000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AE47" s="3">
         <v>4444000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AF47" s="3">
         <v>1234000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AG47" s="3">
         <v>1233000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AH47" s="3">
         <v>1214000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AI47" s="3">
         <v>1233000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AJ47" s="3">
         <v>1213000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AK47" s="3">
         <v>1243000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AL47" s="3">
         <v>1218000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AM47" s="3">
         <v>1446800</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AN47" s="3">
         <v>1448600</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AO47" s="3">
         <v>1479500</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
-        <v>28559000</v>
+        <v>67200</v>
       </c>
       <c r="E48" s="3">
-        <v>27288000</v>
+        <v>67000</v>
       </c>
       <c r="F48" s="3">
-        <v>26994000</v>
+        <v>68400</v>
       </c>
       <c r="G48" s="3">
+        <v>53600</v>
+      </c>
+      <c r="H48" s="3">
+        <v>32400</v>
+      </c>
+      <c r="I48" s="3">
+        <v>29000</v>
+      </c>
+      <c r="J48" s="3">
+        <v>29800</v>
+      </c>
+      <c r="K48" s="3">
         <v>26648000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="L48" s="3">
         <v>26416000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="M48" s="3">
         <v>26621000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="N48" s="3">
         <v>26311000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="O48" s="3">
         <v>26084000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="P48" s="3">
         <v>25821000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="Q48" s="3">
         <v>25329000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="R48" s="3">
         <v>25202000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="S48" s="3">
         <v>25153000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="T48" s="3">
         <v>24954000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="U48" s="3">
         <v>24747000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="V48" s="3">
         <v>24755000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="W48" s="3">
         <v>24628000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="X48" s="3">
         <v>24628000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="Y48" s="3">
         <v>24698000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="Z48" s="3">
         <v>24727000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="AA48" s="3">
         <v>24809000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="AB48" s="3">
         <v>24141000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AC48" s="3">
         <v>24758000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AD48" s="3">
         <v>16890000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AE48" s="3">
         <v>16891000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AF48" s="3">
         <v>12826000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AG48" s="3">
         <v>13226000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AH48" s="3">
         <v>13727000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AI48" s="3">
         <v>13755000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AJ48" s="3">
         <v>13806000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AK48" s="3">
         <v>13961000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AL48" s="3">
         <v>13943000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AM48" s="3">
         <v>1564000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AN48" s="3">
         <v>1560900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AO48" s="3">
         <v>1567300</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
-        <v>3245000</v>
+        <v>357500</v>
       </c>
       <c r="E49" s="3">
+        <v>360800</v>
+      </c>
+      <c r="F49" s="3">
+        <v>366000</v>
+      </c>
+      <c r="G49" s="3">
+        <v>327900</v>
+      </c>
+      <c r="H49" s="3">
+        <v>294000</v>
+      </c>
+      <c r="I49" s="3">
+        <v>297700</v>
+      </c>
+      <c r="J49" s="3">
+        <v>301600</v>
+      </c>
+      <c r="K49" s="3">
         <v>3729000</v>
-      </c>
-      <c r="F49" s="3">
-        <v>3729000</v>
-      </c>
-      <c r="G49" s="3">
-        <v>3729000</v>
-      </c>
-      <c r="H49" s="3">
-        <v>3730000</v>
-      </c>
-      <c r="I49" s="3">
-        <v>3730000</v>
-      </c>
-      <c r="J49" s="3">
-        <v>3730000</v>
-      </c>
-      <c r="K49" s="3">
-        <v>3730000</v>
       </c>
       <c r="L49" s="3">
         <v>3730000</v>
       </c>
       <c r="M49" s="3">
+        <v>3730000</v>
+      </c>
+      <c r="N49" s="3">
+        <v>3730000</v>
+      </c>
+      <c r="O49" s="3">
+        <v>3730000</v>
+      </c>
+      <c r="P49" s="3">
+        <v>3730000</v>
+      </c>
+      <c r="Q49" s="3">
         <v>4918000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="R49" s="3">
         <v>4918000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="S49" s="3">
         <v>4918000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="T49" s="3">
         <v>4919000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="U49" s="3">
         <v>4920000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="V49" s="3">
         <v>4927000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="W49" s="3">
         <v>4937000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="X49" s="3">
         <v>4938000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="Y49" s="3">
         <v>4939000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="Z49" s="3">
         <v>4983000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="AA49" s="3">
         <v>4999000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="AB49" s="3">
         <v>4995000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AC49" s="3">
         <v>5025000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AD49" s="3">
         <v>3064000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AE49" s="3">
         <v>3037000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AF49" s="3">
         <v>1403000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AG49" s="3">
         <v>1559000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AH49" s="3">
         <v>1560000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AI49" s="3">
         <v>1585000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AJ49" s="3">
         <v>1585000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AK49" s="3">
         <v>1556000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AL49" s="3">
         <v>1586000</v>
       </c>
-      <c r="AI49" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ49" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK49" s="3">
+      <c r="AM49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO49" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -4849,8 +5304,20 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -4956,115 +5423,139 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>3819000</v>
+        <v>7100</v>
       </c>
       <c r="E52" s="3">
-        <v>4035000</v>
+        <v>8600</v>
       </c>
       <c r="F52" s="3">
-        <v>4032000</v>
+        <v>4600</v>
       </c>
       <c r="G52" s="3">
+        <v>5700</v>
+      </c>
+      <c r="H52" s="3">
+        <v>4700</v>
+      </c>
+      <c r="I52" s="3">
+        <v>5700</v>
+      </c>
+      <c r="J52" s="3">
+        <v>3800</v>
+      </c>
+      <c r="K52" s="3">
         <v>4007000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="L52" s="3">
         <v>3776000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="M52" s="3">
         <v>3800000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="N52" s="3">
         <v>3852000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="O52" s="3">
         <v>3812000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="P52" s="3">
         <v>3966000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="Q52" s="3">
         <v>3915000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="R52" s="3">
         <v>3799000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="S52" s="3">
         <v>3886000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="T52" s="3">
         <v>4174000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="U52" s="3">
         <v>4194000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="V52" s="3">
         <v>4092000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="W52" s="3">
         <v>3853000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="X52" s="3">
         <v>4127000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="Y52" s="3">
         <v>3977000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="Z52" s="3">
         <v>3964000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="AA52" s="3">
         <v>4124000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="AB52" s="3">
         <v>3842000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AC52" s="3">
         <v>4100000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AD52" s="3">
         <v>3346000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AE52" s="3">
         <v>3383000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AF52" s="3">
         <v>3190000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AG52" s="3">
         <v>3997000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AH52" s="3">
         <v>4046000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AI52" s="3">
         <v>4027000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AJ52" s="3">
         <v>4020000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AK52" s="3">
         <v>3570000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AL52" s="3">
         <v>3557000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AM52" s="3">
         <v>163600</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AN52" s="3">
         <v>164700</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AO52" s="3">
         <v>151000</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -5170,115 +5661,139 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
-        <v>47626000</v>
+        <v>3811900</v>
       </c>
       <c r="E54" s="3">
-        <v>47354000</v>
+        <v>2579400</v>
       </c>
       <c r="F54" s="3">
-        <v>46219000</v>
+        <v>2215400</v>
       </c>
       <c r="G54" s="3">
+        <v>2183500</v>
+      </c>
+      <c r="H54" s="3">
+        <v>1869300</v>
+      </c>
+      <c r="I54" s="3">
+        <v>2029000</v>
+      </c>
+      <c r="J54" s="3">
+        <v>1827800</v>
+      </c>
+      <c r="K54" s="3">
         <v>45843000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="L54" s="3">
         <v>45811000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="M54" s="3">
         <v>45595000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="N54" s="3">
         <v>45286000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="O54" s="3">
         <v>46152000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="P54" s="3">
         <v>45965000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="Q54" s="3">
         <v>46442000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="R54" s="3">
         <v>46842000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="S54" s="3">
         <v>47306000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="T54" s="3">
         <v>46890000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="U54" s="3">
         <v>46634000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="V54" s="3">
         <v>46528000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="W54" s="3">
         <v>46848000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="X54" s="3">
         <v>46506000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="Y54" s="3">
         <v>46116000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="Z54" s="3">
         <v>45180000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="AA54" s="3">
         <v>44939000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="AB54" s="3">
         <v>44392000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AC54" s="3">
         <v>43867000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AD54" s="3">
         <v>32602000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AE54" s="3">
         <v>32629000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AF54" s="3">
         <v>22631000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AG54" s="3">
         <v>24118000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AH54" s="3">
         <v>25122000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AI54" s="3">
         <v>25396000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AJ54" s="3">
         <v>25308000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AK54" s="3">
         <v>25072000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AL54" s="3">
         <v>25807000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AM54" s="3">
         <v>4136000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AN54" s="3">
         <v>4041000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AO54" s="3">
         <v>3918100</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -5316,8 +5831,12 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
+      <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -5355,650 +5874,726 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
+      <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
-        <v>655000</v>
+        <v>76900</v>
       </c>
       <c r="E57" s="3">
-        <v>1479000</v>
+        <v>69100</v>
       </c>
       <c r="F57" s="3">
-        <v>1386000</v>
+        <v>12800</v>
       </c>
       <c r="G57" s="3">
+        <v>18600</v>
+      </c>
+      <c r="H57" s="3">
+        <v>7700</v>
+      </c>
+      <c r="I57" s="3">
+        <v>5400</v>
+      </c>
+      <c r="J57" s="3">
+        <v>12000</v>
+      </c>
+      <c r="K57" s="3">
         <v>1360000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="L57" s="3">
         <v>678000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="M57" s="3">
         <v>1584000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="N57" s="3">
         <v>1525000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="O57" s="3">
         <v>1504000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="P57" s="3">
         <v>1556000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="Q57" s="3">
         <v>1571000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="R57" s="3">
         <v>1537000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="S57" s="3">
         <v>1525000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="T57" s="3">
         <v>1448000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="U57" s="3">
         <v>1444000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="V57" s="3">
         <v>1157000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="W57" s="3">
         <v>1168000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="X57" s="3">
         <v>1458000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="Y57" s="3">
         <v>1032000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="Z57" s="3">
         <v>1072000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="AA57" s="3">
         <v>1140000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="AB57" s="3">
         <v>1155000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AC57" s="3">
         <v>1337000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AD57" s="3">
         <v>1064000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AE57" s="3">
         <v>1213000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AF57" s="3">
         <v>1101000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AG57" s="3">
         <v>1125000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AH57" s="3">
         <v>944000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AI57" s="3">
         <v>1046000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AJ57" s="3">
         <v>1059000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AK57" s="3">
         <v>1118000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AL57" s="3">
         <v>1044000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AM57" s="3">
         <v>120000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AN57" s="3">
         <v>127400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AO57" s="3">
         <v>136700</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
-        <v>84000</v>
+        <v>599400</v>
       </c>
       <c r="E58" s="3">
-        <v>13000</v>
+        <v>445100</v>
       </c>
       <c r="F58" s="3">
-        <v>11000</v>
+        <v>540100</v>
       </c>
       <c r="G58" s="3">
-        <v>12000</v>
+        <v>605800</v>
       </c>
       <c r="H58" s="3">
-        <v>43000</v>
+        <v>592300</v>
       </c>
       <c r="I58" s="3">
-        <v>8000</v>
+        <v>590300</v>
       </c>
       <c r="J58" s="3">
-        <v>13000</v>
+        <v>558100</v>
       </c>
       <c r="K58" s="3">
         <v>12000</v>
       </c>
       <c r="L58" s="3">
-        <v>13000</v>
+        <v>43000</v>
       </c>
       <c r="M58" s="3">
-        <v>12000</v>
+        <v>8000</v>
       </c>
       <c r="N58" s="3">
         <v>13000</v>
       </c>
       <c r="O58" s="3">
+        <v>12000</v>
+      </c>
+      <c r="P58" s="3">
+        <v>13000</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>12000</v>
+      </c>
+      <c r="R58" s="3">
+        <v>13000</v>
+      </c>
+      <c r="S58" s="3">
         <v>14000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="T58" s="3">
         <v>15000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="U58" s="3">
         <v>15000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="V58" s="3">
         <v>15000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="W58" s="3">
         <v>13000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="X58" s="3">
         <v>20000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="Y58" s="3">
         <v>21000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="Z58" s="3">
         <v>26000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="AA58" s="3">
         <v>29000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="AB58" s="3">
         <v>375000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AC58" s="3">
         <v>66000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AD58" s="3">
         <v>303000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AE58" s="3">
         <v>308000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AF58" s="3">
         <v>43000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AG58" s="3">
         <v>49000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AH58" s="3">
         <v>680000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AI58" s="3">
         <v>57000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AJ58" s="3">
         <v>59000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AK58" s="3">
         <v>63000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AL58" s="3">
         <v>116000</v>
       </c>
-      <c r="AI58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK58" s="3">
+      <c r="AM58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO58" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>891000</v>
+        <v>2052900</v>
       </c>
       <c r="E59" s="3">
-        <v>1537000</v>
+        <v>1006300</v>
       </c>
       <c r="F59" s="3">
-        <v>995000</v>
+        <v>537000</v>
       </c>
       <c r="G59" s="3">
+        <v>480200</v>
+      </c>
+      <c r="H59" s="3">
+        <v>332500</v>
+      </c>
+      <c r="I59" s="3">
+        <v>378900</v>
+      </c>
+      <c r="J59" s="3">
+        <v>296900</v>
+      </c>
+      <c r="K59" s="3">
         <v>823000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="L59" s="3">
         <v>760000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="M59" s="3">
         <v>826000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="N59" s="3">
         <v>732000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="O59" s="3">
         <v>1690000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="P59" s="3">
         <v>1551000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="Q59" s="3">
         <v>605000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="R59" s="3">
         <v>680000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="S59" s="3">
         <v>708000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="T59" s="3">
         <v>623000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="U59" s="3">
         <v>521000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="V59" s="3">
         <v>626000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="W59" s="3">
         <v>1150000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="X59" s="3">
         <v>742000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="Y59" s="3">
         <v>698000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="Z59" s="3">
         <v>713000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="AA59" s="3">
         <v>801000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="AB59" s="3">
         <v>846000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AC59" s="3">
         <v>441000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AD59" s="3">
         <v>415000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AE59" s="3">
         <v>463000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AF59" s="3">
         <v>524000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AG59" s="3">
         <v>375000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AH59" s="3">
         <v>536000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AI59" s="3">
         <v>595000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AJ59" s="3">
         <v>629000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AK59" s="3">
         <v>557000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AL59" s="3">
         <v>386000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AM59" s="3">
         <v>71100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AN59" s="3">
         <v>61000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AO59" s="3">
         <v>34700</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
-        <v>2642000</v>
+        <v>2754200</v>
       </c>
       <c r="E60" s="3">
-        <v>3029000</v>
+        <v>1543100</v>
       </c>
       <c r="F60" s="3">
-        <v>2392000</v>
+        <v>1114100</v>
       </c>
       <c r="G60" s="3">
+        <v>1129000</v>
+      </c>
+      <c r="H60" s="3">
+        <v>944600</v>
+      </c>
+      <c r="I60" s="3">
+        <v>989600</v>
+      </c>
+      <c r="J60" s="3">
+        <v>883800</v>
+      </c>
+      <c r="K60" s="3">
         <v>2195000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="L60" s="3">
         <v>2356000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="M60" s="3">
         <v>2418000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="N60" s="3">
         <v>2270000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="O60" s="3">
         <v>3206000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="P60" s="3">
         <v>3120000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="Q60" s="3">
         <v>2188000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="R60" s="3">
         <v>2230000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="S60" s="3">
         <v>2247000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="T60" s="3">
         <v>2086000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="U60" s="3">
         <v>1980000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="V60" s="3">
         <v>1798000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="W60" s="3">
         <v>2331000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="X60" s="3">
         <v>2220000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="Y60" s="3">
         <v>1751000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="Z60" s="3">
         <v>1811000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="AA60" s="3">
         <v>1970000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="AB60" s="3">
         <v>2376000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AC60" s="3">
         <v>1844000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AD60" s="3">
         <v>1782000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AE60" s="3">
         <v>1984000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AF60" s="3">
         <v>1668000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AG60" s="3">
         <v>1549000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AH60" s="3">
         <v>2160000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AI60" s="3">
         <v>1698000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AJ60" s="3">
         <v>1747000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AK60" s="3">
         <v>1738000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AL60" s="3">
         <v>1546000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AM60" s="3">
         <v>191100</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AN60" s="3">
         <v>188400</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AO60" s="3">
         <v>171400</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
-        <v>5172000</v>
+        <v>319400</v>
       </c>
       <c r="E61" s="3">
-        <v>4712000</v>
+        <v>310500</v>
       </c>
       <c r="F61" s="3">
+        <v>366600</v>
+      </c>
+      <c r="G61" s="3">
+        <v>334800</v>
+      </c>
+      <c r="H61" s="3">
+        <v>235500</v>
+      </c>
+      <c r="I61" s="3">
+        <v>348200</v>
+      </c>
+      <c r="J61" s="3">
+        <v>249000</v>
+      </c>
+      <c r="K61" s="3">
         <v>4713000</v>
       </c>
-      <c r="G61" s="3">
-        <v>4713000</v>
-      </c>
-      <c r="H61" s="3">
+      <c r="L61" s="3">
         <v>5180000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="M61" s="3">
         <v>4767000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="N61" s="3">
         <v>4761000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="O61" s="3">
         <v>4765000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="P61" s="3">
         <v>4769000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="Q61" s="3">
         <v>5083000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="R61" s="3">
         <v>5131000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="S61" s="3">
         <v>5130000</v>
-      </c>
-      <c r="P61" s="3">
-        <v>5135000</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>5139000</v>
-      </c>
-      <c r="R61" s="3">
-        <v>5137000</v>
-      </c>
-      <c r="S61" s="3">
-        <v>5140000</v>
       </c>
       <c r="T61" s="3">
         <v>5135000</v>
       </c>
       <c r="U61" s="3">
+        <v>5139000</v>
+      </c>
+      <c r="V61" s="3">
+        <v>5137000</v>
+      </c>
+      <c r="W61" s="3">
         <v>5140000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
+        <v>5135000</v>
+      </c>
+      <c r="Y61" s="3">
+        <v>5140000</v>
+      </c>
+      <c r="Z61" s="3">
         <v>5142000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="AA61" s="3">
         <v>5150000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="AB61" s="3">
         <v>5161000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AC61" s="3">
         <v>5494000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AD61" s="3">
         <v>5504000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AE61" s="3">
         <v>5499000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AF61" s="3">
         <v>5695000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AG61" s="3">
         <v>5696000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AH61" s="3">
         <v>5712000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AI61" s="3">
         <v>6344000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AJ61" s="3">
         <v>6364000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AK61" s="3">
         <v>6384000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AL61" s="3">
         <v>7328000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AM61" s="3">
         <v>2800</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AN61" s="3">
         <v>2800</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AO61" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>2028000</v>
+        <v>11100</v>
       </c>
       <c r="E62" s="3">
-        <v>3237000</v>
+        <v>10500</v>
       </c>
       <c r="F62" s="3">
-        <v>3148000</v>
+        <v>13700</v>
       </c>
       <c r="G62" s="3">
+        <v>2600</v>
+      </c>
+      <c r="H62" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I62" s="3">
+        <v>4200</v>
+      </c>
+      <c r="J62" s="3">
+        <v>11000</v>
+      </c>
+      <c r="K62" s="3">
         <v>3246000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="L62" s="3">
         <v>2202000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="M62" s="3">
         <v>3345000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="N62" s="3">
         <v>3484000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="O62" s="3">
         <v>3593000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="P62" s="3">
         <v>6787000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="Q62" s="3">
         <v>6864000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="R62" s="3">
         <v>6947000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="S62" s="3">
         <v>7303000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="T62" s="3">
         <v>7362000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="U62" s="3">
         <v>7425000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="V62" s="3">
         <v>7419000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="W62" s="3">
         <v>7298000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="X62" s="3">
         <v>7441000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="Y62" s="3">
         <v>7575000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="Z62" s="3">
         <v>7481000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="AA62" s="3">
         <v>7464000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="AB62" s="3">
         <v>7028000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AC62" s="3">
         <v>8129000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AD62" s="3">
         <v>6849000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AE62" s="3">
         <v>6844000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AF62" s="3">
         <v>5883000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AG62" s="3">
         <v>6187000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AH62" s="3">
         <v>6144000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AI62" s="3">
         <v>6088000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AJ62" s="3">
         <v>6130000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AK62" s="3">
         <v>5328000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AL62" s="3">
         <v>5248000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AM62" s="3">
         <v>101700</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AN62" s="3">
         <v>97800</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AO62" s="3">
         <v>88900</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -6104,8 +6699,20 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6211,8 +6818,20 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -6318,115 +6937,139 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
-        <v>14370000</v>
+        <v>3103100</v>
       </c>
       <c r="E66" s="3">
-        <v>14457000</v>
+        <v>1882300</v>
       </c>
       <c r="F66" s="3">
-        <v>13724000</v>
+        <v>1512800</v>
       </c>
       <c r="G66" s="3">
+        <v>1486700</v>
+      </c>
+      <c r="H66" s="3">
+        <v>1203500</v>
+      </c>
+      <c r="I66" s="3">
+        <v>1364300</v>
+      </c>
+      <c r="J66" s="3">
+        <v>1166000</v>
+      </c>
+      <c r="K66" s="3">
         <v>13626000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="L66" s="3">
         <v>13809000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="M66" s="3">
         <v>13897000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="N66" s="3">
         <v>13801000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="O66" s="3">
         <v>14834000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="P66" s="3">
         <v>23194000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="Q66" s="3">
         <v>22578000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="R66" s="3">
         <v>22731000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="S66" s="3">
         <v>23131000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="T66" s="3">
         <v>23033000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="U66" s="3">
         <v>23016000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="V66" s="3">
         <v>22839000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="W66" s="3">
         <v>23174000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="X66" s="3">
         <v>23165000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="Y66" s="3">
         <v>23317000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="Z66" s="3">
         <v>23148000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="AA66" s="3">
         <v>23252000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="AB66" s="3">
         <v>22960000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AC66" s="3">
         <v>23718000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AD66" s="3">
         <v>16856000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AE66" s="3">
         <v>17031000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AF66" s="3">
         <v>15038000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AG66" s="3">
         <v>15211000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AH66" s="3">
         <v>15766000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AI66" s="3">
         <v>15917000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AJ66" s="3">
         <v>16022000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AK66" s="3">
         <v>15458000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AL66" s="3">
         <v>16165000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AM66" s="3">
         <v>559400</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AN66" s="3">
         <v>542300</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AO66" s="3">
         <v>502400</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -6464,8 +7107,12 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
+      <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -6571,8 +7218,20 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -6678,8 +7337,20 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -6785,8 +7456,20 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -6892,115 +7575,139 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
-        <v>-5269000</v>
+        <v>464800</v>
       </c>
       <c r="E72" s="3">
-        <v>-6092000</v>
+        <v>458100</v>
       </c>
       <c r="F72" s="3">
-        <v>-6400000</v>
+        <v>464100</v>
       </c>
       <c r="G72" s="3">
+        <v>458700</v>
+      </c>
+      <c r="H72" s="3">
+        <v>473100</v>
+      </c>
+      <c r="I72" s="3">
+        <v>466600</v>
+      </c>
+      <c r="J72" s="3">
+        <v>466800</v>
+      </c>
+      <c r="K72" s="3">
         <v>-6594000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="L72" s="3">
         <v>-6713000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="M72" s="3">
         <v>-7016000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="N72" s="3">
         <v>-7208000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="O72" s="3">
         <v>-7338000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="P72" s="3">
         <v>-7282000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="Q72" s="3">
         <v>-6284000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="R72" s="3">
         <v>-6173000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="S72" s="3">
         <v>-6306000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="T72" s="3">
         <v>-6566000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="U72" s="3">
         <v>-7132000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="V72" s="3">
         <v>-7320000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="W72" s="3">
         <v>-7571000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="X72" s="3">
         <v>-7949000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="Y72" s="3">
         <v>-8474000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="Z72" s="3">
         <v>-9214000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="AA72" s="3">
         <v>-9446000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="AB72" s="3">
         <v>-9722000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AC72" s="3">
         <v>-11020000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AD72" s="3">
         <v>-13227000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AE72" s="3">
         <v>-13351000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AF72" s="3">
         <v>-13453000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AG72" s="3">
         <v>-12148000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AH72" s="3">
         <v>-11701000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AI72" s="3">
         <v>-11572000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AJ72" s="3">
         <v>-11759000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AK72" s="3">
         <v>-11428000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AL72" s="3">
         <v>-11382000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AM72" s="3">
         <v>2014900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AN72" s="3">
         <v>1956700</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AO72" s="3">
         <v>1874200</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -7106,8 +7813,20 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -7213,8 +7932,20 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -7320,115 +8051,139 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
-        <v>24290000</v>
+        <v>653800</v>
       </c>
       <c r="E76" s="3">
-        <v>23831000</v>
+        <v>644000</v>
       </c>
       <c r="F76" s="3">
-        <v>23616000</v>
+        <v>649500</v>
       </c>
       <c r="G76" s="3">
+        <v>643600</v>
+      </c>
+      <c r="H76" s="3">
+        <v>612700</v>
+      </c>
+      <c r="I76" s="3">
+        <v>611100</v>
+      </c>
+      <c r="J76" s="3">
+        <v>607600</v>
+      </c>
+      <c r="K76" s="3">
         <v>23463000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="L76" s="3">
         <v>23341000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="M76" s="3">
         <v>23020000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="N76" s="3">
         <v>22839000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="O76" s="3">
         <v>22713000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="P76" s="3">
         <v>22771000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="Q76" s="3">
         <v>23864000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="R76" s="3">
         <v>24111000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="S76" s="3">
         <v>24175000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="T76" s="3">
         <v>23857000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="U76" s="3">
         <v>23618000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="V76" s="3">
         <v>23689000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="W76" s="3">
         <v>23674000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="X76" s="3">
         <v>23341000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="Y76" s="3">
         <v>22799000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="Z76" s="3">
         <v>22032000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="AA76" s="3">
         <v>21687000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="AB76" s="3">
         <v>21432000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AC76" s="3">
         <v>20149000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AD76" s="3">
         <v>15746000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AE76" s="3">
         <v>15598000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AF76" s="3">
         <v>7593000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AG76" s="3">
         <v>8907000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AH76" s="3">
         <v>9356000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AI76" s="3">
         <v>9479000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AJ76" s="3">
         <v>9286000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AK76" s="3">
         <v>9614000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AL76" s="3">
         <v>9642000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AM76" s="3">
         <v>3576600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AN76" s="3">
         <v>3498700</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AO76" s="3">
         <v>3415700</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -7534,227 +8289,263 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="G80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>996000</v>
+        <v>11600</v>
       </c>
       <c r="E81" s="3">
-        <v>483000</v>
+        <v>-900</v>
       </c>
       <c r="F81" s="3">
-        <v>370000</v>
+        <v>10300</v>
       </c>
       <c r="G81" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="H81" s="3">
+        <v>6600</v>
+      </c>
+      <c r="I81" s="3">
+        <v>9000</v>
+      </c>
+      <c r="J81" s="3">
+        <v>30900</v>
+      </c>
+      <c r="K81" s="3">
         <v>295000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="L81" s="3">
         <v>479000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="M81" s="3">
         <v>368000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="N81" s="3">
         <v>305000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="O81" s="3">
         <v>120000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="P81" s="3">
         <v>-735000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="Q81" s="3">
         <v>241000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="R81" s="3">
         <v>488000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="S81" s="3">
         <v>438000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="T81" s="3">
         <v>726000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="U81" s="3">
         <v>347000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="V81" s="3">
         <v>411000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="W81" s="3">
         <v>538000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="X81" s="3">
         <v>685000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="Y81" s="3">
         <v>882000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="Z81" s="3">
         <v>357000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="AA81" s="3">
         <v>400000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="AB81" s="3">
         <v>1387000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AC81" s="3">
         <v>2277000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AD81" s="3">
         <v>194000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AE81" s="3">
         <v>111000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AF81" s="3">
         <v>-1197000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AG81" s="3">
         <v>-412000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AH81" s="3">
         <v>-94000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AI81" s="3">
         <v>158000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AJ81" s="3">
         <v>-314000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AK81" s="3">
         <v>-11000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AL81" s="3">
         <v>1084000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AM81" s="3">
         <v>69800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AN81" s="3">
         <v>78500</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AO81" s="3">
         <v>65600</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -7792,37 +8583,41 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
+      <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>564000</v>
+        <v>800</v>
       </c>
       <c r="E83" s="3">
-        <v>504000</v>
+        <v>800</v>
       </c>
       <c r="F83" s="3">
-        <v>480000</v>
+        <v>800</v>
       </c>
       <c r="G83" s="3">
+        <v>800</v>
+      </c>
+      <c r="H83" s="3">
+        <v>600</v>
+      </c>
+      <c r="I83" s="3">
+        <v>600</v>
+      </c>
+      <c r="J83" s="3">
+        <v>600</v>
+      </c>
+      <c r="K83" s="3">
         <v>495000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="L83" s="3">
         <v>603000</v>
-      </c>
-      <c r="I83" s="3">
-        <v>457000</v>
-      </c>
-      <c r="J83" s="3">
-        <v>476000</v>
-      </c>
-      <c r="K83" s="3">
-        <v>460000</v>
-      </c>
-      <c r="L83" s="3">
-        <v>604000</v>
       </c>
       <c r="M83" s="3">
         <v>457000</v>
@@ -7834,73 +8629,85 @@
         <v>460000</v>
       </c>
       <c r="P83" s="3">
+        <v>604000</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>457000</v>
+      </c>
+      <c r="R83" s="3">
+        <v>476000</v>
+      </c>
+      <c r="S83" s="3">
+        <v>460000</v>
+      </c>
+      <c r="T83" s="3">
         <v>557000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="U83" s="3">
         <v>538000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="V83" s="3">
         <v>500000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="W83" s="3">
         <v>507000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="X83" s="3">
         <v>544000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="Y83" s="3">
         <v>574000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="Z83" s="3">
         <v>566000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="AA83" s="3">
         <v>524000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="AB83" s="3">
         <v>572000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AC83" s="3">
         <v>559000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AD83" s="3">
         <v>466000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AE83" s="3">
         <v>435000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AF83" s="3">
         <v>441000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AG83" s="3">
         <v>363000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AH83" s="3">
         <v>328000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AI83" s="3">
         <v>325000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AJ83" s="3">
         <v>434000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AK83" s="3">
         <v>390000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AL83" s="3">
         <v>409000</v>
       </c>
-      <c r="AI83" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ83" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK83" s="3">
+      <c r="AM83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO83" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -8006,8 +8813,20 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -8113,8 +8932,20 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -8220,8 +9051,20 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -8327,8 +9170,20 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -8434,115 +9289,139 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
-        <v>1392000</v>
+        <v>-42600</v>
       </c>
       <c r="E89" s="3">
-        <v>1180000</v>
+        <v>195400</v>
       </c>
       <c r="F89" s="3">
-        <v>1159000</v>
+        <v>67000</v>
       </c>
       <c r="G89" s="3">
+        <v>102800</v>
+      </c>
+      <c r="H89" s="3">
+        <v>110100</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-127500</v>
+      </c>
+      <c r="J89" s="3">
+        <v>82900</v>
+      </c>
+      <c r="K89" s="3">
         <v>760000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="L89" s="3">
         <v>997000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="M89" s="3">
         <v>1127000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="N89" s="3">
         <v>832000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="O89" s="3">
         <v>776000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="P89" s="3">
         <v>795000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="Q89" s="3">
         <v>758000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="R89" s="3">
         <v>924000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="S89" s="3">
         <v>1004000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="T89" s="3">
         <v>1387000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="U89" s="3">
         <v>1050000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="V89" s="3">
         <v>639000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="W89" s="3">
         <v>1302000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="X89" s="3">
         <v>1638000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="Y89" s="3">
         <v>1859000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="Z89" s="3">
         <v>1031000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="AA89" s="3">
         <v>889000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="AB89" s="3">
         <v>875000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AC89" s="3">
         <v>1004000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AD89" s="3">
         <v>434000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AE89" s="3">
         <v>520000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AF89" s="3">
         <v>411000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AG89" s="3">
         <v>706000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AH89" s="3">
         <v>141000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AI89" s="3">
         <v>507000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AJ89" s="3">
         <v>590000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AK89" s="3">
         <v>532000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AL89" s="3">
         <v>448000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AM89" s="3">
         <v>133100</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AN89" s="3">
         <v>204700</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AO89" s="3">
         <v>119300</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -8580,115 +9459,131 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
+      <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F91" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="G91" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="K91" s="3">
+        <v>-728000</v>
+      </c>
+      <c r="L91" s="3">
+        <v>-861000</v>
+      </c>
+      <c r="M91" s="3">
+        <v>-768000</v>
+      </c>
+      <c r="N91" s="3">
+        <v>-769000</v>
+      </c>
+      <c r="O91" s="3">
+        <v>-688000</v>
+      </c>
+      <c r="P91" s="3">
         <v>-891000</v>
       </c>
-      <c r="E91" s="3">
-        <v>-736000</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-819000</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-728000</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-861000</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-768000</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-769000</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-688000</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-891000</v>
-      </c>
-      <c r="M91" s="3">
+      <c r="Q91" s="3">
         <v>-792000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="R91" s="3">
         <v>-755000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="S91" s="3">
         <v>-611000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="T91" s="3">
         <v>-669000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="U91" s="3">
         <v>-569000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="V91" s="3">
         <v>-658000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="W91" s="3">
         <v>-539000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="X91" s="3">
         <v>-546000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="Y91" s="3">
         <v>-548000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="Z91" s="3">
         <v>-509000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="AA91" s="3">
         <v>-451000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="AB91" s="3">
         <v>-446000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AC91" s="3">
         <v>-502000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AD91" s="3">
         <v>-379000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AE91" s="3">
         <v>-374000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AF91" s="3">
         <v>-374000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AG91" s="3">
         <v>-387000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AH91" s="3">
         <v>-313000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AI91" s="3">
         <v>-326000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AJ91" s="3">
         <v>-350000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AK91" s="3">
         <v>-307000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AL91" s="3">
         <v>-405000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AM91" s="3">
         <v>-41300</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AN91" s="3">
         <v>-50300</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AO91" s="3">
         <v>-32000</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -8794,8 +9689,20 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -8901,115 +9808,139 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
-        <v>-778000</v>
+        <v>-28100</v>
       </c>
       <c r="E94" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="F94" s="3">
+        <v>-61200</v>
+      </c>
+      <c r="G94" s="3">
+        <v>-54000</v>
+      </c>
+      <c r="H94" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="I94" s="3">
+        <v>15500</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="K94" s="3">
+        <v>-680000</v>
+      </c>
+      <c r="L94" s="3">
+        <v>-766000</v>
+      </c>
+      <c r="M94" s="3">
+        <v>-689000</v>
+      </c>
+      <c r="N94" s="3">
+        <v>-743000</v>
+      </c>
+      <c r="O94" s="3">
+        <v>-618000</v>
+      </c>
+      <c r="P94" s="3">
+        <v>-780000</v>
+      </c>
+      <c r="Q94" s="3">
+        <v>-639000</v>
+      </c>
+      <c r="R94" s="3">
+        <v>-301000</v>
+      </c>
+      <c r="S94" s="3">
+        <v>9000</v>
+      </c>
+      <c r="T94" s="3">
+        <v>-387000</v>
+      </c>
+      <c r="U94" s="3">
+        <v>-499000</v>
+      </c>
+      <c r="V94" s="3">
         <v>-603000</v>
       </c>
-      <c r="F94" s="3">
-        <v>-703000</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-680000</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-766000</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-689000</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-743000</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-618000</v>
-      </c>
-      <c r="L94" s="3">
-        <v>-780000</v>
-      </c>
-      <c r="M94" s="3">
-        <v>-639000</v>
-      </c>
-      <c r="N94" s="3">
-        <v>-301000</v>
-      </c>
-      <c r="O94" s="3">
-        <v>9000</v>
-      </c>
-      <c r="P94" s="3">
-        <v>-387000</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>-499000</v>
-      </c>
-      <c r="R94" s="3">
-        <v>-603000</v>
-      </c>
-      <c r="S94" s="3">
+      <c r="W94" s="3">
         <v>-408000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="X94" s="3">
         <v>-405000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="Y94" s="3">
         <v>-454000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="Z94" s="3">
         <v>-264000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="AA94" s="3">
         <v>-163000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="AB94" s="3">
         <v>362000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AC94" s="3">
         <v>-383000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AD94" s="3">
         <v>-351000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AE94" s="3">
         <v>422000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AF94" s="3">
         <v>-477000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AG94" s="3">
         <v>-386000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AH94" s="3">
         <v>-347000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AI94" s="3">
         <v>-284000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AJ94" s="3">
         <v>-256000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AK94" s="3">
         <v>-306000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AL94" s="3">
         <v>556000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AM94" s="3">
         <v>-44700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AN94" s="3">
         <v>-48000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AO94" s="3">
         <v>-27900</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -9047,94 +9978,98 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
+      <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
-        <v>172000</v>
+        <v>4900</v>
       </c>
       <c r="E96" s="3">
-        <v>174000</v>
+        <v>5000</v>
       </c>
       <c r="F96" s="3">
-        <v>175000</v>
+        <v>4900</v>
       </c>
       <c r="G96" s="3">
-        <v>175000</v>
+        <v>4600</v>
       </c>
       <c r="H96" s="3">
-        <v>176000</v>
+        <v>4600</v>
       </c>
       <c r="I96" s="3">
-        <v>175000</v>
-      </c>
-      <c r="J96" s="3">
-        <v>174000</v>
+        <v>4600</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="K96" s="3">
         <v>175000</v>
       </c>
       <c r="L96" s="3">
+        <v>176000</v>
+      </c>
+      <c r="M96" s="3">
+        <v>175000</v>
+      </c>
+      <c r="N96" s="3">
+        <v>174000</v>
+      </c>
+      <c r="O96" s="3">
+        <v>175000</v>
+      </c>
+      <c r="P96" s="3">
         <v>-261000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="Q96" s="3">
         <v>-351000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="R96" s="3">
         <v>-353000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="S96" s="3">
         <v>-178000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="T96" s="3">
         <v>-159000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="U96" s="3">
         <v>-158000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="V96" s="3">
         <v>-159000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="W96" s="3">
         <v>-158000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="X96" s="3">
         <v>-160000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="Y96" s="3">
         <v>-141000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="Z96" s="3">
         <v>-124000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="AA96" s="3">
         <v>-122000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="AB96" s="3">
         <v>-87000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AC96" s="3">
         <v>-67000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AD96" s="3">
         <v>-61000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AE96" s="3">
         <v>-333000</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-31000</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-31000</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-32000</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>-31000</v>
       </c>
       <c r="AF96" s="3">
         <v>-31000</v>
@@ -9146,16 +10081,28 @@
         <v>-32000</v>
       </c>
       <c r="AI96" s="3">
-        <v>0</v>
+        <v>-31000</v>
       </c>
       <c r="AJ96" s="3">
-        <v>0</v>
+        <v>-31000</v>
       </c>
       <c r="AK96" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="AL96" s="3">
+        <v>-32000</v>
+      </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -9261,8 +10208,20 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -9368,8 +10327,20 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -9475,123 +10446,147 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
-        <v>-762000</v>
+        <v>133600</v>
       </c>
       <c r="E100" s="3">
-        <v>-387000</v>
+        <v>-172500</v>
       </c>
       <c r="F100" s="3">
-        <v>-362000</v>
+        <v>-42400</v>
       </c>
       <c r="G100" s="3">
+        <v>27700</v>
+      </c>
+      <c r="H100" s="3">
+        <v>-114200</v>
+      </c>
+      <c r="I100" s="3">
+        <v>110300</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-64300</v>
+      </c>
+      <c r="K100" s="3">
         <v>-284000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="L100" s="3">
         <v>-342000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="M100" s="3">
         <v>-333000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="N100" s="3">
         <v>-309000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="O100" s="3">
         <v>-221000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="P100" s="3">
         <v>-815000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="Q100" s="3">
         <v>-656000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="R100" s="3">
         <v>-727000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="S100" s="3">
         <v>-406000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="T100" s="3">
         <v>-763000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="U100" s="3">
         <v>-646000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="V100" s="3">
         <v>-570000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="W100" s="3">
         <v>-409000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="X100" s="3">
         <v>-789000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="Y100" s="3">
         <v>-408000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="Z100" s="3">
         <v>-348000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="AA100" s="3">
         <v>-709000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="AB100" s="3">
         <v>-328000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AC100" s="3">
         <v>-369000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AD100" s="3">
         <v>-82000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AE100" s="3">
         <v>-360000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AF100" s="3">
         <v>-57000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AG100" s="3">
         <v>-704000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AH100" s="3">
         <v>-92000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AI100" s="3">
         <v>-72000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AJ100" s="3">
         <v>-126000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AK100" s="3">
         <v>-1127000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AL100" s="3">
         <v>-355000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AM100" s="3">
         <v>-4400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AN100" s="3">
         <v>-1400</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AO100" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D101" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="E101" s="3">
-        <v>-1000</v>
+      <c r="D101" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>91</v>
@@ -9599,14 +10594,14 @@
       <c r="G101" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="J101" s="3">
-        <v>-3000</v>
+      <c r="H101" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>91</v>
@@ -9620,180 +10615,204 @@
       <c r="N101" s="3">
         <v>-3000</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
       </c>
       <c r="Q101" s="3">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="R101" s="3">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
         <v>-1000</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
-      <c r="U101" s="3">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
         <v>4000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="Z101" s="3">
         <v>-3000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="AA101" s="3">
         <v>-4000</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
       <c r="AB101" s="3">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="AC101" s="3">
-        <v>-4000</v>
+        <v>0</v>
       </c>
       <c r="AD101" s="3">
         <v>-1000</v>
       </c>
       <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="AG101" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="AH101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AI101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AJ101" s="3">
         <v>1000</v>
       </c>
-      <c r="AG101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ101" s="3">
-        <v>0</v>
-      </c>
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
-        <v>-151000</v>
+        <v>62800</v>
       </c>
       <c r="E102" s="3">
-        <v>189000</v>
+        <v>11500</v>
       </c>
       <c r="F102" s="3">
-        <v>94000</v>
+        <v>-36600</v>
       </c>
       <c r="G102" s="3">
+        <v>76600</v>
+      </c>
+      <c r="H102" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="I102" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="J102" s="3">
+        <v>13500</v>
+      </c>
+      <c r="K102" s="3">
         <v>-206000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="L102" s="3">
         <v>-113000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="M102" s="3">
         <v>104000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="N102" s="3">
         <v>-220000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="O102" s="3">
         <v>-63000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="P102" s="3">
         <v>-800000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="Q102" s="3">
         <v>-540000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="R102" s="3">
         <v>-107000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="S102" s="3">
         <v>607000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="T102" s="3">
         <v>237000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="U102" s="3">
         <v>-95000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="V102" s="3">
         <v>-534000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="W102" s="3">
         <v>484000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="X102" s="3">
         <v>444000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="Y102" s="3">
         <v>1001000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="Z102" s="3">
         <v>416000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="AA102" s="3">
         <v>13000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="AB102" s="3">
         <v>909000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AC102" s="3">
         <v>252000</v>
       </c>
-      <c r="Z102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA102" s="3">
+      <c r="AD102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="3">
         <v>582000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AF102" s="3">
         <v>-126000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AG102" s="3">
         <v>-388000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AH102" s="3">
         <v>-299000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AI102" s="3">
         <v>150000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AJ102" s="3">
         <v>209000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AK102" s="3">
         <v>-901000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AL102" s="3">
         <v>649000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AM102" s="3">
         <v>84000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AN102" s="3">
         <v>155200</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AO102" s="3">
         <v>88400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GOLD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GOLD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="92">
   <si>
     <t>GOLD</t>
   </si>
@@ -656,524 +656,537 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="38" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="39" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>10350700</v>
+      </c>
+      <c r="E8" s="3">
         <v>6476900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3680800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2512000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3009100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2742300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2715100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2525000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2747000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3059000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2862000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2833000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2643000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2774000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2527000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2859000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2853000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3310000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2826000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2893000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2956000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3279000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3540000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3055000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2721000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2883000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2678000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2063000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2093000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1904000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1837000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1712000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1790000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2228000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1993000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2160000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>316700</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>356400</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>300000</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>10174100</v>
+      </c>
+      <c r="E9" s="3">
         <v>6383500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3607900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2430400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2968100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2697600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2671700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2482000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1914000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2166000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1902000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1936000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1928000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2093000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1815000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1850000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1739000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1905000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1768000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1704000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1712000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1814000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1927000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1900000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1776000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1987000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1889000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1545000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1490000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1577000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1315000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1176000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1152000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1411000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1270000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1277000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>167400</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>196700</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>169100</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>176600</v>
+      </c>
+      <c r="E10" s="3">
         <v>93400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>72900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>81700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>41000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>44800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>43400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>43000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>833000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>893000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>960000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>897000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>715000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>681000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>712000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1009000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1114000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1405000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1058000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1189000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1244000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1465000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1613000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1155000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>945000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>896000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>789000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>518000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>603000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>327000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>522000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>536000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>638000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>817000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>723000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>883000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>149300</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>159700</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>130900</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1215,8 +1228,9 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1256,86 +1270,89 @@
       <c r="O12" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="P12" s="3">
+      <c r="P12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q12" s="3">
         <v>106000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>77000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>100000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>67000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>82000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>67000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>77000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>61000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>74000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>72000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>78000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>71000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>40000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>86000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>98000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>74000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>87000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>89000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>97000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>73000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>98000</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>100000</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>81000</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>10900</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>8000</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>11200</v>
       </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1453,169 +1470,175 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>400</v>
+      </c>
+      <c r="E14" s="3">
         <v>100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-2400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-3600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>11700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-16700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>44000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-32000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>31000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>27000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>18000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1637000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>60000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>17000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>19000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>57000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>27000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>23000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-77000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>64000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-80000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>81000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-311000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>-514000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>-2726000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>27000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>44000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>451000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>495000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>67000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>28000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>1029000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>117000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>18000</v>
       </c>
-      <c r="AM14" s="3">
-        <v>0</v>
-      </c>
       <c r="AN14" s="3">
         <v>0</v>
       </c>
       <c r="AO14" s="3">
         <v>0</v>
       </c>
+      <c r="AP14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>7600</v>
+        <v>9400</v>
       </c>
       <c r="E15" s="3">
         <v>7600</v>
       </c>
       <c r="F15" s="3">
+        <v>7600</v>
+      </c>
+      <c r="G15" s="3">
         <v>8600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>5000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>4600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>4700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>495000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>268000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>526000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>501000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>516000</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1691,8 +1714,11 @@
       <c r="AO15" s="3">
         <v>0</v>
       </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1731,246 +1757,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>10261200</v>
+      </c>
+      <c r="E17" s="3">
         <v>6450800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3677700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2492900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3001900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2727300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2703100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2507200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2073000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2260000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2042000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2093000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2134000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3658000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1827000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1774000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1758000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1770000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1798000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1765000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1665000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1737000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1904000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2093000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1583000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>217000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>-670000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1681000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1666000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2176000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1988000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1536000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1264000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2514000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1585000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>602000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>192200</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>223900</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>196300</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>89500</v>
+      </c>
+      <c r="E18" s="3">
         <v>26100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>19200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>7300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>15100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>12000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>17800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>674000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>799000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>820000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>740000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>509000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-884000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>700000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1085000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1095000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1540000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1028000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1128000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1291000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1542000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1636000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>962000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1138000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2666000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>3348000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>382000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>427000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-272000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-151000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>176000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>526000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-286000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>408000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>1558000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>124500</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>132500</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>103700</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -2012,603 +2045,619 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-35000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>69000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-36000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-69000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-14000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>21000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>12000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-4000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-3000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-10000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-2000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-6000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>325000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-13000</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>-12000</v>
       </c>
       <c r="AE20" s="3">
         <v>-12000</v>
       </c>
       <c r="AF20" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="AG20" s="3">
         <v>-2000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-20000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>1000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>4000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>5000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>7000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>6000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-4800</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-4700</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>103800</v>
+      </c>
+      <c r="E21" s="3">
         <v>34000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>11900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>25600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>13000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>16900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>17700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>21700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1204000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>998000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1382000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1310000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1039000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-259000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1169000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1557000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1553000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2098000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1563000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1618000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1796000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2085000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2210000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1526000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1656000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>3563000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>3894000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>836000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>850000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>167000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>192000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>505000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>855000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>153000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>805000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1973000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>158600</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>263000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>113700</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E22" s="3">
         <v>16300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>12600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>12900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>13000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>10400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>10000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>9600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>80000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>78000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>88000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>86000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>98000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>84000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>87000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>85000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>86000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>85000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>90000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>81000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>85000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>79000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>81000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>80000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>83000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>431000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>109000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>106000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>108000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>115000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>110000</v>
-      </c>
-      <c r="AH22" s="3">
-        <v>137000</v>
       </c>
       <c r="AI22" s="3">
         <v>137000</v>
       </c>
       <c r="AJ22" s="3">
+        <v>137000</v>
+      </c>
+      <c r="AK22" s="3">
         <v>135000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>144000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>153000</v>
       </c>
-      <c r="AM22" s="3">
-        <v>0</v>
-      </c>
       <c r="AN22" s="3">
         <v>0</v>
       </c>
       <c r="AO22" s="3">
         <v>0</v>
       </c>
+      <c r="AP22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>81800</v>
+      </c>
+      <c r="E23" s="3">
         <v>15800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>13000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-9900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>8000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>10200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>34000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>661000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>771000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>803000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>766000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>474000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-947000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>625000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>996000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1007000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1456000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>935000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1037000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1204000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1462000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1555000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>880000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1049000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2560000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>3226000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>264000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>307000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-389000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-281000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>40000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>393000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-416000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>271000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>1411000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>119600</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>127800</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>109500</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>17700</v>
+      </c>
+      <c r="E24" s="3">
         <v>2200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-1200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3000</v>
-      </c>
-      <c r="K24" s="3">
-        <v>174000</v>
       </c>
       <c r="L24" s="3">
         <v>174000</v>
       </c>
       <c r="M24" s="3">
+        <v>174000</v>
+      </c>
+      <c r="N24" s="3">
         <v>218000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>264000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>205000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-131000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>215000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>279000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>301000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>304000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>323000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>343000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>374000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>404000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>284000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>258000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>386000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>784000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>791000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>41000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>167000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>776000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>105000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>116000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>201000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>394000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>314000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>274000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>34700</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>33500</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>32200</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2726,246 +2775,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>64000</v>
+      </c>
+      <c r="E26" s="3">
         <v>13500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>10200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-8700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>6000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>8400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>30900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>487000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>597000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>585000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>502000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>269000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-816000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>410000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>717000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>706000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1152000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>612000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>694000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>830000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1058000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1271000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>622000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>663000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1776000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>2435000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>223000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>140000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-1165000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-386000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-76000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>192000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-810000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-43000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>1137000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>84900</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>94300</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>77300</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>59500</v>
+      </c>
+      <c r="E27" s="3">
         <v>11600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>10300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-8500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>6600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>9000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>30900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>295000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>479000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>368000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>305000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>120000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-735000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>241000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>488000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>438000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>726000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>347000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>411000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>538000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>685000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>882000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>357000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>400000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1387000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>2277000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>194000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>111000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-1197000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-412000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-94000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>158000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-657000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-11000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>1084000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>69800</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>78500</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>65600</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3083,8 +3141,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3166,8 +3227,8 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>91</v>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>91</v>
@@ -3184,17 +3245,17 @@
       <c r="AI29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AJ29" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="AK29" s="3">
         <v>343000</v>
-      </c>
-      <c r="AK29" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="AL29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AM29" s="3">
-        <v>0</v>
+      <c r="AM29" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="AN29" s="3">
         <v>0</v>
@@ -3202,8 +3263,11 @@
       <c r="AO29" s="3">
         <v>0</v>
       </c>
+      <c r="AP29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -3321,8 +3385,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -3440,246 +3507,255 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E32" s="3">
         <v>300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>35000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-69000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>36000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>69000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>14000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-21000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-12000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>4000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>3000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>10000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>2000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1000</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>2000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>6000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-325000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>13000</v>
-      </c>
-      <c r="AD32" s="3">
-        <v>12000</v>
       </c>
       <c r="AE32" s="3">
         <v>12000</v>
       </c>
       <c r="AF32" s="3">
+        <v>12000</v>
+      </c>
+      <c r="AG32" s="3">
         <v>2000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>20000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-5000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-7000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-6000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>4800</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>4700</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-5800</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>59500</v>
+      </c>
+      <c r="E33" s="3">
         <v>11600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>10300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-8500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>6600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>9000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>30900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>295000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>479000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>368000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>305000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>120000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-735000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>241000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>488000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>438000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>726000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>347000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>411000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>538000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>685000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>882000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>357000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>400000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1387000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>2277000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>194000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>111000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-1197000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-412000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-94000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>158000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-314000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-11000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>1084000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>69800</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>78500</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>65600</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3797,251 +3873,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>59500</v>
+      </c>
+      <c r="E35" s="3">
         <v>11600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>10300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-8500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>6600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>9000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>30900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>295000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>479000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>368000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>305000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>120000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-735000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>241000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>488000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>438000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>726000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>347000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>411000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>538000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>685000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>882000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>357000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>400000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1387000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>2277000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>194000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>111000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-1197000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-412000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-94000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>158000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-314000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-11000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>1084000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>69800</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>78500</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>65600</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -4083,8 +4168,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -4126,127 +4212,131 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>143600</v>
+      </c>
+      <c r="E41" s="3">
         <v>152100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>89200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>77700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>114300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>37800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>46900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>48600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3942000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4148000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4261000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4157000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4377000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4440000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5240000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5780000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5887000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>5280000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5043000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>5138000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>5672000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5188000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4744000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3743000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3327000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3314000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2405000</v>
-      </c>
-      <c r="AD41" s="3">
-        <v>2153000</v>
       </c>
       <c r="AE41" s="3">
         <v>2153000</v>
       </c>
       <c r="AF41" s="3">
+        <v>2153000</v>
+      </c>
+      <c r="AG41" s="3">
         <v>1571000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1697000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2085000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2384000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>2234000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>2025000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>2926000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>600300</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>516300</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>361100</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
@@ -4364,751 +4454,772 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>250200</v>
+      </c>
+      <c r="E43" s="3">
         <v>652500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>368900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>211300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>197500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>126100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>157400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>140200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>654000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1178000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>561000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>603000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>557000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>554000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>499000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>577000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>640000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>623000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>600000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>554000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>530000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>558000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>509000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>407000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>371000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>363000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>311000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>427000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>383000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>248000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>189000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>194000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>173000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>239000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>224000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>190000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>236800</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>231400</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>223400</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>2812500</v>
+      </c>
+      <c r="E44" s="3">
         <v>1569900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1245500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1304600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1339600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1205300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1295900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1108200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1805000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1782000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1913000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1868000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1913000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1781000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1691000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1699000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1766000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1734000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1821000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1825000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1776000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1878000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>2111000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>2160000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>2159000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>2289000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>2265000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1930000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1966000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1852000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1898000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1940000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1887000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1890000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>2038000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>1901000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>124600</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>119000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>135800</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>434800</v>
+      </c>
+      <c r="E45" s="3">
         <v>947700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>390200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>134500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>92400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>112300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>136100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>136800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>880000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>127000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>684000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>742000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1691000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1690000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>786000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>754000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>722000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>612000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>547000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>522000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>806000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>519000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>495000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>609000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>594000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>921000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>529000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>333000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>372000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>307000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>319000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>356000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>352000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>321000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>455000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>486000</v>
       </c>
-      <c r="AM45" s="3">
-        <v>0</v>
-      </c>
       <c r="AN45" s="3">
         <v>0</v>
       </c>
       <c r="AO45" s="3">
         <v>0</v>
       </c>
+      <c r="AP45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>3668300</v>
+      </c>
+      <c r="E46" s="3">
         <v>3341700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2111300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1743500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1757900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1489700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1645500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1442200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7281000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>7438000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>7419000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>7370000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>8538000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>8465000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>8216000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>8810000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>9015000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>8249000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>8011000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>8039000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>8784000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>8143000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>7859000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>6919000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>6451000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>6887000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>5510000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4843000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>4874000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>3978000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>4103000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>4575000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>4796000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>4684000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>4742000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>5503000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>961600</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>866800</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>720300</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>39500</v>
+      </c>
+      <c r="E47" s="3">
         <v>38400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>31700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>33000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>38400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>48500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>51000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>50500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4178000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4264000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3998000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4004000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>3969000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>3983000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>4064000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>4113000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>4334000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>4594000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>4762000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>4715000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>4646000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>4670000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>4643000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>4587000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>4556000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>4527000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>4474000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>4459000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>4444000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1234000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1233000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1214000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1233000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>1213000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>1243000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>1218000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>1446800</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>1448600</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>1479500</v>
       </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>68700</v>
+      </c>
+      <c r="E48" s="3">
         <v>67200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>67000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>68400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>53600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>32400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>29000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>29800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>26648000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>26416000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>26621000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>26311000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>26084000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>25821000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>25329000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>25202000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>25153000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>24954000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>24747000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>24755000</v>
-      </c>
-      <c r="W48" s="3">
-        <v>24628000</v>
       </c>
       <c r="X48" s="3">
         <v>24628000</v>
       </c>
       <c r="Y48" s="3">
+        <v>24628000</v>
+      </c>
+      <c r="Z48" s="3">
         <v>24698000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>24727000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>24809000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>24141000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>24758000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>16890000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>16891000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>12826000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>13226000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>13727000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>13755000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>13806000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>13961000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>13943000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>1564000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>1560900</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>1567300</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>391400</v>
+      </c>
+      <c r="E49" s="3">
         <v>357500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>360800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>366000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>327900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>294000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>297700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>301600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3729000</v>
-      </c>
-      <c r="L49" s="3">
-        <v>3730000</v>
       </c>
       <c r="M49" s="3">
         <v>3730000</v>
@@ -5123,7 +5234,7 @@
         <v>3730000</v>
       </c>
       <c r="Q49" s="3">
-        <v>4918000</v>
+        <v>3730000</v>
       </c>
       <c r="R49" s="3">
         <v>4918000</v>
@@ -5132,73 +5243,76 @@
         <v>4918000</v>
       </c>
       <c r="T49" s="3">
+        <v>4918000</v>
+      </c>
+      <c r="U49" s="3">
         <v>4919000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4920000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4927000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4937000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>4938000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>4939000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>4983000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>4999000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>4995000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>5025000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3064000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3037000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1403000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1559000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1560000</v>
-      </c>
-      <c r="AI49" s="3">
-        <v>1585000</v>
       </c>
       <c r="AJ49" s="3">
         <v>1585000</v>
       </c>
       <c r="AK49" s="3">
+        <v>1585000</v>
+      </c>
+      <c r="AL49" s="3">
         <v>1556000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>1586000</v>
       </c>
-      <c r="AM49" s="3">
-        <v>0</v>
-      </c>
       <c r="AN49" s="3">
         <v>0</v>
       </c>
       <c r="AO49" s="3">
         <v>0</v>
       </c>
+      <c r="AP49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -5316,8 +5430,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -5435,127 +5552,133 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E52" s="3">
         <v>7100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>8600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4007000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3776000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3800000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3852000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3812000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3966000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3915000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3799000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3886000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4174000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4194000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4092000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3853000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>4127000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3977000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3964000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>4124000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>3842000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>4100000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>3346000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>3383000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>3190000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>3997000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>4046000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>4027000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>4020000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>3570000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>3557000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>163600</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>164700</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>151000</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -5673,127 +5796,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>4174100</v>
+      </c>
+      <c r="E54" s="3">
         <v>3811900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2579400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2215400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2183500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1869300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2029000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1827800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>45843000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>45811000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>45595000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>45286000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>46152000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>45965000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>46442000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>46842000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>47306000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>46890000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>46634000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>46528000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>46848000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>46506000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>46116000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>45180000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>44939000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>44392000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>43867000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>32602000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>32629000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>22631000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>24118000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>25122000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>25396000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>25308000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>25072000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>25807000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>4136000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>4041000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>3918100</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -5835,8 +5964,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -5878,180 +6008,184 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>71900</v>
+      </c>
+      <c r="E57" s="3">
         <v>76900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>69100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>12800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>18600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>12000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1360000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>678000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1584000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1525000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1504000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1556000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1571000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1537000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1525000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1448000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1444000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1157000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1168000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1458000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1032000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1072000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1140000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1155000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1337000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1064000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1213000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1101000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1125000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>944000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1046000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1059000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1118000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1044000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>120000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>127400</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>136700</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>1535800</v>
+      </c>
+      <c r="E58" s="3">
         <v>599400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>445100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>540100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>605800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>592300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>590300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>558100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>12000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>43000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>8000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>13000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>12000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>13000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>12000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>13000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>14000</v>
-      </c>
-      <c r="T58" s="3">
-        <v>15000</v>
       </c>
       <c r="U58" s="3">
         <v>15000</v>
@@ -6060,412 +6194,421 @@
         <v>15000</v>
       </c>
       <c r="W58" s="3">
+        <v>15000</v>
+      </c>
+      <c r="X58" s="3">
         <v>13000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>20000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>21000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>26000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>29000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>375000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>66000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>303000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>308000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>43000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>49000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>680000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>57000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>59000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>63000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>116000</v>
       </c>
-      <c r="AM58" s="3">
-        <v>0</v>
-      </c>
       <c r="AN58" s="3">
         <v>0</v>
       </c>
       <c r="AO58" s="3">
         <v>0</v>
       </c>
+      <c r="AP58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>1467300</v>
+      </c>
+      <c r="E59" s="3">
         <v>2052900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1006300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>537000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>480200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>332500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>378900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>296900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>823000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>760000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>826000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>732000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1690000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1551000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>605000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>680000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>708000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>623000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>521000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>626000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1150000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>742000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>698000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>713000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>801000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>846000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>441000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>415000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>463000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>524000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>375000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>536000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>595000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>629000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>557000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>386000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>71100</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>61000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>34700</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>3119300</v>
+      </c>
+      <c r="E60" s="3">
         <v>2754200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1543100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1114100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1129000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>944600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>989600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>883800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2195000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2356000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2418000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2270000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3206000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3120000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2188000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2230000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2247000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2086000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1980000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1798000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2331000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2220000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1751000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1811000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1970000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2376000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1844000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1782000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1984000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1668000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1549000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2160000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>1698000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>1747000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>1738000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>1546000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>191100</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>188400</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>171400</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>118400</v>
+      </c>
+      <c r="E61" s="3">
         <v>319400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>310500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>366600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>334800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>235500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>348200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>249000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4713000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5180000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4767000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4761000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4765000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4769000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>5083000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>5131000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>5130000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>5135000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>5139000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>5137000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>5140000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>5135000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>5140000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>5142000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>5150000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>5161000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>5494000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>5504000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>5499000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>5695000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>5696000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>5712000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>6344000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>6364000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>6384000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>7328000</v>
-      </c>
-      <c r="AM61" s="3">
-        <v>2800</v>
       </c>
       <c r="AN61" s="3">
         <v>2800</v>
@@ -6473,127 +6616,133 @@
       <c r="AO61" s="3">
         <v>2800</v>
       </c>
+      <c r="AP61" s="3">
+        <v>2800</v>
+      </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E62" s="3">
         <v>11100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>10500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>13700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>11000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3246000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2202000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3345000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3484000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3593000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>6787000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>6864000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>6947000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>7303000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>7362000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>7425000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>7419000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>7298000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>7441000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>7575000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>7481000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>7464000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>7028000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>8129000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>6849000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>6844000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>5883000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>6187000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>6144000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>6088000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>6130000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>5328000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>5248000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>101700</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>97800</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>88900</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -6711,8 +6860,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6830,8 +6982,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -6949,127 +7104,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>3267200</v>
+      </c>
+      <c r="E66" s="3">
         <v>3103100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1882300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1512800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1486700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1203500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1364300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1166000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>13626000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>13809000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>13897000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>13801000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>14834000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>23194000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>22578000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>22731000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>23131000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>23033000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>23016000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>22839000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>23174000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>23165000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>23317000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>23148000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>23252000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>22960000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>23718000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>16856000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>17031000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>15038000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>15211000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>15766000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>15917000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>16022000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>15458000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>16165000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>559400</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>542300</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>502400</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -7111,8 +7272,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -7230,8 +7392,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -7349,8 +7514,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -7468,8 +7636,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -7587,127 +7758,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>518600</v>
+      </c>
+      <c r="E72" s="3">
         <v>464800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>458100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>464100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>458700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>473100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>466600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>466800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-6594000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-6713000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-7016000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-7208000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-7338000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-7282000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-6284000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-6173000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-6306000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-6566000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-7132000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-7320000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-7571000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-7949000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-8474000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-9214000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-9446000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-9722000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-11020000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-13227000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-13351000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-13453000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-12148000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-11701000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-11572000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-11759000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-11428000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-11382000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>2014900</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>1956700</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>1874200</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -7825,8 +8002,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -7944,8 +8124,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -8063,127 +8246,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>847300</v>
+      </c>
+      <c r="E76" s="3">
         <v>653800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>644000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>649500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>643600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>612700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>611100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>607600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>23463000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>23341000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>23020000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>22839000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>22713000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>22771000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>23864000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>24111000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>24175000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>23857000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>23618000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>23689000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>23674000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>23341000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>22799000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>22032000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>21687000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>21432000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>20149000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>15746000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>15598000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>7593000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>8907000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>9356000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>9479000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>9286000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>9614000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>9642000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>3576600</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>3498700</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>3415700</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -8301,251 +8490,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>59500</v>
+      </c>
+      <c r="E81" s="3">
         <v>11600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>10300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-8500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>6600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>9000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>30900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>295000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>479000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>368000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>305000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>120000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-735000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>241000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>488000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>438000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>726000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>347000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>411000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>538000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>685000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>882000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>357000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>400000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1387000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>2277000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>194000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>111000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-1197000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-412000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-94000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>158000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-314000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-11000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>1084000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>69800</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>78500</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>65600</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -8587,13 +8785,14 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="E83" s="3">
         <v>800</v>
@@ -8605,7 +8804,7 @@
         <v>800</v>
       </c>
       <c r="H83" s="3">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="I83" s="3">
         <v>600</v>
@@ -8614,100 +8813,103 @@
         <v>600</v>
       </c>
       <c r="K83" s="3">
+        <v>600</v>
+      </c>
+      <c r="L83" s="3">
         <v>495000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>603000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>457000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>476000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>460000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>604000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>457000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>476000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>460000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>557000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>538000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>500000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>507000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>544000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>574000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>566000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>524000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>572000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>559000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>466000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>435000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>441000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>363000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>328000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>325000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>434000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>390000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>409000</v>
       </c>
-      <c r="AM83" s="3">
-        <v>0</v>
-      </c>
       <c r="AN83" s="3">
         <v>0</v>
       </c>
       <c r="AO83" s="3">
         <v>0</v>
       </c>
+      <c r="AP83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -8825,8 +9027,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -8944,8 +9149,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -9063,8 +9271,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -9182,8 +9393,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -9301,127 +9515,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-42600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>195400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>67000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>102800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>110100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-127500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>82900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>760000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>997000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1127000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>832000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>776000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>795000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>758000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>924000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1004000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1387000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1050000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>639000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1302000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1638000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1859000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1031000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>889000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>875000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1004000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>434000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>520000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>411000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>706000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>141000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>507000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>590000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>532000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>448000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>133100</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>204700</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>119300</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -9463,127 +9683,131 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-728000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-861000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-768000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-769000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-688000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-891000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-792000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-755000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-611000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-669000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-569000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-658000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-539000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-546000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-548000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-509000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-451000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-446000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-502000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-379000</v>
-      </c>
-      <c r="AE91" s="3">
-        <v>-374000</v>
       </c>
       <c r="AF91" s="3">
         <v>-374000</v>
       </c>
       <c r="AG91" s="3">
+        <v>-374000</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-387000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-313000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-326000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-350000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-307000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-405000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-41300</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-50300</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-32000</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -9701,8 +9925,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -9820,127 +10047,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-24100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-28100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-11400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-61200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-54000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>15500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-680000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-766000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-689000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-743000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-618000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-780000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-639000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-301000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>9000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-387000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-499000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-603000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-408000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-405000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-454000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-264000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-163000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>362000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-383000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-351000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>422000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-477000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-386000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-347000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-284000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-256000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-306000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>556000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-44700</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-48000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-27900</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -9982,22 +10215,23 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E96" s="3">
         <v>4900</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>5000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>4900</v>
-      </c>
-      <c r="G96" s="3">
-        <v>4600</v>
       </c>
       <c r="H96" s="3">
         <v>4600</v>
@@ -10005,83 +10239,83 @@
       <c r="I96" s="3">
         <v>4600</v>
       </c>
-      <c r="J96" s="3" t="s">
+      <c r="J96" s="3">
+        <v>4600</v>
+      </c>
+      <c r="K96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>175000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>176000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>175000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>174000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>175000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-261000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-351000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-353000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-178000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-159000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-158000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-159000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-158000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-160000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-141000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-124000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-122000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-87000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-67000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-61000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-333000</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>-31000</v>
       </c>
       <c r="AG96" s="3">
         <v>-31000</v>
       </c>
       <c r="AH96" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-32000</v>
-      </c>
-      <c r="AI96" s="3">
-        <v>-31000</v>
       </c>
       <c r="AJ96" s="3">
         <v>-31000</v>
@@ -10090,19 +10324,22 @@
         <v>-31000</v>
       </c>
       <c r="AL96" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="AM96" s="3">
         <v>-32000</v>
       </c>
-      <c r="AM96" s="3">
-        <v>0</v>
-      </c>
       <c r="AN96" s="3">
         <v>0</v>
       </c>
       <c r="AO96" s="3">
         <v>0</v>
       </c>
+      <c r="AP96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -10220,8 +10457,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -10339,8 +10579,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -10458,127 +10701,133 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>15400</v>
+      </c>
+      <c r="E100" s="3">
         <v>133600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-172500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-42400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>27700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-114200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>110300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-64300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-284000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-342000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-333000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-309000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-221000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-815000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-656000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-727000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-406000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-763000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-646000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-570000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-409000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-789000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-408000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-348000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-709000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-328000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-369000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-82000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-360000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-57000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-704000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-92000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-72000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-126000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-1127000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-355000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-4400</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-1400</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
@@ -10606,29 +10855,29 @@
       <c r="K101" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="M101" s="3">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="N101" s="3">
         <v>-3000</v>
       </c>
-      <c r="O101" s="3" t="s">
+      <c r="O101" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="P101" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
       <c r="Q101" s="3">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="R101" s="3">
         <v>-3000</v>
       </c>
       <c r="S101" s="3">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="T101" s="3">
         <v>0</v>
@@ -10640,50 +10889,50 @@
         <v>0</v>
       </c>
       <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
         <v>-1000</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
       <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
         <v>4000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
-      </c>
       <c r="AC101" s="3">
         <v>0</v>
       </c>
       <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE101" s="3">
-        <v>0</v>
-      </c>
       <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
         <v>-3000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-4000</v>
-      </c>
-      <c r="AH101" s="3">
-        <v>-1000</v>
       </c>
       <c r="AI101" s="3">
         <v>-1000</v>
       </c>
       <c r="AJ101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AK101" s="3">
         <v>1000</v>
       </c>
-      <c r="AK101" s="3">
-        <v>0</v>
-      </c>
       <c r="AL101" s="3">
         <v>0</v>
       </c>
@@ -10696,123 +10945,129 @@
       <c r="AO101" s="3">
         <v>0</v>
       </c>
+      <c r="AP101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="E102" s="3">
         <v>62800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>11500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-36600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>76600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-9200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>13500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-206000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-113000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>104000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-220000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-63000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-800000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-540000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-107000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>607000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>237000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-95000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-534000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>484000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>444000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1001000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>416000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>13000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>909000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>252000</v>
       </c>
-      <c r="AD102" s="3">
-        <v>0</v>
-      </c>
       <c r="AE102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="3">
         <v>582000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-126000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-388000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-299000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>150000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>209000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-901000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>649000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>84000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>155200</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>88400</v>
       </c>
     </row>
